--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>284667</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>5.42999982833862</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>5.44999980926514</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>494817</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>5.43499994277954</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>5.41499996185303</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>5.30999994277954</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>463249</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>5.55999994277954</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>5.31500005722046</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>5.32999992370605</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>5.53999996185303</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>352012</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>5.53000020980835</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>5.53000020980835</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>5.57999992370605</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>346672</v>
+        <v>344818</v>
       </c>
       <c r="C2715" t="n">
-        <v>5.80000019073486</v>
+        <v>5.86499977111816</v>
       </c>
       <c r="D2715" t="n">
-        <v>5.61999988555908</v>
+        <v>5.67999982833862</v>
       </c>
       <c r="E2715" t="n">
+        <v>5.86499977111816</v>
+      </c>
+      <c r="F2715" t="n">
         <v>5.67999982833862</v>
-      </c>
-      <c r="F2715" t="n">
-        <v>5.74499988555908</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>445613</v>
+        <v>346672</v>
       </c>
       <c r="C2716" t="n">
-        <v>5.70499992370605</v>
+        <v>5.80000019073486</v>
       </c>
       <c r="D2716" t="n">
-        <v>5.55999994277954</v>
+        <v>5.61999988555908</v>
       </c>
       <c r="E2716" t="n">
-        <v>5.69999980926514</v>
+        <v>5.67999982833862</v>
       </c>
       <c r="F2716" t="n">
-        <v>5.59499979019165</v>
+        <v>5.74499988555908</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>532051</v>
+        <v>445613</v>
       </c>
       <c r="C2717" t="n">
-        <v>5.63000011444092</v>
+        <v>5.70499992370605</v>
       </c>
       <c r="D2717" t="n">
-        <v>5.45499992370605</v>
+        <v>5.55999994277954</v>
       </c>
       <c r="E2717" t="n">
-        <v>5.59999990463257</v>
+        <v>5.69999980926514</v>
       </c>
       <c r="F2717" t="n">
-        <v>5.53499984741211</v>
+        <v>5.59499979019165</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>228930</v>
+        <v>532051</v>
       </c>
       <c r="C2718" t="n">
-        <v>5.55499982833862</v>
+        <v>5.63000011444092</v>
       </c>
       <c r="D2718" t="n">
-        <v>5.48999977111816</v>
+        <v>5.45499992370605</v>
       </c>
       <c r="E2718" t="n">
-        <v>5.52500009536743</v>
+        <v>5.59999990463257</v>
       </c>
       <c r="F2718" t="n">
-        <v>5.50500011444092</v>
+        <v>5.53499984741211</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>284667</v>
+        <v>228930</v>
       </c>
       <c r="C2719" t="n">
-        <v>5.5</v>
+        <v>5.55499982833862</v>
       </c>
       <c r="D2719" t="n">
-        <v>5.42999982833862</v>
+        <v>5.48999977111816</v>
       </c>
       <c r="E2719" t="n">
-        <v>5.5</v>
+        <v>5.52500009536743</v>
       </c>
       <c r="F2719" t="n">
-        <v>5.44999980926514</v>
+        <v>5.50500011444092</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>494817</v>
+        <v>284667</v>
       </c>
       <c r="C2720" t="n">
-        <v>5.43499994277954</v>
+        <v>5.5</v>
       </c>
       <c r="D2720" t="n">
-        <v>5.30999994277954</v>
+        <v>5.42999982833862</v>
       </c>
       <c r="E2720" t="n">
-        <v>5.41499996185303</v>
+        <v>5.5</v>
       </c>
       <c r="F2720" t="n">
-        <v>5.30999994277954</v>
+        <v>5.44999980926514</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>463249</v>
+        <v>494817</v>
       </c>
       <c r="C2721" t="n">
-        <v>5.55999994277954</v>
+        <v>5.43499994277954</v>
       </c>
       <c r="D2721" t="n">
-        <v>5.31500005722046</v>
+        <v>5.30999994277954</v>
       </c>
       <c r="E2721" t="n">
-        <v>5.32999992370605</v>
+        <v>5.41499996185303</v>
       </c>
       <c r="F2721" t="n">
-        <v>5.53999996185303</v>
+        <v>5.30999994277954</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>352012</v>
+        <v>463249</v>
       </c>
       <c r="C2722" t="n">
-        <v>5.625</v>
+        <v>5.55999994277954</v>
       </c>
       <c r="D2722" t="n">
-        <v>5.53000020980835</v>
+        <v>5.31500005722046</v>
       </c>
       <c r="E2722" t="n">
-        <v>5.53000020980835</v>
+        <v>5.32999992370605</v>
       </c>
       <c r="F2722" t="n">
-        <v>5.57999992370605</v>
+        <v>5.53999996185303</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>336606</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>5.59999990463257</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>5.49499988555908</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>5.57000017166138</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>5.51000022888184</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>5.8600001335144</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>5.80000019073486</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>203397</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>5.92000007629395</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>5.81500005722046</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>5.82000017166138</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>5.82000017166138</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>5.8899998664856</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>303812</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>5.97499990463257</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>5.82499980926514</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>5.8899998664856</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>5.8899998664856</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>5.82499980926514</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>309213</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>5.84499979019165</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>5.67999982833862</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>5.80000019073486</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>5.80000019073486</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>5.68499994277954</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>189753</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>5.84499979019165</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>5.73000001907349</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>5.73999977111816</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>224446</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>5.875</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>5.78499984741211</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>5.79500007629395</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>5.81500005722046</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/OVS.MI.xlsx
+++ b/data/OVS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.98100709915161</v>
       </c>
       <c r="G2" t="n">
-        <v>4.92771005630493</v>
+        <v>4.92771053314209</v>
       </c>
       <c r="H2" t="n">
         <v>151718</v>
@@ -485,7 +485,7 @@
         <v>5.65579891204834</v>
       </c>
       <c r="G4" t="n">
-        <v>4.65977334976196</v>
+        <v>4.65977382659912</v>
       </c>
       <c r="H4" t="n">
         <v>362567</v>
@@ -543,7 +543,7 @@
         <v>5.60395383834839</v>
       </c>
       <c r="G6" t="n">
-        <v>4.61705827713013</v>
+        <v>4.61705875396729</v>
       </c>
       <c r="H6" t="n">
         <v>397030</v>
@@ -630,7 +630,7 @@
         <v>5.86789083480835</v>
       </c>
       <c r="G9" t="n">
-        <v>4.83451461791992</v>
+        <v>4.83451509475708</v>
       </c>
       <c r="H9" t="n">
         <v>511981</v>
@@ -659,7 +659,7 @@
         <v>5.57096195220947</v>
       </c>
       <c r="G10" t="n">
-        <v>4.58987665176392</v>
+        <v>4.58987760543823</v>
       </c>
       <c r="H10" t="n">
         <v>362578</v>
@@ -717,7 +717,7 @@
         <v>5.50497817993164</v>
       </c>
       <c r="G12" t="n">
-        <v>4.53551292419434</v>
+        <v>4.53551340103149</v>
       </c>
       <c r="H12" t="n">
         <v>402675</v>
@@ -775,7 +775,7 @@
         <v>5.04780006408691</v>
       </c>
       <c r="G14" t="n">
-        <v>4.15884780883789</v>
+        <v>4.15884828567505</v>
       </c>
       <c r="H14" t="n">
         <v>688014</v>
@@ -862,7 +862,7 @@
         <v>5.29288482666016</v>
       </c>
       <c r="G17" t="n">
-        <v>4.36077117919922</v>
+        <v>4.36077070236206</v>
       </c>
       <c r="H17" t="n">
         <v>123825</v>
@@ -920,7 +920,7 @@
         <v>5.34001684188843</v>
       </c>
       <c r="G19" t="n">
-        <v>4.39960241317749</v>
+        <v>4.39960289001465</v>
       </c>
       <c r="H19" t="n">
         <v>177186</v>
@@ -949,7 +949,7 @@
         <v>5.35886907577515</v>
       </c>
       <c r="G20" t="n">
-        <v>4.41513538360596</v>
+        <v>4.41513586044312</v>
       </c>
       <c r="H20" t="n">
         <v>380092</v>
@@ -978,7 +978,7 @@
         <v>5.27874612808228</v>
       </c>
       <c r="G21" t="n">
-        <v>4.34912157058716</v>
+        <v>4.34912204742432</v>
       </c>
       <c r="H21" t="n">
         <v>299124</v>
@@ -1036,7 +1036,7 @@
         <v>5.45313310623169</v>
       </c>
       <c r="G23" t="n">
-        <v>4.49279880523682</v>
+        <v>4.49279832839966</v>
       </c>
       <c r="H23" t="n">
         <v>259609</v>
@@ -1123,7 +1123,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G26" t="n">
-        <v>4.23262739181519</v>
+        <v>4.23262786865234</v>
       </c>
       <c r="H26" t="n">
         <v>220639</v>
@@ -1181,7 +1181,7 @@
         <v>4.78386306762695</v>
       </c>
       <c r="G28" t="n">
-        <v>3.94139099121094</v>
+        <v>3.9413914680481</v>
       </c>
       <c r="H28" t="n">
         <v>409255</v>
@@ -1210,7 +1210,7 @@
         <v>5.08079290390015</v>
       </c>
       <c r="G29" t="n">
-        <v>4.18602991104126</v>
+        <v>4.18603038787842</v>
       </c>
       <c r="H29" t="n">
         <v>367369</v>
@@ -1268,7 +1268,7 @@
         <v>5.014808177948</v>
       </c>
       <c r="G31" t="n">
-        <v>4.13166522979736</v>
+        <v>4.13166475296021</v>
       </c>
       <c r="H31" t="n">
         <v>308870</v>
@@ -1297,7 +1297,7 @@
         <v>5.20333480834961</v>
       </c>
       <c r="G32" t="n">
-        <v>4.28699159622192</v>
+        <v>4.28699207305908</v>
       </c>
       <c r="H32" t="n">
         <v>99612</v>
@@ -1471,7 +1471,7 @@
         <v>5.33058977127075</v>
       </c>
       <c r="G38" t="n">
-        <v>4.39183616638184</v>
+        <v>4.39183568954468</v>
       </c>
       <c r="H38" t="n">
         <v>67703</v>
@@ -1500,7 +1500,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G39" t="n">
-        <v>4.17826366424561</v>
+        <v>4.17826318740845</v>
       </c>
       <c r="H39" t="n">
         <v>287338</v>
@@ -1529,7 +1529,7 @@
         <v>5.03366088867188</v>
       </c>
       <c r="G40" t="n">
-        <v>4.14719820022583</v>
+        <v>4.14719867706299</v>
       </c>
       <c r="H40" t="n">
         <v>215759</v>
@@ -1558,7 +1558,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G41" t="n">
-        <v>4.17826366424561</v>
+        <v>4.17826318740845</v>
       </c>
       <c r="H41" t="n">
         <v>269796</v>
@@ -1645,7 +1645,7 @@
         <v>5.42014122009277</v>
       </c>
       <c r="G44" t="n">
-        <v>4.46561670303345</v>
+        <v>4.46561717987061</v>
       </c>
       <c r="H44" t="n">
         <v>126723</v>
@@ -1703,7 +1703,7 @@
         <v>5.65579891204834</v>
       </c>
       <c r="G46" t="n">
-        <v>4.65977334976196</v>
+        <v>4.65977382659912</v>
       </c>
       <c r="H46" t="n">
         <v>231609</v>
@@ -1761,7 +1761,7 @@
         <v>5.59924077987671</v>
       </c>
       <c r="G48" t="n">
-        <v>4.61317539215088</v>
+        <v>4.61317586898804</v>
       </c>
       <c r="H48" t="n">
         <v>72641</v>
@@ -1819,7 +1819,7 @@
         <v>5.42014122009277</v>
       </c>
       <c r="G50" t="n">
-        <v>4.46561670303345</v>
+        <v>4.46561717987061</v>
       </c>
       <c r="H50" t="n">
         <v>77148</v>
@@ -1877,7 +1877,7 @@
         <v>5.50497817993164</v>
       </c>
       <c r="G52" t="n">
-        <v>4.53551292419434</v>
+        <v>4.53551340103149</v>
       </c>
       <c r="H52" t="n">
         <v>266319</v>
@@ -1964,7 +1964,7 @@
         <v>5.20804786682129</v>
       </c>
       <c r="G55" t="n">
-        <v>4.29087400436401</v>
+        <v>4.29087495803833</v>
       </c>
       <c r="H55" t="n">
         <v>122760</v>
@@ -1993,7 +1993,7 @@
         <v>5.25989294052124</v>
       </c>
       <c r="G56" t="n">
-        <v>4.33358907699585</v>
+        <v>4.33358955383301</v>
       </c>
       <c r="H56" t="n">
         <v>103535</v>
@@ -2022,7 +2022,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G57" t="n">
-        <v>4.30640745162964</v>
+        <v>4.3064079284668</v>
       </c>
       <c r="H57" t="n">
         <v>107705</v>
@@ -2051,7 +2051,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G58" t="n">
-        <v>4.30640745162964</v>
+        <v>4.3064079284668</v>
       </c>
       <c r="H58" t="n">
         <v>83676</v>
@@ -2080,7 +2080,7 @@
         <v>5.09493207931519</v>
       </c>
       <c r="G59" t="n">
-        <v>4.19767904281616</v>
+        <v>4.19767951965332</v>
       </c>
       <c r="H59" t="n">
         <v>77928</v>
@@ -2167,7 +2167,7 @@
         <v>4.82628202438354</v>
       </c>
       <c r="G62" t="n">
-        <v>3.97634029388428</v>
+        <v>3.97633981704712</v>
       </c>
       <c r="H62" t="n">
         <v>621220</v>
@@ -2196,7 +2196,7 @@
         <v>4.85456085205078</v>
       </c>
       <c r="G63" t="n">
-        <v>3.99963903427124</v>
+        <v>3.99963855743408</v>
       </c>
       <c r="H63" t="n">
         <v>251931</v>
@@ -2254,7 +2254,7 @@
         <v>5.00066900253296</v>
       </c>
       <c r="G65" t="n">
-        <v>4.12001609802246</v>
+        <v>4.12001657485962</v>
       </c>
       <c r="H65" t="n">
         <v>214443</v>
@@ -2341,7 +2341,7 @@
         <v>4.77443695068359</v>
       </c>
       <c r="G68" t="n">
-        <v>3.93362522125244</v>
+        <v>3.9336256980896</v>
       </c>
       <c r="H68" t="n">
         <v>245991</v>
@@ -2457,7 +2457,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G72" t="n">
-        <v>4.17826366424561</v>
+        <v>4.17826318740845</v>
       </c>
       <c r="H72" t="n">
         <v>334565</v>
@@ -2486,7 +2486,7 @@
         <v>5.0289478302002</v>
       </c>
       <c r="G73" t="n">
-        <v>4.14331531524658</v>
+        <v>4.14331579208374</v>
       </c>
       <c r="H73" t="n">
         <v>152381</v>
@@ -2515,7 +2515,7 @@
         <v>5.35415601730347</v>
       </c>
       <c r="G74" t="n">
-        <v>4.41125154495239</v>
+        <v>4.41125202178955</v>
       </c>
       <c r="H74" t="n">
         <v>1035612</v>
@@ -2544,7 +2544,7 @@
         <v>5.42014122009277</v>
       </c>
       <c r="G75" t="n">
-        <v>4.46561670303345</v>
+        <v>4.46561717987061</v>
       </c>
       <c r="H75" t="n">
         <v>601470</v>
@@ -2602,7 +2602,7 @@
         <v>5.40128803253174</v>
       </c>
       <c r="G77" t="n">
-        <v>4.45008420944214</v>
+        <v>4.45008373260498</v>
       </c>
       <c r="H77" t="n">
         <v>26907526</v>
@@ -2631,7 +2631,7 @@
         <v>5.35886907577515</v>
       </c>
       <c r="G78" t="n">
-        <v>4.41513538360596</v>
+        <v>4.41513586044312</v>
       </c>
       <c r="H78" t="n">
         <v>1003784</v>
@@ -2660,7 +2660,7 @@
         <v>5.34472990036011</v>
       </c>
       <c r="G79" t="n">
-        <v>4.40348529815674</v>
+        <v>4.4034857749939</v>
       </c>
       <c r="H79" t="n">
         <v>438318</v>
@@ -2718,7 +2718,7 @@
         <v>5.35415601730347</v>
       </c>
       <c r="G81" t="n">
-        <v>4.41125154495239</v>
+        <v>4.41125202178955</v>
       </c>
       <c r="H81" t="n">
         <v>623284</v>
@@ -2776,7 +2776,7 @@
         <v>5.32116413116455</v>
       </c>
       <c r="G83" t="n">
-        <v>4.38407039642334</v>
+        <v>4.38406991958618</v>
       </c>
       <c r="H83" t="n">
         <v>576176</v>
@@ -2834,7 +2834,7 @@
         <v>5.36829614639282</v>
       </c>
       <c r="G85" t="n">
-        <v>4.42290210723877</v>
+        <v>4.42290258407593</v>
       </c>
       <c r="H85" t="n">
         <v>299514</v>
@@ -2863,7 +2863,7 @@
         <v>5.40128803253174</v>
       </c>
       <c r="G86" t="n">
-        <v>4.45008420944214</v>
+        <v>4.45008373260498</v>
       </c>
       <c r="H86" t="n">
         <v>941829</v>
@@ -2892,7 +2892,7 @@
         <v>5.40600109100342</v>
       </c>
       <c r="G87" t="n">
-        <v>4.45396614074707</v>
+        <v>4.45396709442139</v>
       </c>
       <c r="H87" t="n">
         <v>917247</v>
@@ -2950,7 +2950,7 @@
         <v>5.35415601730347</v>
       </c>
       <c r="G89" t="n">
-        <v>4.41125154495239</v>
+        <v>4.41125202178955</v>
       </c>
       <c r="H89" t="n">
         <v>351885</v>
@@ -3008,7 +3008,7 @@
         <v>5.50497817993164</v>
       </c>
       <c r="G91" t="n">
-        <v>4.53551292419434</v>
+        <v>4.53551340103149</v>
       </c>
       <c r="H91" t="n">
         <v>1662969</v>
@@ -3037,7 +3037,7 @@
         <v>5.42485380172729</v>
       </c>
       <c r="G92" t="n">
-        <v>4.46949863433838</v>
+        <v>4.46949911117554</v>
       </c>
       <c r="H92" t="n">
         <v>389386</v>
@@ -3066,7 +3066,7 @@
         <v>5.42014122009277</v>
       </c>
       <c r="G93" t="n">
-        <v>4.46561670303345</v>
+        <v>4.46561717987061</v>
       </c>
       <c r="H93" t="n">
         <v>372936</v>
@@ -3095,7 +3095,7 @@
         <v>5.40600109100342</v>
       </c>
       <c r="G94" t="n">
-        <v>4.45396614074707</v>
+        <v>4.45396709442139</v>
       </c>
       <c r="H94" t="n">
         <v>197639</v>
@@ -3124,7 +3124,7 @@
         <v>5.34472990036011</v>
       </c>
       <c r="G95" t="n">
-        <v>4.40348529815674</v>
+        <v>4.4034857749939</v>
       </c>
       <c r="H95" t="n">
         <v>536003</v>
@@ -3211,7 +3211,7 @@
         <v>5.51911687850952</v>
       </c>
       <c r="G98" t="n">
-        <v>4.54716205596924</v>
+        <v>4.5471625328064</v>
       </c>
       <c r="H98" t="n">
         <v>9303459</v>
@@ -3269,7 +3269,7 @@
         <v>5.75006198883057</v>
       </c>
       <c r="G100" t="n">
-        <v>4.73743581771851</v>
+        <v>4.73743629455566</v>
       </c>
       <c r="H100" t="n">
         <v>588301</v>
@@ -3327,7 +3327,7 @@
         <v>5.71707010269165</v>
       </c>
       <c r="G102" t="n">
-        <v>4.71025466918945</v>
+        <v>4.71025514602661</v>
       </c>
       <c r="H102" t="n">
         <v>463960</v>
@@ -3356,7 +3356,7 @@
         <v>5.79248094558716</v>
       </c>
       <c r="G103" t="n">
-        <v>4.77238464355469</v>
+        <v>4.77238512039185</v>
       </c>
       <c r="H103" t="n">
         <v>224143</v>
@@ -3385,7 +3385,7 @@
         <v>5.75006198883057</v>
       </c>
       <c r="G104" t="n">
-        <v>4.73743581771851</v>
+        <v>4.73743629455566</v>
       </c>
       <c r="H104" t="n">
         <v>327250</v>
@@ -3472,7 +3472,7 @@
         <v>5.75006198883057</v>
       </c>
       <c r="G107" t="n">
-        <v>4.73743581771851</v>
+        <v>4.73743629455566</v>
       </c>
       <c r="H107" t="n">
         <v>489388</v>
@@ -3501,7 +3501,7 @@
         <v>5.65108585357666</v>
       </c>
       <c r="G108" t="n">
-        <v>4.65589046478271</v>
+        <v>4.65588998794556</v>
       </c>
       <c r="H108" t="n">
         <v>376314</v>
@@ -3559,7 +3559,7 @@
         <v>5.48141193389893</v>
       </c>
       <c r="G110" t="n">
-        <v>4.63494157791138</v>
+        <v>4.63494205474854</v>
       </c>
       <c r="H110" t="n">
         <v>372359</v>
@@ -3646,7 +3646,7 @@
         <v>5.66993808746338</v>
       </c>
       <c r="G113" t="n">
-        <v>4.79435443878174</v>
+        <v>4.7943549156189</v>
       </c>
       <c r="H113" t="n">
         <v>799297</v>
@@ -3733,7 +3733,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G116" t="n">
-        <v>4.41973400115967</v>
+        <v>4.41973447799683</v>
       </c>
       <c r="H116" t="n">
         <v>496697</v>
@@ -3762,7 +3762,7 @@
         <v>5.17505598068237</v>
       </c>
       <c r="G117" t="n">
-        <v>4.37589502334595</v>
+        <v>4.37589454650879</v>
       </c>
       <c r="H117" t="n">
         <v>1001395</v>
@@ -3820,7 +3820,7 @@
         <v>5.19390916824341</v>
       </c>
       <c r="G119" t="n">
-        <v>4.39183664321899</v>
+        <v>4.39183712005615</v>
       </c>
       <c r="H119" t="n">
         <v>1339760</v>
@@ -3849,7 +3849,7 @@
         <v>5.35886907577515</v>
       </c>
       <c r="G120" t="n">
-        <v>4.53132343292236</v>
+        <v>4.53132295608521</v>
       </c>
       <c r="H120" t="n">
         <v>387794</v>
@@ -3878,7 +3878,7 @@
         <v>5.33530378341675</v>
       </c>
       <c r="G121" t="n">
-        <v>4.5113959312439</v>
+        <v>4.51139640808105</v>
       </c>
       <c r="H121" t="n">
         <v>328533</v>
@@ -3907,7 +3907,7 @@
         <v>5.26460599899292</v>
       </c>
       <c r="G122" t="n">
-        <v>4.45161581039429</v>
+        <v>4.45161628723145</v>
       </c>
       <c r="H122" t="n">
         <v>305258</v>
@@ -3936,7 +3936,7 @@
         <v>5.22218799591064</v>
       </c>
       <c r="G123" t="n">
-        <v>4.41574954986572</v>
+        <v>4.41574907302856</v>
       </c>
       <c r="H123" t="n">
         <v>231709</v>
@@ -3965,7 +3965,7 @@
         <v>5.01009511947632</v>
       </c>
       <c r="G124" t="n">
-        <v>4.23640871047974</v>
+        <v>4.23640775680542</v>
       </c>
       <c r="H124" t="n">
         <v>1183612</v>
@@ -3994,7 +3994,7 @@
         <v>4.56611490249634</v>
       </c>
       <c r="G125" t="n">
-        <v>3.86098957061768</v>
+        <v>3.86099004745483</v>
       </c>
       <c r="H125" t="n">
         <v>725393</v>
@@ -4139,7 +4139,7 @@
         <v>4.92525815963745</v>
       </c>
       <c r="G130" t="n">
-        <v>4.16467189788818</v>
+        <v>4.16467237472534</v>
       </c>
       <c r="H130" t="n">
         <v>218440</v>
@@ -4168,7 +4168,7 @@
         <v>4.75558376312256</v>
       </c>
       <c r="G131" t="n">
-        <v>4.02119922637939</v>
+        <v>4.02120065689087</v>
       </c>
       <c r="H131" t="n">
         <v>421232</v>
@@ -4197,7 +4197,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G132" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H132" t="n">
         <v>481008</v>
@@ -4284,7 +4284,7 @@
         <v>4.81685495376587</v>
       </c>
       <c r="G135" t="n">
-        <v>4.0730094909668</v>
+        <v>4.07300996780396</v>
       </c>
       <c r="H135" t="n">
         <v>231561</v>
@@ -4313,7 +4313,7 @@
         <v>4.80742883682251</v>
       </c>
       <c r="G136" t="n">
-        <v>4.06503963470459</v>
+        <v>4.06503915786743</v>
       </c>
       <c r="H136" t="n">
         <v>480900</v>
@@ -4371,7 +4371,7 @@
         <v>4.75087118148804</v>
       </c>
       <c r="G138" t="n">
-        <v>4.01721477508545</v>
+        <v>4.01721525192261</v>
       </c>
       <c r="H138" t="n">
         <v>736583</v>
@@ -4429,7 +4429,7 @@
         <v>4.76500988006592</v>
       </c>
       <c r="G140" t="n">
-        <v>4.02917003631592</v>
+        <v>4.02917051315308</v>
       </c>
       <c r="H140" t="n">
         <v>634896</v>
@@ -4516,7 +4516,7 @@
         <v>4.92997121810913</v>
       </c>
       <c r="G143" t="n">
-        <v>4.16865730285645</v>
+        <v>4.1686577796936</v>
       </c>
       <c r="H143" t="n">
         <v>311702</v>
@@ -4545,7 +4545,7 @@
         <v>4.85927391052246</v>
       </c>
       <c r="G144" t="n">
-        <v>4.10887813568115</v>
+        <v>4.10887861251831</v>
       </c>
       <c r="H144" t="n">
         <v>260785</v>
@@ -4603,7 +4603,7 @@
         <v>4.89697885513306</v>
       </c>
       <c r="G146" t="n">
-        <v>4.14076042175293</v>
+        <v>4.14075994491577</v>
       </c>
       <c r="H146" t="n">
         <v>170946</v>
@@ -4719,7 +4719,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G150" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H150" t="n">
         <v>127248</v>
@@ -4748,7 +4748,7 @@
         <v>4.89697885513306</v>
       </c>
       <c r="G151" t="n">
-        <v>4.14076042175293</v>
+        <v>4.14075994491577</v>
       </c>
       <c r="H151" t="n">
         <v>299292</v>
@@ -4777,7 +4777,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G152" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H152" t="n">
         <v>373340</v>
@@ -4835,7 +4835,7 @@
         <v>4.92054510116577</v>
       </c>
       <c r="G154" t="n">
-        <v>4.16068649291992</v>
+        <v>4.1606879234314</v>
       </c>
       <c r="H154" t="n">
         <v>119833</v>
@@ -4864,7 +4864,7 @@
         <v>4.97239017486572</v>
       </c>
       <c r="G155" t="n">
-        <v>4.2045259475708</v>
+        <v>4.20452642440796</v>
       </c>
       <c r="H155" t="n">
         <v>107804</v>
@@ -5009,7 +5009,7 @@
         <v>4.71127986907959</v>
       </c>
       <c r="G160" t="n">
-        <v>3.98373770713806</v>
+        <v>3.98373794555664</v>
       </c>
       <c r="H160" t="n">
         <v>833784</v>
@@ -5038,7 +5038,7 @@
         <v>4.75558376312256</v>
       </c>
       <c r="G161" t="n">
-        <v>4.02119922637939</v>
+        <v>4.02120065689087</v>
       </c>
       <c r="H161" t="n">
         <v>711489</v>
@@ -5096,7 +5096,7 @@
         <v>4.84984683990479</v>
       </c>
       <c r="G163" t="n">
-        <v>4.10090589523315</v>
+        <v>4.10090637207031</v>
       </c>
       <c r="H163" t="n">
         <v>365876</v>
@@ -5125,7 +5125,7 @@
         <v>4.74615812301636</v>
       </c>
       <c r="G164" t="n">
-        <v>4.01322937011719</v>
+        <v>4.0132303237915</v>
       </c>
       <c r="H164" t="n">
         <v>1027903</v>
@@ -5183,7 +5183,7 @@
         <v>4.78857612609863</v>
       </c>
       <c r="G166" t="n">
-        <v>4.04909801483154</v>
+        <v>4.04909753799438</v>
       </c>
       <c r="H166" t="n">
         <v>1639048</v>
@@ -5212,7 +5212,7 @@
         <v>4.75558376312256</v>
       </c>
       <c r="G167" t="n">
-        <v>4.02119922637939</v>
+        <v>4.02120065689087</v>
       </c>
       <c r="H167" t="n">
         <v>559732</v>
@@ -5241,7 +5241,7 @@
         <v>4.74144506454468</v>
       </c>
       <c r="G168" t="n">
-        <v>4.00924491882324</v>
+        <v>4.0092453956604</v>
       </c>
       <c r="H168" t="n">
         <v>295834</v>
@@ -5299,7 +5299,7 @@
         <v>4.6189022064209</v>
       </c>
       <c r="G170" t="n">
-        <v>3.90562534332275</v>
+        <v>3.90562605857849</v>
       </c>
       <c r="H170" t="n">
         <v>769796</v>
@@ -5357,7 +5357,7 @@
         <v>4.74144506454468</v>
       </c>
       <c r="G172" t="n">
-        <v>4.00924491882324</v>
+        <v>4.0092453956604</v>
       </c>
       <c r="H172" t="n">
         <v>446805</v>
@@ -5386,7 +5386,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G173" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H173" t="n">
         <v>543033</v>
@@ -5415,7 +5415,7 @@
         <v>4.80742883682251</v>
       </c>
       <c r="G174" t="n">
-        <v>4.06503963470459</v>
+        <v>4.06503915786743</v>
       </c>
       <c r="H174" t="n">
         <v>346206</v>
@@ -5444,7 +5444,7 @@
         <v>4.85456085205078</v>
       </c>
       <c r="G175" t="n">
-        <v>4.10489273071289</v>
+        <v>4.10489225387573</v>
       </c>
       <c r="H175" t="n">
         <v>894040</v>
@@ -5560,7 +5560,7 @@
         <v>4.81685495376587</v>
       </c>
       <c r="G179" t="n">
-        <v>4.0730094909668</v>
+        <v>4.07300996780396</v>
       </c>
       <c r="H179" t="n">
         <v>696907</v>
@@ -5589,7 +5589,7 @@
         <v>4.78857612609863</v>
       </c>
       <c r="G180" t="n">
-        <v>4.04909801483154</v>
+        <v>4.04909753799438</v>
       </c>
       <c r="H180" t="n">
         <v>496038</v>
@@ -5647,7 +5647,7 @@
         <v>4.69808387756348</v>
       </c>
       <c r="G182" t="n">
-        <v>3.97257995605469</v>
+        <v>3.97258043289185</v>
       </c>
       <c r="H182" t="n">
         <v>489564</v>
@@ -5676,7 +5676,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G183" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H183" t="n">
         <v>491388</v>
@@ -5705,7 +5705,7 @@
         <v>5.04308700561523</v>
       </c>
       <c r="G184" t="n">
-        <v>4.26430559158325</v>
+        <v>4.26430606842041</v>
       </c>
       <c r="H184" t="n">
         <v>1425256</v>
@@ -5734,7 +5734,7 @@
         <v>5.04308700561523</v>
       </c>
       <c r="G185" t="n">
-        <v>4.26430559158325</v>
+        <v>4.26430606842041</v>
       </c>
       <c r="H185" t="n">
         <v>601213</v>
@@ -5792,7 +5792,7 @@
         <v>5.13735103607178</v>
       </c>
       <c r="G187" t="n">
-        <v>4.34401273727417</v>
+        <v>4.34401369094849</v>
       </c>
       <c r="H187" t="n">
         <v>1206871</v>
@@ -5821,7 +5821,7 @@
         <v>5.10435819625854</v>
       </c>
       <c r="G188" t="n">
-        <v>4.31611442565918</v>
+        <v>4.3161153793335</v>
       </c>
       <c r="H188" t="n">
         <v>665596</v>
@@ -5850,7 +5850,7 @@
         <v>5.10435819625854</v>
       </c>
       <c r="G189" t="n">
-        <v>4.31611442565918</v>
+        <v>4.3161153793335</v>
       </c>
       <c r="H189" t="n">
         <v>814756</v>
@@ -5966,7 +5966,7 @@
         <v>4.84984683990479</v>
       </c>
       <c r="G193" t="n">
-        <v>4.10090589523315</v>
+        <v>4.10090637207031</v>
       </c>
       <c r="H193" t="n">
         <v>756613</v>
@@ -5995,7 +5995,7 @@
         <v>4.89697885513306</v>
       </c>
       <c r="G194" t="n">
-        <v>4.14076042175293</v>
+        <v>4.14075994491577</v>
       </c>
       <c r="H194" t="n">
         <v>377363</v>
@@ -6024,7 +6024,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G195" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H195" t="n">
         <v>237771</v>
@@ -6111,7 +6111,7 @@
         <v>4.93939781188965</v>
       </c>
       <c r="G198" t="n">
-        <v>4.17662811279297</v>
+        <v>4.17662858963013</v>
       </c>
       <c r="H198" t="n">
         <v>308574</v>
@@ -6169,7 +6169,7 @@
         <v>4.8357081413269</v>
       </c>
       <c r="G200" t="n">
-        <v>4.08895111083984</v>
+        <v>4.08895063400269</v>
       </c>
       <c r="H200" t="n">
         <v>391065</v>
@@ -6227,7 +6227,7 @@
         <v>4.75087118148804</v>
       </c>
       <c r="G202" t="n">
-        <v>4.01721477508545</v>
+        <v>4.01721525192261</v>
       </c>
       <c r="H202" t="n">
         <v>238154</v>
@@ -6256,7 +6256,7 @@
         <v>4.76029682159424</v>
       </c>
       <c r="G203" t="n">
-        <v>4.02518510818481</v>
+        <v>4.02518558502197</v>
       </c>
       <c r="H203" t="n">
         <v>318952</v>
@@ -6285,7 +6285,7 @@
         <v>4.76029682159424</v>
       </c>
       <c r="G204" t="n">
-        <v>4.02518510818481</v>
+        <v>4.02518558502197</v>
       </c>
       <c r="H204" t="n">
         <v>181204</v>
@@ -6314,7 +6314,7 @@
         <v>4.71316623687744</v>
       </c>
       <c r="G205" t="n">
-        <v>3.98533320426941</v>
+        <v>3.98533272743225</v>
       </c>
       <c r="H205" t="n">
         <v>680391</v>
@@ -6343,7 +6343,7 @@
         <v>4.71127986907959</v>
       </c>
       <c r="G206" t="n">
-        <v>3.98373770713806</v>
+        <v>3.98373794555664</v>
       </c>
       <c r="H206" t="n">
         <v>569507</v>
@@ -6372,7 +6372,7 @@
         <v>4.71316623687744</v>
       </c>
       <c r="G207" t="n">
-        <v>3.98533320426941</v>
+        <v>3.98533272743225</v>
       </c>
       <c r="H207" t="n">
         <v>274842</v>
@@ -6430,7 +6430,7 @@
         <v>4.72259187698364</v>
       </c>
       <c r="G209" t="n">
-        <v>3.9933032989502</v>
+        <v>3.99330282211304</v>
       </c>
       <c r="H209" t="n">
         <v>416525</v>
@@ -6459,7 +6459,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G210" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H210" t="n">
         <v>363289</v>
@@ -6488,7 +6488,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G211" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H211" t="n">
         <v>342137</v>
@@ -6517,7 +6517,7 @@
         <v>4.71316623687744</v>
       </c>
       <c r="G212" t="n">
-        <v>3.98533320426941</v>
+        <v>3.98533272743225</v>
       </c>
       <c r="H212" t="n">
         <v>362947</v>
@@ -6546,7 +6546,7 @@
         <v>4.732017993927</v>
       </c>
       <c r="G213" t="n">
-        <v>4.00127410888672</v>
+        <v>4.00127363204956</v>
       </c>
       <c r="H213" t="n">
         <v>315366</v>
@@ -6575,7 +6575,7 @@
         <v>4.70185422897339</v>
       </c>
       <c r="G214" t="n">
-        <v>3.97576713562012</v>
+        <v>3.97576856613159</v>
       </c>
       <c r="H214" t="n">
         <v>241700</v>
@@ -6604,7 +6604,7 @@
         <v>4.74144506454468</v>
       </c>
       <c r="G215" t="n">
-        <v>4.00924491882324</v>
+        <v>4.0092453956604</v>
       </c>
       <c r="H215" t="n">
         <v>247680</v>
@@ -6633,7 +6633,7 @@
         <v>4.63398408889771</v>
       </c>
       <c r="G216" t="n">
-        <v>3.91837882995605</v>
+        <v>3.9183783531189</v>
       </c>
       <c r="H216" t="n">
         <v>335835</v>
@@ -6662,7 +6662,7 @@
         <v>4.58119678497314</v>
       </c>
       <c r="G217" t="n">
-        <v>3.8737428188324</v>
+        <v>3.87374305725098</v>
       </c>
       <c r="H217" t="n">
         <v>332292</v>
@@ -6720,7 +6720,7 @@
         <v>4.75087118148804</v>
       </c>
       <c r="G219" t="n">
-        <v>4.01721477508545</v>
+        <v>4.01721525192261</v>
       </c>
       <c r="H219" t="n">
         <v>508808</v>
@@ -6749,7 +6749,7 @@
         <v>4.78857612609863</v>
       </c>
       <c r="G220" t="n">
-        <v>4.04909801483154</v>
+        <v>4.04909753799438</v>
       </c>
       <c r="H220" t="n">
         <v>287032</v>
@@ -6778,7 +6778,7 @@
         <v>4.77915000915527</v>
       </c>
       <c r="G221" t="n">
-        <v>4.04112720489502</v>
+        <v>4.04112672805786</v>
       </c>
       <c r="H221" t="n">
         <v>482074</v>
@@ -6807,7 +6807,7 @@
         <v>4.75558376312256</v>
       </c>
       <c r="G222" t="n">
-        <v>4.02119922637939</v>
+        <v>4.02120065689087</v>
       </c>
       <c r="H222" t="n">
         <v>260733</v>
@@ -6836,7 +6836,7 @@
         <v>4.68111610412598</v>
       </c>
       <c r="G223" t="n">
-        <v>3.95823168754578</v>
+        <v>3.95823216438293</v>
       </c>
       <c r="H223" t="n">
         <v>310397</v>
@@ -7039,7 +7039,7 @@
         <v>4.65472221374512</v>
       </c>
       <c r="G230" t="n">
-        <v>3.93591451644897</v>
+        <v>3.93591403961182</v>
       </c>
       <c r="H230" t="n">
         <v>346856</v>
@@ -7068,7 +7068,7 @@
         <v>4.69619798660278</v>
       </c>
       <c r="G231" t="n">
-        <v>3.97098517417908</v>
+        <v>3.97098469734192</v>
       </c>
       <c r="H231" t="n">
         <v>205658</v>
@@ -7097,7 +7097,7 @@
         <v>4.68300104141235</v>
       </c>
       <c r="G232" t="n">
-        <v>3.95982646942139</v>
+        <v>3.95982599258423</v>
       </c>
       <c r="H232" t="n">
         <v>274938</v>
@@ -7126,7 +7126,7 @@
         <v>4.68677186965942</v>
       </c>
       <c r="G233" t="n">
-        <v>3.96301412582397</v>
+        <v>3.96301460266113</v>
       </c>
       <c r="H233" t="n">
         <v>135868</v>
@@ -7155,7 +7155,7 @@
         <v>4.6189022064209</v>
       </c>
       <c r="G234" t="n">
-        <v>3.90562534332275</v>
+        <v>3.90562605857849</v>
       </c>
       <c r="H234" t="n">
         <v>363824</v>
@@ -7184,7 +7184,7 @@
         <v>4.60381984710693</v>
       </c>
       <c r="G235" t="n">
-        <v>3.89287257194519</v>
+        <v>3.89287281036377</v>
       </c>
       <c r="H235" t="n">
         <v>453931</v>
@@ -7213,7 +7213,7 @@
         <v>4.66226291656494</v>
       </c>
       <c r="G236" t="n">
-        <v>3.94228982925415</v>
+        <v>3.94229078292847</v>
       </c>
       <c r="H236" t="n">
         <v>395280</v>
@@ -7242,7 +7242,7 @@
         <v>4.65095186233521</v>
       </c>
       <c r="G237" t="n">
-        <v>3.93272590637207</v>
+        <v>3.93272638320923</v>
       </c>
       <c r="H237" t="n">
         <v>457273</v>
@@ -7271,7 +7271,7 @@
         <v>4.62644290924072</v>
       </c>
       <c r="G238" t="n">
-        <v>3.91200184822083</v>
+        <v>3.9120020866394</v>
       </c>
       <c r="H238" t="n">
         <v>366129</v>
@@ -7358,7 +7358,7 @@
         <v>4.85456085205078</v>
       </c>
       <c r="G241" t="n">
-        <v>4.10489273071289</v>
+        <v>4.10489225387573</v>
       </c>
       <c r="H241" t="n">
         <v>258622</v>
@@ -7416,7 +7416,7 @@
         <v>4.86398696899414</v>
       </c>
       <c r="G243" t="n">
-        <v>4.1128625869751</v>
+        <v>4.11286354064941</v>
       </c>
       <c r="H243" t="n">
         <v>237016</v>
@@ -7532,7 +7532,7 @@
         <v>4.74144506454468</v>
       </c>
       <c r="G247" t="n">
-        <v>4.00924491882324</v>
+        <v>4.0092453956604</v>
       </c>
       <c r="H247" t="n">
         <v>1978024</v>
@@ -7561,7 +7561,7 @@
         <v>4.64718103408813</v>
       </c>
       <c r="G248" t="n">
-        <v>3.92953681945801</v>
+        <v>3.92953729629517</v>
       </c>
       <c r="H248" t="n">
         <v>1400722</v>
@@ -7619,7 +7619,7 @@
         <v>4.54726219177246</v>
       </c>
       <c r="G250" t="n">
-        <v>3.84504866600037</v>
+        <v>3.84504890441895</v>
       </c>
       <c r="H250" t="n">
         <v>2196397</v>
@@ -7648,7 +7648,7 @@
         <v>4.52652406692505</v>
       </c>
       <c r="G251" t="n">
-        <v>3.82751274108887</v>
+        <v>3.82751226425171</v>
       </c>
       <c r="H251" t="n">
         <v>884033</v>
@@ -7677,7 +7677,7 @@
         <v>4.50578594207764</v>
       </c>
       <c r="G252" t="n">
-        <v>3.80997753143311</v>
+        <v>3.80997776985168</v>
       </c>
       <c r="H252" t="n">
         <v>853131</v>
@@ -7706,7 +7706,7 @@
         <v>4.48316287994385</v>
       </c>
       <c r="G253" t="n">
-        <v>3.79084753990173</v>
+        <v>3.79084777832031</v>
       </c>
       <c r="H253" t="n">
         <v>548752</v>
@@ -7764,7 +7764,7 @@
         <v>4.55103302001953</v>
       </c>
       <c r="G255" t="n">
-        <v>3.84823727607727</v>
+        <v>3.84823703765869</v>
       </c>
       <c r="H255" t="n">
         <v>342192</v>
@@ -7793,7 +7793,7 @@
         <v>4.50767183303833</v>
       </c>
       <c r="G256" t="n">
-        <v>3.81157159805298</v>
+        <v>3.81157231330872</v>
       </c>
       <c r="H256" t="n">
         <v>214001</v>
@@ -7822,7 +7822,7 @@
         <v>4.50578594207764</v>
       </c>
       <c r="G257" t="n">
-        <v>3.80997753143311</v>
+        <v>3.80997776985168</v>
       </c>
       <c r="H257" t="n">
         <v>217400</v>
@@ -7851,7 +7851,7 @@
         <v>4.5755410194397</v>
       </c>
       <c r="G258" t="n">
-        <v>3.86896061897278</v>
+        <v>3.86896085739136</v>
       </c>
       <c r="H258" t="n">
         <v>316025</v>
@@ -7880,7 +7880,7 @@
         <v>4.63021421432495</v>
       </c>
       <c r="G259" t="n">
-        <v>3.91519117355347</v>
+        <v>3.91519021987915</v>
       </c>
       <c r="H259" t="n">
         <v>1256139</v>
@@ -7996,7 +7996,7 @@
         <v>4.58119678497314</v>
       </c>
       <c r="G263" t="n">
-        <v>3.8737428188324</v>
+        <v>3.87374305725098</v>
       </c>
       <c r="H263" t="n">
         <v>615893</v>
@@ -8054,7 +8054,7 @@
         <v>4.92997121810913</v>
       </c>
       <c r="G265" t="n">
-        <v>4.16865730285645</v>
+        <v>4.1686577796936</v>
       </c>
       <c r="H265" t="n">
         <v>1705730</v>
@@ -8112,7 +8112,7 @@
         <v>5.06665277481079</v>
       </c>
       <c r="G267" t="n">
-        <v>4.28423261642456</v>
+        <v>4.2842321395874</v>
       </c>
       <c r="H267" t="n">
         <v>732485</v>
@@ -8141,7 +8141,7 @@
         <v>4.97239017486572</v>
       </c>
       <c r="G268" t="n">
-        <v>4.2045259475708</v>
+        <v>4.20452642440796</v>
       </c>
       <c r="H268" t="n">
         <v>432427</v>
@@ -8170,7 +8170,7 @@
         <v>5.01009511947632</v>
       </c>
       <c r="G269" t="n">
-        <v>4.23640871047974</v>
+        <v>4.23640775680542</v>
       </c>
       <c r="H269" t="n">
         <v>517673</v>
@@ -8199,7 +8199,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G270" t="n">
-        <v>4.28821754455566</v>
+        <v>4.28821706771851</v>
       </c>
       <c r="H270" t="n">
         <v>413038</v>
@@ -8228,7 +8228,7 @@
         <v>5.08079290390015</v>
       </c>
       <c r="G271" t="n">
-        <v>4.2961893081665</v>
+        <v>4.29618883132935</v>
       </c>
       <c r="H271" t="n">
         <v>405011</v>
@@ -8257,7 +8257,7 @@
         <v>5.01009511947632</v>
       </c>
       <c r="G272" t="n">
-        <v>4.23640871047974</v>
+        <v>4.23640775680542</v>
       </c>
       <c r="H272" t="n">
         <v>410169</v>
@@ -8315,7 +8315,7 @@
         <v>5.04308700561523</v>
       </c>
       <c r="G274" t="n">
-        <v>4.26430559158325</v>
+        <v>4.26430606842041</v>
       </c>
       <c r="H274" t="n">
         <v>671778</v>
@@ -8344,7 +8344,7 @@
         <v>4.96296310424805</v>
       </c>
       <c r="G275" t="n">
-        <v>4.19655466079712</v>
+        <v>4.19655513763428</v>
       </c>
       <c r="H275" t="n">
         <v>419000</v>
@@ -8431,7 +8431,7 @@
         <v>4.80742883682251</v>
       </c>
       <c r="G278" t="n">
-        <v>4.06503963470459</v>
+        <v>4.06503915786743</v>
       </c>
       <c r="H278" t="n">
         <v>435491</v>
@@ -8489,7 +8489,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G280" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H280" t="n">
         <v>589046</v>
@@ -8518,7 +8518,7 @@
         <v>4.95353698730469</v>
       </c>
       <c r="G281" t="n">
-        <v>4.18858337402344</v>
+        <v>4.18858432769775</v>
       </c>
       <c r="H281" t="n">
         <v>401649</v>
@@ -8547,7 +8547,7 @@
         <v>5.00538206100464</v>
       </c>
       <c r="G282" t="n">
-        <v>4.23242378234863</v>
+        <v>4.23242282867432</v>
       </c>
       <c r="H282" t="n">
         <v>373986</v>
@@ -8576,7 +8576,7 @@
         <v>4.86398696899414</v>
       </c>
       <c r="G283" t="n">
-        <v>4.1128625869751</v>
+        <v>4.11286354064941</v>
       </c>
       <c r="H283" t="n">
         <v>368330</v>
@@ -8605,7 +8605,7 @@
         <v>4.93939781188965</v>
       </c>
       <c r="G284" t="n">
-        <v>4.17662811279297</v>
+        <v>4.17662858963013</v>
       </c>
       <c r="H284" t="n">
         <v>283292</v>
@@ -8634,7 +8634,7 @@
         <v>4.96767711639404</v>
       </c>
       <c r="G285" t="n">
-        <v>4.20054054260254</v>
+        <v>4.2005410194397</v>
       </c>
       <c r="H285" t="n">
         <v>613052</v>
@@ -8663,7 +8663,7 @@
         <v>4.96767711639404</v>
       </c>
       <c r="G286" t="n">
-        <v>4.20054054260254</v>
+        <v>4.2005410194397</v>
       </c>
       <c r="H286" t="n">
         <v>529658</v>
@@ -8692,7 +8692,7 @@
         <v>5.01952123641968</v>
       </c>
       <c r="G287" t="n">
-        <v>4.2443790435791</v>
+        <v>4.24437856674194</v>
       </c>
       <c r="H287" t="n">
         <v>349703</v>
@@ -8779,7 +8779,7 @@
         <v>5.02423477172852</v>
       </c>
       <c r="G290" t="n">
-        <v>4.24836444854736</v>
+        <v>4.24836492538452</v>
       </c>
       <c r="H290" t="n">
         <v>308472</v>
@@ -8808,7 +8808,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G291" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H291" t="n">
         <v>644908</v>
@@ -8837,7 +8837,7 @@
         <v>4.96296310424805</v>
       </c>
       <c r="G292" t="n">
-        <v>4.19655466079712</v>
+        <v>4.19655513763428</v>
       </c>
       <c r="H292" t="n">
         <v>418503</v>
@@ -8895,7 +8895,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G294" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H294" t="n">
         <v>338605</v>
@@ -8953,7 +8953,7 @@
         <v>4.94882392883301</v>
       </c>
       <c r="G296" t="n">
-        <v>4.18459939956665</v>
+        <v>4.18459892272949</v>
       </c>
       <c r="H296" t="n">
         <v>221124</v>
@@ -9069,7 +9069,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G300" t="n">
-        <v>4.38386631011963</v>
+        <v>4.38386535644531</v>
       </c>
       <c r="H300" t="n">
         <v>543804</v>
@@ -9098,7 +9098,7 @@
         <v>5.09964513778687</v>
       </c>
       <c r="G301" t="n">
-        <v>4.31212902069092</v>
+        <v>4.31212949752808</v>
       </c>
       <c r="H301" t="n">
         <v>372880</v>
@@ -9127,7 +9127,7 @@
         <v>5.17505598068237</v>
       </c>
       <c r="G302" t="n">
-        <v>4.37589502334595</v>
+        <v>4.37589454650879</v>
       </c>
       <c r="H302" t="n">
         <v>443589</v>
@@ -9185,7 +9185,7 @@
         <v>5.2693190574646</v>
       </c>
       <c r="G304" t="n">
-        <v>4.45560169219971</v>
+        <v>4.45560216903687</v>
       </c>
       <c r="H304" t="n">
         <v>650212</v>
@@ -9243,7 +9243,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G306" t="n">
-        <v>4.38386631011963</v>
+        <v>4.38386535644531</v>
       </c>
       <c r="H306" t="n">
         <v>369045</v>
@@ -9272,7 +9272,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G307" t="n">
-        <v>4.38386631011963</v>
+        <v>4.38386535644531</v>
       </c>
       <c r="H307" t="n">
         <v>322882</v>
@@ -9301,7 +9301,7 @@
         <v>5.21276092529297</v>
       </c>
       <c r="G308" t="n">
-        <v>4.40777778625488</v>
+        <v>4.40777826309204</v>
       </c>
       <c r="H308" t="n">
         <v>598467</v>
@@ -9388,7 +9388,7 @@
         <v>5.31645107269287</v>
       </c>
       <c r="G311" t="n">
-        <v>4.49545478820801</v>
+        <v>4.49545574188232</v>
       </c>
       <c r="H311" t="n">
         <v>1952620</v>
@@ -9446,7 +9446,7 @@
         <v>5.40600109100342</v>
       </c>
       <c r="G313" t="n">
-        <v>4.57117605209351</v>
+        <v>4.57117652893066</v>
       </c>
       <c r="H313" t="n">
         <v>675019</v>
@@ -9533,7 +9533,7 @@
         <v>5.61809396743774</v>
       </c>
       <c r="G316" t="n">
-        <v>4.75051689147949</v>
+        <v>4.75051641464233</v>
       </c>
       <c r="H316" t="n">
         <v>1482421</v>
@@ -9562,7 +9562,7 @@
         <v>5.58038806915283</v>
       </c>
       <c r="G317" t="n">
-        <v>4.71863412857056</v>
+        <v>4.7186336517334</v>
       </c>
       <c r="H317" t="n">
         <v>635651</v>
@@ -9707,7 +9707,7 @@
         <v>5.48612499237061</v>
       </c>
       <c r="G322" t="n">
-        <v>4.63892698287964</v>
+        <v>4.6389274597168</v>
       </c>
       <c r="H322" t="n">
         <v>467743</v>
@@ -9736,7 +9736,7 @@
         <v>5.53325700759888</v>
       </c>
       <c r="G323" t="n">
-        <v>4.6787805557251</v>
+        <v>4.67878103256226</v>
       </c>
       <c r="H323" t="n">
         <v>651867</v>
@@ -9765,7 +9765,7 @@
         <v>5.46727180480957</v>
       </c>
       <c r="G324" t="n">
-        <v>4.62298488616943</v>
+        <v>4.62298536300659</v>
       </c>
       <c r="H324" t="n">
         <v>411828</v>
@@ -9852,7 +9852,7 @@
         <v>5.6275200843811</v>
       </c>
       <c r="G327" t="n">
-        <v>4.75848722457886</v>
+        <v>4.7584867477417</v>
       </c>
       <c r="H327" t="n">
         <v>359021</v>
@@ -9881,7 +9881,7 @@
         <v>5.83961200714111</v>
       </c>
       <c r="G328" t="n">
-        <v>4.93782711029053</v>
+        <v>4.93782663345337</v>
       </c>
       <c r="H328" t="n">
         <v>965701</v>
@@ -9910,7 +9910,7 @@
         <v>5.80190706253052</v>
       </c>
       <c r="G329" t="n">
-        <v>4.90594434738159</v>
+        <v>4.90594387054443</v>
       </c>
       <c r="H329" t="n">
         <v>1026814</v>
@@ -9997,7 +9997,7 @@
         <v>5.65579891204834</v>
       </c>
       <c r="G332" t="n">
-        <v>4.78239870071411</v>
+        <v>4.78239917755127</v>
       </c>
       <c r="H332" t="n">
         <v>572504</v>
@@ -10200,7 +10200,7 @@
         <v>5.75948905944824</v>
       </c>
       <c r="G339" t="n">
-        <v>4.87007617950439</v>
+        <v>4.87007665634155</v>
       </c>
       <c r="H339" t="n">
         <v>610334</v>
@@ -10229,7 +10229,7 @@
         <v>5.75948905944824</v>
       </c>
       <c r="G340" t="n">
-        <v>4.87007617950439</v>
+        <v>4.87007665634155</v>
       </c>
       <c r="H340" t="n">
         <v>326044</v>
@@ -10258,7 +10258,7 @@
         <v>5.82075977325439</v>
       </c>
       <c r="G341" t="n">
-        <v>4.92188596725464</v>
+        <v>4.92188549041748</v>
       </c>
       <c r="H341" t="n">
         <v>511035</v>
@@ -10287,7 +10287,7 @@
         <v>5.88203096389771</v>
       </c>
       <c r="G342" t="n">
-        <v>4.97369480133057</v>
+        <v>4.97369575500488</v>
       </c>
       <c r="H342" t="n">
         <v>550576</v>
@@ -10316,7 +10316,7 @@
         <v>6.0611310005188</v>
       </c>
       <c r="G343" t="n">
-        <v>5.12513780593872</v>
+        <v>5.12513828277588</v>
       </c>
       <c r="H343" t="n">
         <v>843122</v>
@@ -10345,7 +10345,7 @@
         <v>6.01399898529053</v>
       </c>
       <c r="G344" t="n">
-        <v>5.0852837562561</v>
+        <v>5.08528423309326</v>
       </c>
       <c r="H344" t="n">
         <v>471794</v>
@@ -10374,7 +10374,7 @@
         <v>5.95272779464722</v>
       </c>
       <c r="G345" t="n">
-        <v>5.0334734916687</v>
+        <v>5.03347444534302</v>
       </c>
       <c r="H345" t="n">
         <v>440562</v>
@@ -10403,7 +10403,7 @@
         <v>6.00928592681885</v>
       </c>
       <c r="G346" t="n">
-        <v>5.08129835128784</v>
+        <v>5.081298828125</v>
       </c>
       <c r="H346" t="n">
         <v>279343</v>
@@ -10432,7 +10432,7 @@
         <v>5.84903907775879</v>
       </c>
       <c r="G347" t="n">
-        <v>4.94579792022705</v>
+        <v>4.94579839706421</v>
       </c>
       <c r="H347" t="n">
         <v>4737298</v>
@@ -10490,7 +10490,7 @@
         <v>5.88203096389771</v>
       </c>
       <c r="G349" t="n">
-        <v>4.97369480133057</v>
+        <v>4.97369575500488</v>
       </c>
       <c r="H349" t="n">
         <v>756716</v>
@@ -10519,7 +10519,7 @@
         <v>5.93858909606934</v>
       </c>
       <c r="G350" t="n">
-        <v>5.02151870727539</v>
+        <v>5.02151918411255</v>
       </c>
       <c r="H350" t="n">
         <v>387672</v>
@@ -10548,7 +10548,7 @@
         <v>5.93858909606934</v>
       </c>
       <c r="G351" t="n">
-        <v>5.02151870727539</v>
+        <v>5.02151918411255</v>
       </c>
       <c r="H351" t="n">
         <v>410211</v>
@@ -10664,7 +10664,7 @@
         <v>6.07527112960815</v>
       </c>
       <c r="G355" t="n">
-        <v>5.13709449768066</v>
+        <v>5.13709402084351</v>
       </c>
       <c r="H355" t="n">
         <v>683168</v>
@@ -10693,7 +10693,7 @@
         <v>5.99514722824097</v>
       </c>
       <c r="G356" t="n">
-        <v>5.06934356689453</v>
+        <v>5.06934261322021</v>
       </c>
       <c r="H356" t="n">
         <v>295336</v>
@@ -10722,7 +10722,7 @@
         <v>5.99043416976929</v>
       </c>
       <c r="G357" t="n">
-        <v>5.06535816192627</v>
+        <v>5.06535863876343</v>
       </c>
       <c r="H357" t="n">
         <v>409735</v>
@@ -10780,7 +10780,7 @@
         <v>6.09883594512939</v>
       </c>
       <c r="G359" t="n">
-        <v>5.15701961517334</v>
+        <v>5.15701913833618</v>
       </c>
       <c r="H359" t="n">
         <v>459721</v>
@@ -10838,7 +10838,7 @@
         <v>5.97629404067993</v>
       </c>
       <c r="G361" t="n">
-        <v>5.05340194702148</v>
+        <v>5.05340147018433</v>
       </c>
       <c r="H361" t="n">
         <v>614077</v>
@@ -10867,7 +10867,7 @@
         <v>5.95272779464722</v>
       </c>
       <c r="G362" t="n">
-        <v>5.0334734916687</v>
+        <v>5.03347444534302</v>
       </c>
       <c r="H362" t="n">
         <v>823147</v>
@@ -10954,7 +10954,7 @@
         <v>5.90559720993042</v>
       </c>
       <c r="G365" t="n">
-        <v>4.99362230300903</v>
+        <v>4.99362182617188</v>
       </c>
       <c r="H365" t="n">
         <v>272356</v>
@@ -10983,7 +10983,7 @@
         <v>5.86789083480835</v>
       </c>
       <c r="G366" t="n">
-        <v>4.96173858642578</v>
+        <v>4.96173906326294</v>
       </c>
       <c r="H366" t="n">
         <v>872052</v>
@@ -11012,7 +11012,7 @@
         <v>5.72178316116333</v>
       </c>
       <c r="G367" t="n">
-        <v>4.83819389343262</v>
+        <v>4.83819437026978</v>
       </c>
       <c r="H367" t="n">
         <v>636007</v>
@@ -11070,7 +11070,7 @@
         <v>5.7689151763916</v>
       </c>
       <c r="G369" t="n">
-        <v>4.87804698944092</v>
+        <v>4.87804746627808</v>
       </c>
       <c r="H369" t="n">
         <v>783581</v>
@@ -11099,7 +11099,7 @@
         <v>5.68407821655273</v>
       </c>
       <c r="G370" t="n">
-        <v>4.92707300186157</v>
+        <v>4.92707347869873</v>
       </c>
       <c r="H370" t="n">
         <v>504555</v>
@@ -11128,7 +11128,7 @@
         <v>6.05170488357544</v>
       </c>
       <c r="G371" t="n">
-        <v>5.2457389831543</v>
+        <v>5.24573850631714</v>
       </c>
       <c r="H371" t="n">
         <v>4254042</v>
@@ -11157,7 +11157,7 @@
         <v>6.08469676971436</v>
       </c>
       <c r="G372" t="n">
-        <v>5.27433633804321</v>
+        <v>5.27433681488037</v>
       </c>
       <c r="H372" t="n">
         <v>905761</v>
@@ -11186,7 +11186,7 @@
         <v>5.99514722824097</v>
       </c>
       <c r="G373" t="n">
-        <v>5.19671392440796</v>
+        <v>5.1967134475708</v>
       </c>
       <c r="H373" t="n">
         <v>677655</v>
@@ -11215,7 +11215,7 @@
         <v>5.9574408531189</v>
       </c>
       <c r="G374" t="n">
-        <v>5.16402912139893</v>
+        <v>5.16402864456177</v>
       </c>
       <c r="H374" t="n">
         <v>1825102</v>
@@ -11244,7 +11244,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G375" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H375" t="n">
         <v>545453</v>
@@ -11273,7 +11273,7 @@
         <v>6.04227781295776</v>
       </c>
       <c r="G376" t="n">
-        <v>5.23756742477417</v>
+        <v>5.23756790161133</v>
       </c>
       <c r="H376" t="n">
         <v>1158100</v>
@@ -11302,7 +11302,7 @@
         <v>6.00457286834717</v>
       </c>
       <c r="G377" t="n">
-        <v>5.20488452911377</v>
+        <v>5.20488357543945</v>
       </c>
       <c r="H377" t="n">
         <v>435971</v>
@@ -11418,7 +11418,7 @@
         <v>5.85375213623047</v>
       </c>
       <c r="G381" t="n">
-        <v>5.07414960861206</v>
+        <v>5.07415008544922</v>
       </c>
       <c r="H381" t="n">
         <v>539469</v>
@@ -11447,7 +11447,7 @@
         <v>5.79248094558716</v>
       </c>
       <c r="G382" t="n">
-        <v>5.02103900909424</v>
+        <v>5.02103853225708</v>
       </c>
       <c r="H382" t="n">
         <v>524647</v>
@@ -11476,7 +11476,7 @@
         <v>5.68407821655273</v>
       </c>
       <c r="G383" t="n">
-        <v>4.92707300186157</v>
+        <v>4.92707347869873</v>
       </c>
       <c r="H383" t="n">
         <v>683877</v>
@@ -11592,7 +11592,7 @@
         <v>5.93858909606934</v>
       </c>
       <c r="G387" t="n">
-        <v>5.1476879119873</v>
+        <v>5.14768838882446</v>
       </c>
       <c r="H387" t="n">
         <v>406511</v>
@@ -11737,7 +11737,7 @@
         <v>5.93858909606934</v>
       </c>
       <c r="G392" t="n">
-        <v>5.1476879119873</v>
+        <v>5.14768838882446</v>
       </c>
       <c r="H392" t="n">
         <v>279025</v>
@@ -11795,7 +11795,7 @@
         <v>5.85375213623047</v>
       </c>
       <c r="G394" t="n">
-        <v>5.07414960861206</v>
+        <v>5.07415008544922</v>
       </c>
       <c r="H394" t="n">
         <v>294798</v>
@@ -11998,7 +11998,7 @@
         <v>5.9574408531189</v>
       </c>
       <c r="G401" t="n">
-        <v>5.16402912139893</v>
+        <v>5.16402864456177</v>
       </c>
       <c r="H401" t="n">
         <v>220721</v>
@@ -12027,7 +12027,7 @@
         <v>5.9574408531189</v>
       </c>
       <c r="G402" t="n">
-        <v>5.16402912139893</v>
+        <v>5.16402864456177</v>
       </c>
       <c r="H402" t="n">
         <v>261968</v>
@@ -12056,7 +12056,7 @@
         <v>5.98100709915161</v>
       </c>
       <c r="G403" t="n">
-        <v>5.18445634841919</v>
+        <v>5.18445682525635</v>
       </c>
       <c r="H403" t="n">
         <v>253579</v>
@@ -12085,7 +12085,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G404" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H404" t="n">
         <v>677683</v>
@@ -12143,7 +12143,7 @@
         <v>6.09883594512939</v>
       </c>
       <c r="G406" t="n">
-        <v>5.28659296035767</v>
+        <v>5.28659248352051</v>
       </c>
       <c r="H406" t="n">
         <v>471675</v>
@@ -12172,7 +12172,7 @@
         <v>6.00457286834717</v>
       </c>
       <c r="G407" t="n">
-        <v>5.20488452911377</v>
+        <v>5.20488357543945</v>
       </c>
       <c r="H407" t="n">
         <v>340188</v>
@@ -12201,7 +12201,7 @@
         <v>6.06584405899048</v>
       </c>
       <c r="G408" t="n">
-        <v>5.25799512863159</v>
+        <v>5.25799465179443</v>
       </c>
       <c r="H408" t="n">
         <v>293859</v>
@@ -12259,7 +12259,7 @@
         <v>6.07527112960815</v>
       </c>
       <c r="G410" t="n">
-        <v>5.26616621017456</v>
+        <v>5.26616668701172</v>
       </c>
       <c r="H410" t="n">
         <v>132674</v>
@@ -12317,7 +12317,7 @@
         <v>5.99514722824097</v>
       </c>
       <c r="G412" t="n">
-        <v>5.19671392440796</v>
+        <v>5.1967134475708</v>
       </c>
       <c r="H412" t="n">
         <v>281114</v>
@@ -12433,7 +12433,7 @@
         <v>6.06584405899048</v>
       </c>
       <c r="G416" t="n">
-        <v>5.25799512863159</v>
+        <v>5.25799465179443</v>
       </c>
       <c r="H416" t="n">
         <v>341897</v>
@@ -12462,7 +12462,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G417" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H417" t="n">
         <v>271207</v>
@@ -12578,7 +12578,7 @@
         <v>5.87731790542603</v>
       </c>
       <c r="G421" t="n">
-        <v>5.09457731246948</v>
+        <v>5.09457683563232</v>
       </c>
       <c r="H421" t="n">
         <v>173205</v>
@@ -12665,7 +12665,7 @@
         <v>5.79719400405884</v>
       </c>
       <c r="G424" t="n">
-        <v>5.02512454986572</v>
+        <v>5.02512407302856</v>
       </c>
       <c r="H424" t="n">
         <v>149898</v>
@@ -12694,7 +12694,7 @@
         <v>5.7689151763916</v>
       </c>
       <c r="G425" t="n">
-        <v>5.00061130523682</v>
+        <v>5.00061082839966</v>
       </c>
       <c r="H425" t="n">
         <v>303048</v>
@@ -12723,7 +12723,7 @@
         <v>5.81604719161987</v>
       </c>
       <c r="G426" t="n">
-        <v>5.04146671295166</v>
+        <v>5.04146575927734</v>
       </c>
       <c r="H426" t="n">
         <v>139420</v>
@@ -12752,7 +12752,7 @@
         <v>5.91030979156494</v>
       </c>
       <c r="G427" t="n">
-        <v>5.12317514419556</v>
+        <v>5.1231746673584</v>
       </c>
       <c r="H427" t="n">
         <v>452463</v>
@@ -12868,7 +12868,7 @@
         <v>6.00457286834717</v>
       </c>
       <c r="G431" t="n">
-        <v>5.20488452911377</v>
+        <v>5.20488357543945</v>
       </c>
       <c r="H431" t="n">
         <v>126321</v>
@@ -12955,7 +12955,7 @@
         <v>6.01399898529053</v>
       </c>
       <c r="G434" t="n">
-        <v>5.21305465698242</v>
+        <v>5.21305513381958</v>
       </c>
       <c r="H434" t="n">
         <v>447803</v>
@@ -13013,7 +13013,7 @@
         <v>6.24965810775757</v>
       </c>
       <c r="G436" t="n">
-        <v>5.41732835769653</v>
+        <v>5.41732883453369</v>
       </c>
       <c r="H436" t="n">
         <v>700498</v>
@@ -13042,7 +13042,7 @@
         <v>6.3156418800354</v>
       </c>
       <c r="G437" t="n">
-        <v>5.474524974823</v>
+        <v>5.47452402114868</v>
       </c>
       <c r="H437" t="n">
         <v>1437728</v>
@@ -13071,7 +13071,7 @@
         <v>6.34863376617432</v>
       </c>
       <c r="G438" t="n">
-        <v>5.50312232971191</v>
+        <v>5.50312280654907</v>
       </c>
       <c r="H438" t="n">
         <v>1162591</v>
@@ -13129,7 +13129,7 @@
         <v>6.33449506759644</v>
       </c>
       <c r="G440" t="n">
-        <v>5.49086713790894</v>
+        <v>5.49086666107178</v>
       </c>
       <c r="H440" t="n">
         <v>796037</v>
@@ -13216,7 +13216,7 @@
         <v>6.34392118453979</v>
       </c>
       <c r="G443" t="n">
-        <v>5.49903774261475</v>
+        <v>5.4990382194519</v>
       </c>
       <c r="H443" t="n">
         <v>1542051</v>
@@ -13274,7 +13274,7 @@
         <v>6.36748695373535</v>
       </c>
       <c r="G445" t="n">
-        <v>5.51946496963501</v>
+        <v>5.51946544647217</v>
       </c>
       <c r="H445" t="n">
         <v>706633</v>
@@ -13361,7 +13361,7 @@
         <v>6.08940982818604</v>
       </c>
       <c r="G448" t="n">
-        <v>5.2784218788147</v>
+        <v>5.27842235565186</v>
       </c>
       <c r="H448" t="n">
         <v>1011505</v>
@@ -13390,7 +13390,7 @@
         <v>6.07998418807983</v>
       </c>
       <c r="G449" t="n">
-        <v>5.27025127410889</v>
+        <v>5.27025175094604</v>
       </c>
       <c r="H449" t="n">
         <v>859217</v>
@@ -13419,7 +13419,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G450" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H450" t="n">
         <v>597455</v>
@@ -13448,7 +13448,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G451" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H451" t="n">
         <v>1040983</v>
@@ -13477,7 +13477,7 @@
         <v>6.07998418807983</v>
       </c>
       <c r="G452" t="n">
-        <v>5.27025127410889</v>
+        <v>5.27025175094604</v>
       </c>
       <c r="H452" t="n">
         <v>767742</v>
@@ -13506,7 +13506,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G453" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H453" t="n">
         <v>421091</v>
@@ -13564,7 +13564,7 @@
         <v>5.91502285003662</v>
       </c>
       <c r="G455" t="n">
-        <v>5.12726068496704</v>
+        <v>5.12726020812988</v>
       </c>
       <c r="H455" t="n">
         <v>728051</v>
@@ -13680,7 +13680,7 @@
         <v>5.93858909606934</v>
       </c>
       <c r="G459" t="n">
-        <v>5.1476879119873</v>
+        <v>5.14768838882446</v>
       </c>
       <c r="H459" t="n">
         <v>837053</v>
@@ -13796,7 +13796,7 @@
         <v>5.9574408531189</v>
       </c>
       <c r="G463" t="n">
-        <v>5.16402912139893</v>
+        <v>5.16402864456177</v>
       </c>
       <c r="H463" t="n">
         <v>339919</v>
@@ -13883,7 +13883,7 @@
         <v>5.9574408531189</v>
       </c>
       <c r="G466" t="n">
-        <v>5.16402912139893</v>
+        <v>5.16402864456177</v>
       </c>
       <c r="H466" t="n">
         <v>435608</v>
@@ -13970,7 +13970,7 @@
         <v>6.03285217285156</v>
       </c>
       <c r="G469" t="n">
-        <v>5.22939682006836</v>
+        <v>5.22939729690552</v>
       </c>
       <c r="H469" t="n">
         <v>638649</v>
@@ -13999,7 +13999,7 @@
         <v>6.05170488357544</v>
       </c>
       <c r="G470" t="n">
-        <v>5.2457389831543</v>
+        <v>5.24573850631714</v>
       </c>
       <c r="H470" t="n">
         <v>370019</v>
@@ -14028,7 +14028,7 @@
         <v>6.07998418807983</v>
       </c>
       <c r="G471" t="n">
-        <v>5.27025127410889</v>
+        <v>5.27025175094604</v>
       </c>
       <c r="H471" t="n">
         <v>678574</v>
@@ -14086,7 +14086,7 @@
         <v>5.99514722824097</v>
       </c>
       <c r="G473" t="n">
-        <v>5.19671392440796</v>
+        <v>5.1967134475708</v>
       </c>
       <c r="H473" t="n">
         <v>443981</v>
@@ -14231,7 +14231,7 @@
         <v>5.73592281341553</v>
       </c>
       <c r="G478" t="n">
-        <v>4.97201251983643</v>
+        <v>4.97201299667358</v>
       </c>
       <c r="H478" t="n">
         <v>1168174</v>
@@ -14260,7 +14260,7 @@
         <v>5.51440382003784</v>
       </c>
       <c r="G479" t="n">
-        <v>4.77999544143677</v>
+        <v>4.77999591827393</v>
       </c>
       <c r="H479" t="n">
         <v>2444405</v>
@@ -14289,7 +14289,7 @@
         <v>5.53797006607056</v>
       </c>
       <c r="G480" t="n">
-        <v>4.80042362213135</v>
+        <v>4.80042314529419</v>
       </c>
       <c r="H480" t="n">
         <v>1129596</v>
@@ -14318,7 +14318,7 @@
         <v>5.43899297714233</v>
       </c>
       <c r="G481" t="n">
-        <v>4.71462869644165</v>
+        <v>4.71462774276733</v>
       </c>
       <c r="H481" t="n">
         <v>861462</v>
@@ -14405,7 +14405,7 @@
         <v>5.45784616470337</v>
       </c>
       <c r="G484" t="n">
-        <v>4.73097038269043</v>
+        <v>4.73096990585327</v>
       </c>
       <c r="H484" t="n">
         <v>392610</v>
@@ -14434,7 +14434,7 @@
         <v>5.51440382003784</v>
       </c>
       <c r="G485" t="n">
-        <v>4.77999544143677</v>
+        <v>4.77999591827393</v>
       </c>
       <c r="H485" t="n">
         <v>1043118</v>
@@ -14492,7 +14492,7 @@
         <v>5.51440382003784</v>
       </c>
       <c r="G487" t="n">
-        <v>4.77999544143677</v>
+        <v>4.77999591827393</v>
       </c>
       <c r="H487" t="n">
         <v>363321</v>
@@ -14550,7 +14550,7 @@
         <v>5.49083805084229</v>
       </c>
       <c r="G489" t="n">
-        <v>4.75956869125366</v>
+        <v>4.7595682144165</v>
       </c>
       <c r="H489" t="n">
         <v>776620</v>
@@ -14579,7 +14579,7 @@
         <v>5.50497817993164</v>
       </c>
       <c r="G490" t="n">
-        <v>4.77182579040527</v>
+        <v>4.77182483673096</v>
       </c>
       <c r="H490" t="n">
         <v>806412</v>
@@ -14637,7 +14637,7 @@
         <v>5.42956686019897</v>
       </c>
       <c r="G492" t="n">
-        <v>4.70645761489868</v>
+        <v>4.70645713806152</v>
       </c>
       <c r="H492" t="n">
         <v>2971530</v>
@@ -14724,7 +14724,7 @@
         <v>5.51440382003784</v>
       </c>
       <c r="G495" t="n">
-        <v>4.77999544143677</v>
+        <v>4.77999591827393</v>
       </c>
       <c r="H495" t="n">
         <v>550046</v>
@@ -14956,7 +14956,7 @@
         <v>5.25989294052124</v>
       </c>
       <c r="G503" t="n">
-        <v>4.55938100814819</v>
+        <v>4.55938053131104</v>
       </c>
       <c r="H503" t="n">
         <v>1787531</v>
@@ -14985,7 +14985,7 @@
         <v>5.30231094360352</v>
       </c>
       <c r="G504" t="n">
-        <v>4.59614944458008</v>
+        <v>4.59614896774292</v>
       </c>
       <c r="H504" t="n">
         <v>994111</v>
@@ -15043,7 +15043,7 @@
         <v>5.231614112854</v>
       </c>
       <c r="G506" t="n">
-        <v>4.53486824035645</v>
+        <v>4.53486776351929</v>
       </c>
       <c r="H506" t="n">
         <v>845572</v>
@@ -15072,7 +15072,7 @@
         <v>5.30702495574951</v>
       </c>
       <c r="G507" t="n">
-        <v>4.60023546218872</v>
+        <v>4.60023498535156</v>
       </c>
       <c r="H507" t="n">
         <v>800035</v>
@@ -15101,7 +15101,7 @@
         <v>5.30702495574951</v>
       </c>
       <c r="G508" t="n">
-        <v>4.60023546218872</v>
+        <v>4.60023498535156</v>
       </c>
       <c r="H508" t="n">
         <v>699714</v>
@@ -15130,7 +15130,7 @@
         <v>5.27403211593628</v>
       </c>
       <c r="G509" t="n">
-        <v>4.57163667678833</v>
+        <v>4.57163619995117</v>
       </c>
       <c r="H509" t="n">
         <v>504727</v>
@@ -15159,7 +15159,7 @@
         <v>5.30231094360352</v>
       </c>
       <c r="G510" t="n">
-        <v>4.59614944458008</v>
+        <v>4.59614896774292</v>
       </c>
       <c r="H510" t="n">
         <v>735378</v>
@@ -15188,7 +15188,7 @@
         <v>5.23632717132568</v>
       </c>
       <c r="G511" t="n">
-        <v>4.53895378112793</v>
+        <v>4.53895330429077</v>
       </c>
       <c r="H511" t="n">
         <v>734074</v>
@@ -15217,7 +15217,7 @@
         <v>5.23632717132568</v>
       </c>
       <c r="G512" t="n">
-        <v>4.53895378112793</v>
+        <v>4.53895330429077</v>
       </c>
       <c r="H512" t="n">
         <v>360692</v>
@@ -15246,7 +15246,7 @@
         <v>5.32587718963623</v>
       </c>
       <c r="G513" t="n">
-        <v>4.61657667160034</v>
+        <v>4.6165771484375</v>
       </c>
       <c r="H513" t="n">
         <v>531448</v>
@@ -15275,7 +15275,7 @@
         <v>5.40600109100342</v>
       </c>
       <c r="G514" t="n">
-        <v>4.68602991104126</v>
+        <v>4.68603038787842</v>
       </c>
       <c r="H514" t="n">
         <v>722262</v>
@@ -15333,7 +15333,7 @@
         <v>5.34001684188843</v>
       </c>
       <c r="G516" t="n">
-        <v>4.62883377075195</v>
+        <v>4.62883329391479</v>
       </c>
       <c r="H516" t="n">
         <v>832404</v>
@@ -15391,7 +15391,7 @@
         <v>5.27874612808228</v>
       </c>
       <c r="G518" t="n">
-        <v>4.57572317123413</v>
+        <v>4.57572269439697</v>
       </c>
       <c r="H518" t="n">
         <v>1086598</v>
@@ -15420,7 +15420,7 @@
         <v>5.30231094360352</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59614944458008</v>
+        <v>4.59614896774292</v>
       </c>
       <c r="H519" t="n">
         <v>671419</v>
@@ -15449,7 +15449,7 @@
         <v>5.54739618301392</v>
       </c>
       <c r="G520" t="n">
-        <v>4.80859470367432</v>
+        <v>4.80859422683716</v>
       </c>
       <c r="H520" t="n">
         <v>3160136</v>
@@ -15507,7 +15507,7 @@
         <v>5.55682182312012</v>
       </c>
       <c r="G522" t="n">
-        <v>4.81676483154297</v>
+        <v>4.81676435470581</v>
       </c>
       <c r="H522" t="n">
         <v>818391</v>
@@ -15536,7 +15536,7 @@
         <v>5.5238299369812</v>
       </c>
       <c r="G523" t="n">
-        <v>4.78816604614258</v>
+        <v>4.78816699981689</v>
       </c>
       <c r="H523" t="n">
         <v>874300</v>
@@ -15565,7 +15565,7 @@
         <v>5.46255922317505</v>
       </c>
       <c r="G524" t="n">
-        <v>4.73505592346191</v>
+        <v>4.73505544662476</v>
       </c>
       <c r="H524" t="n">
         <v>835940</v>
@@ -15594,7 +15594,7 @@
         <v>5.7689151763916</v>
       </c>
       <c r="G525" t="n">
-        <v>5.00061130523682</v>
+        <v>5.00061082839966</v>
       </c>
       <c r="H525" t="n">
         <v>2644903</v>
@@ -15652,7 +15652,7 @@
         <v>5.79719400405884</v>
       </c>
       <c r="G527" t="n">
-        <v>5.02512454986572</v>
+        <v>5.02512407302856</v>
       </c>
       <c r="H527" t="n">
         <v>1083963</v>
@@ -15681,7 +15681,7 @@
         <v>5.64165878295898</v>
       </c>
       <c r="G528" t="n">
-        <v>4.89030265808105</v>
+        <v>4.89030313491821</v>
       </c>
       <c r="H528" t="n">
         <v>1296828</v>
@@ -15710,7 +15710,7 @@
         <v>5.6652250289917</v>
       </c>
       <c r="G529" t="n">
-        <v>4.91073083877563</v>
+        <v>4.91073036193848</v>
       </c>
       <c r="H529" t="n">
         <v>979165</v>
@@ -15768,7 +15768,7 @@
         <v>5.75477504730225</v>
       </c>
       <c r="G531" t="n">
-        <v>4.98835468292236</v>
+        <v>4.98835420608521</v>
       </c>
       <c r="H531" t="n">
         <v>687971</v>
@@ -15797,7 +15797,7 @@
         <v>5.58981513977051</v>
       </c>
       <c r="G532" t="n">
-        <v>4.84536409378052</v>
+        <v>4.84536361694336</v>
       </c>
       <c r="H532" t="n">
         <v>1128600</v>
@@ -15855,7 +15855,7 @@
         <v>5.6652250289917</v>
       </c>
       <c r="G534" t="n">
-        <v>4.91073083877563</v>
+        <v>4.91073036193848</v>
       </c>
       <c r="H534" t="n">
         <v>947938</v>
@@ -16000,7 +16000,7 @@
         <v>5.23632717132568</v>
       </c>
       <c r="G539" t="n">
-        <v>4.53895378112793</v>
+        <v>4.53895330429077</v>
       </c>
       <c r="H539" t="n">
         <v>819211</v>
@@ -16058,7 +16058,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G541" t="n">
-        <v>4.50626945495605</v>
+        <v>4.50626993179321</v>
       </c>
       <c r="H541" t="n">
         <v>584670</v>
@@ -16087,7 +16087,7 @@
         <v>5.18448209762573</v>
       </c>
       <c r="G542" t="n">
-        <v>4.49401330947876</v>
+        <v>4.4940128326416</v>
       </c>
       <c r="H542" t="n">
         <v>581309</v>
@@ -16116,7 +16116,7 @@
         <v>5.20804786682129</v>
       </c>
       <c r="G543" t="n">
-        <v>4.51443958282471</v>
+        <v>4.51444053649902</v>
       </c>
       <c r="H543" t="n">
         <v>406872</v>
@@ -16145,7 +16145,7 @@
         <v>5.22690105438232</v>
       </c>
       <c r="G544" t="n">
-        <v>4.53078317642212</v>
+        <v>4.5307822227478</v>
       </c>
       <c r="H544" t="n">
         <v>389762</v>
@@ -16174,7 +16174,7 @@
         <v>5.31173801422119</v>
       </c>
       <c r="G545" t="n">
-        <v>4.60432100296021</v>
+        <v>4.60432052612305</v>
       </c>
       <c r="H545" t="n">
         <v>434613</v>
@@ -16203,7 +16203,7 @@
         <v>5.25989294052124</v>
       </c>
       <c r="G546" t="n">
-        <v>4.55938100814819</v>
+        <v>4.55938053131104</v>
       </c>
       <c r="H546" t="n">
         <v>238286</v>
@@ -16319,7 +16319,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G550" t="n">
-        <v>4.44090223312378</v>
+        <v>4.44090175628662</v>
       </c>
       <c r="H550" t="n">
         <v>291892</v>
@@ -16348,7 +16348,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G551" t="n">
-        <v>4.50626945495605</v>
+        <v>4.50626993179321</v>
       </c>
       <c r="H551" t="n">
         <v>340572</v>
@@ -16406,7 +16406,7 @@
         <v>5.06665277481079</v>
       </c>
       <c r="G553" t="n">
-        <v>4.39187669754028</v>
+        <v>4.39187622070312</v>
       </c>
       <c r="H553" t="n">
         <v>523357</v>
@@ -16435,7 +16435,7 @@
         <v>4.9771032333374</v>
       </c>
       <c r="G554" t="n">
-        <v>4.31425285339355</v>
+        <v>4.3142523765564</v>
       </c>
       <c r="H554" t="n">
         <v>868376</v>
@@ -16464,7 +16464,7 @@
         <v>5.014808177948</v>
       </c>
       <c r="G555" t="n">
-        <v>4.34693574905396</v>
+        <v>4.34693622589111</v>
       </c>
       <c r="H555" t="n">
         <v>789569</v>
@@ -16493,7 +16493,7 @@
         <v>5.07136583328247</v>
       </c>
       <c r="G556" t="n">
-        <v>4.39596176147461</v>
+        <v>4.39596080780029</v>
       </c>
       <c r="H556" t="n">
         <v>540514</v>
@@ -16522,7 +16522,7 @@
         <v>5.04780006408691</v>
       </c>
       <c r="G557" t="n">
-        <v>4.37553405761719</v>
+        <v>4.37553453445435</v>
       </c>
       <c r="H557" t="n">
         <v>779003</v>
@@ -16551,7 +16551,7 @@
         <v>5.09964513778687</v>
       </c>
       <c r="G558" t="n">
-        <v>4.4204740524292</v>
+        <v>4.42047452926636</v>
       </c>
       <c r="H558" t="n">
         <v>736840</v>
@@ -16609,7 +16609,7 @@
         <v>5.12321090698242</v>
       </c>
       <c r="G560" t="n">
-        <v>4.44090223312378</v>
+        <v>4.44090175628662</v>
       </c>
       <c r="H560" t="n">
         <v>392393</v>
@@ -16638,7 +16638,7 @@
         <v>5.17976903915405</v>
       </c>
       <c r="G561" t="n">
-        <v>4.48992776870728</v>
+        <v>4.48992729187012</v>
       </c>
       <c r="H561" t="n">
         <v>408879</v>
@@ -16667,7 +16667,7 @@
         <v>5.25517988204956</v>
       </c>
       <c r="G562" t="n">
-        <v>4.55529546737671</v>
+        <v>4.55529499053955</v>
       </c>
       <c r="H562" t="n">
         <v>686343</v>
@@ -16696,7 +16696,7 @@
         <v>5.231614112854</v>
       </c>
       <c r="G563" t="n">
-        <v>4.53486824035645</v>
+        <v>4.53486776351929</v>
       </c>
       <c r="H563" t="n">
         <v>731144</v>
@@ -16812,7 +16812,7 @@
         <v>5.19862222671509</v>
       </c>
       <c r="G567" t="n">
-        <v>4.50626945495605</v>
+        <v>4.50626993179321</v>
       </c>
       <c r="H567" t="n">
         <v>679310</v>
@@ -16841,7 +16841,7 @@
         <v>5.14677715301514</v>
       </c>
       <c r="G568" t="n">
-        <v>4.46132946014404</v>
+        <v>4.46132898330688</v>
       </c>
       <c r="H568" t="n">
         <v>433413</v>
@@ -16870,7 +16870,7 @@
         <v>5.06194019317627</v>
       </c>
       <c r="G569" t="n">
-        <v>4.3877911567688</v>
+        <v>4.38779163360596</v>
       </c>
       <c r="H569" t="n">
         <v>633113</v>
@@ -16899,7 +16899,7 @@
         <v>5.01009511947632</v>
       </c>
       <c r="G570" t="n">
-        <v>4.34285116195679</v>
+        <v>4.34285068511963</v>
       </c>
       <c r="H570" t="n">
         <v>740438</v>
@@ -16928,7 +16928,7 @@
         <v>4.92054510116577</v>
       </c>
       <c r="G571" t="n">
-        <v>4.26522731781006</v>
+        <v>4.2652268409729</v>
       </c>
       <c r="H571" t="n">
         <v>885597</v>
@@ -17015,7 +17015,7 @@
         <v>4.69619798660278</v>
       </c>
       <c r="G574" t="n">
-        <v>4.07075786590576</v>
+        <v>4.07075834274292</v>
       </c>
       <c r="H574" t="n">
         <v>1676367</v>
@@ -17044,7 +17044,7 @@
         <v>4.68488693237305</v>
       </c>
       <c r="G575" t="n">
-        <v>4.06095409393311</v>
+        <v>4.06095361709595</v>
       </c>
       <c r="H575" t="n">
         <v>950101</v>
@@ -17102,7 +17102,7 @@
         <v>4.68488693237305</v>
       </c>
       <c r="G577" t="n">
-        <v>4.06095409393311</v>
+        <v>4.06095361709595</v>
       </c>
       <c r="H577" t="n">
         <v>1402245</v>
@@ -17160,7 +17160,7 @@
         <v>4.62455797195435</v>
       </c>
       <c r="G579" t="n">
-        <v>4.00865936279297</v>
+        <v>4.00865983963013</v>
       </c>
       <c r="H579" t="n">
         <v>772000</v>
@@ -17218,7 +17218,7 @@
         <v>4.63021421432495</v>
       </c>
       <c r="G581" t="n">
-        <v>4.01356267929077</v>
+        <v>4.01356220245361</v>
       </c>
       <c r="H581" t="n">
         <v>906916</v>
@@ -17334,7 +17334,7 @@
         <v>4.67545986175537</v>
       </c>
       <c r="G585" t="n">
-        <v>4.05278253555298</v>
+        <v>4.05278205871582</v>
       </c>
       <c r="H585" t="n">
         <v>814446</v>
@@ -17363,7 +17363,7 @@
         <v>4.70373916625977</v>
       </c>
       <c r="G586" t="n">
-        <v>4.07729482650757</v>
+        <v>4.07729530334473</v>
       </c>
       <c r="H586" t="n">
         <v>1729690</v>
@@ -17421,7 +17421,7 @@
         <v>3.28036308288574</v>
       </c>
       <c r="G588" t="n">
-        <v>2.84348464012146</v>
+        <v>2.84348440170288</v>
       </c>
       <c r="H588" t="n">
         <v>19510898</v>
@@ -17508,7 +17508,7 @@
         <v>3.26528096199036</v>
       </c>
       <c r="G591" t="n">
-        <v>2.83041095733643</v>
+        <v>2.830411195755</v>
       </c>
       <c r="H591" t="n">
         <v>2500612</v>
@@ -17566,7 +17566,7 @@
         <v>3.2992160320282</v>
       </c>
       <c r="G593" t="n">
-        <v>2.85982632637024</v>
+        <v>2.85982656478882</v>
       </c>
       <c r="H593" t="n">
         <v>5647949</v>
@@ -17653,7 +17653,7 @@
         <v>3.47643089294434</v>
       </c>
       <c r="G596" t="n">
-        <v>3.01343989372253</v>
+        <v>3.01344013214111</v>
       </c>
       <c r="H596" t="n">
         <v>4580985</v>
@@ -17740,7 +17740,7 @@
         <v>3.56315302848816</v>
       </c>
       <c r="G599" t="n">
-        <v>3.08861255645752</v>
+        <v>3.08861231803894</v>
       </c>
       <c r="H599" t="n">
         <v>2502209</v>
@@ -17827,7 +17827,7 @@
         <v>3.58766198158264</v>
       </c>
       <c r="G602" t="n">
-        <v>3.10985732078552</v>
+        <v>3.10985708236694</v>
       </c>
       <c r="H602" t="n">
         <v>3751232</v>
@@ -17856,7 +17856,7 @@
         <v>3.58200597763062</v>
       </c>
       <c r="G603" t="n">
-        <v>3.1049542427063</v>
+        <v>3.10495471954346</v>
       </c>
       <c r="H603" t="n">
         <v>1193334</v>
@@ -17885,7 +17885,7 @@
         <v>3.50282502174377</v>
       </c>
       <c r="G604" t="n">
-        <v>3.0363187789917</v>
+        <v>3.03631901741028</v>
       </c>
       <c r="H604" t="n">
         <v>1657974</v>
@@ -17914,7 +17914,7 @@
         <v>3.39913511276245</v>
       </c>
       <c r="G605" t="n">
-        <v>2.9464385509491</v>
+        <v>2.94643831253052</v>
       </c>
       <c r="H605" t="n">
         <v>3948642</v>
@@ -17972,7 +17972,7 @@
         <v>3.32372403144836</v>
       </c>
       <c r="G607" t="n">
-        <v>2.8810703754425</v>
+        <v>2.88107061386108</v>
       </c>
       <c r="H607" t="n">
         <v>1863979</v>
@@ -18001,7 +18001,7 @@
         <v>3.33692097663879</v>
       </c>
       <c r="G608" t="n">
-        <v>2.89250993728638</v>
+        <v>2.8925096988678</v>
       </c>
       <c r="H608" t="n">
         <v>1825564</v>
@@ -18030,7 +18030,7 @@
         <v>3.27093696594238</v>
       </c>
       <c r="G609" t="n">
-        <v>2.83531355857849</v>
+        <v>2.83531379699707</v>
       </c>
       <c r="H609" t="n">
         <v>2073505</v>
@@ -18146,7 +18146,7 @@
         <v>3.09937810897827</v>
       </c>
       <c r="G613" t="n">
-        <v>2.68660283088684</v>
+        <v>2.68660306930542</v>
       </c>
       <c r="H613" t="n">
         <v>1539852</v>
@@ -18175,7 +18175,7 @@
         <v>2.88634204864502</v>
       </c>
       <c r="G614" t="n">
-        <v>2.50193905830383</v>
+        <v>2.50193929672241</v>
       </c>
       <c r="H614" t="n">
         <v>3938706</v>
@@ -18320,7 +18320,7 @@
         <v>2.83921098709106</v>
       </c>
       <c r="G619" t="n">
-        <v>2.46108460426331</v>
+        <v>2.46108508110046</v>
       </c>
       <c r="H619" t="n">
         <v>1620787</v>
@@ -18349,7 +18349,7 @@
         <v>2.82789897918701</v>
       </c>
       <c r="G620" t="n">
-        <v>2.45127964019775</v>
+        <v>2.45127940177917</v>
       </c>
       <c r="H620" t="n">
         <v>1320296</v>
@@ -18378,7 +18378,7 @@
         <v>2.79773497581482</v>
       </c>
       <c r="G621" t="n">
-        <v>2.42513298988342</v>
+        <v>2.42513275146484</v>
       </c>
       <c r="H621" t="n">
         <v>1568122</v>
@@ -18407,7 +18407,7 @@
         <v>2.72986507415771</v>
       </c>
       <c r="G622" t="n">
-        <v>2.36630129814148</v>
+        <v>2.36630177497864</v>
       </c>
       <c r="H622" t="n">
         <v>859959</v>
@@ -18465,7 +18465,7 @@
         <v>2.6638810634613</v>
       </c>
       <c r="G624" t="n">
-        <v>2.30910563468933</v>
+        <v>2.30910515785217</v>
       </c>
       <c r="H624" t="n">
         <v>2202075</v>
@@ -18552,7 +18552,7 @@
         <v>2.56773209571838</v>
       </c>
       <c r="G627" t="n">
-        <v>2.2257616519928</v>
+        <v>2.22576141357422</v>
       </c>
       <c r="H627" t="n">
         <v>3206598</v>
@@ -18639,7 +18639,7 @@
         <v>2.56396198272705</v>
       </c>
       <c r="G630" t="n">
-        <v>2.22249388694763</v>
+        <v>2.22249364852905</v>
       </c>
       <c r="H630" t="n">
         <v>1879595</v>
@@ -18755,7 +18755,7 @@
         <v>2.59789705276489</v>
       </c>
       <c r="G634" t="n">
-        <v>2.25190925598145</v>
+        <v>2.25190901756287</v>
       </c>
       <c r="H634" t="n">
         <v>1615061</v>
@@ -18784,7 +18784,7 @@
         <v>2.59224104881287</v>
       </c>
       <c r="G635" t="n">
-        <v>2.24700665473938</v>
+        <v>2.2470064163208</v>
       </c>
       <c r="H635" t="n">
         <v>1949836</v>
@@ -18813,7 +18813,7 @@
         <v>2.62240505218506</v>
       </c>
       <c r="G636" t="n">
-        <v>2.27315306663513</v>
+        <v>2.27315282821655</v>
       </c>
       <c r="H636" t="n">
         <v>1544547</v>
@@ -18871,7 +18871,7 @@
         <v>2.65633988380432</v>
       </c>
       <c r="G638" t="n">
-        <v>2.30256843566895</v>
+        <v>2.3025689125061</v>
       </c>
       <c r="H638" t="n">
         <v>1287154</v>
@@ -18929,7 +18929,7 @@
         <v>2.6638810634613</v>
       </c>
       <c r="G640" t="n">
-        <v>2.30910563468933</v>
+        <v>2.30910515785217</v>
       </c>
       <c r="H640" t="n">
         <v>1593429</v>
@@ -18987,7 +18987,7 @@
         <v>2.65256905555725</v>
       </c>
       <c r="G642" t="n">
-        <v>2.29929995536804</v>
+        <v>2.29929971694946</v>
       </c>
       <c r="H642" t="n">
         <v>935202</v>
@@ -19074,7 +19074,7 @@
         <v>2.54510903358459</v>
       </c>
       <c r="G645" t="n">
-        <v>2.20615124702454</v>
+        <v>2.20615148544312</v>
       </c>
       <c r="H645" t="n">
         <v>1275497</v>
@@ -19103,7 +19103,7 @@
         <v>2.50551891326904</v>
       </c>
       <c r="G646" t="n">
-        <v>2.17183375358582</v>
+        <v>2.17183399200439</v>
       </c>
       <c r="H646" t="n">
         <v>1294097</v>
@@ -19190,7 +19190,7 @@
         <v>2.51682996749878</v>
       </c>
       <c r="G649" t="n">
-        <v>2.18163871765137</v>
+        <v>2.18163847923279</v>
       </c>
       <c r="H649" t="n">
         <v>638737</v>
@@ -19219,7 +19219,7 @@
         <v>2.62240505218506</v>
       </c>
       <c r="G650" t="n">
-        <v>2.27315306663513</v>
+        <v>2.27315282821655</v>
       </c>
       <c r="H650" t="n">
         <v>1740904</v>
@@ -19306,7 +19306,7 @@
         <v>2.73552107810974</v>
       </c>
       <c r="G653" t="n">
-        <v>2.3712043762207</v>
+        <v>2.37120461463928</v>
       </c>
       <c r="H653" t="n">
         <v>667776</v>
@@ -19335,7 +19335,7 @@
         <v>2.65256905555725</v>
       </c>
       <c r="G654" t="n">
-        <v>2.29929995536804</v>
+        <v>2.29929971694946</v>
       </c>
       <c r="H654" t="n">
         <v>963715</v>
@@ -19364,7 +19364,7 @@
         <v>2.61674904823303</v>
       </c>
       <c r="G655" t="n">
-        <v>2.26825046539307</v>
+        <v>2.26825070381165</v>
       </c>
       <c r="H655" t="n">
         <v>1138128</v>
@@ -19451,7 +19451,7 @@
         <v>2.6638810634613</v>
       </c>
       <c r="G658" t="n">
-        <v>2.30910563468933</v>
+        <v>2.30910515785217</v>
       </c>
       <c r="H658" t="n">
         <v>623187</v>
@@ -19480,7 +19480,7 @@
         <v>2.63183093070984</v>
       </c>
       <c r="G659" t="n">
-        <v>2.28132343292236</v>
+        <v>2.28132390975952</v>
       </c>
       <c r="H659" t="n">
         <v>625782</v>
@@ -19596,7 +19596,7 @@
         <v>2.43010807037354</v>
       </c>
       <c r="G663" t="n">
-        <v>2.10646605491638</v>
+        <v>2.10646629333496</v>
       </c>
       <c r="H663" t="n">
         <v>707782</v>
@@ -19654,7 +19654,7 @@
         <v>2.49609208106995</v>
       </c>
       <c r="G665" t="n">
-        <v>2.16366243362427</v>
+        <v>2.16366267204285</v>
       </c>
       <c r="H665" t="n">
         <v>529839</v>
@@ -19683,7 +19683,7 @@
         <v>2.49609208106995</v>
       </c>
       <c r="G666" t="n">
-        <v>2.16366243362427</v>
+        <v>2.16366267204285</v>
       </c>
       <c r="H666" t="n">
         <v>457968</v>
@@ -19799,7 +19799,7 @@
         <v>2.22838401794434</v>
       </c>
       <c r="G670" t="n">
-        <v>1.93160796165466</v>
+        <v>1.93160772323608</v>
       </c>
       <c r="H670" t="n">
         <v>972884</v>
@@ -19828,7 +19828,7 @@
         <v>2.26231908798218</v>
       </c>
       <c r="G671" t="n">
-        <v>1.96102344989777</v>
+        <v>1.96102368831635</v>
       </c>
       <c r="H671" t="n">
         <v>850463</v>
@@ -19915,7 +19915,7 @@
         <v>2.42822289466858</v>
       </c>
       <c r="G674" t="n">
-        <v>2.1048321723938</v>
+        <v>2.10483241081238</v>
       </c>
       <c r="H674" t="n">
         <v>1482628</v>
@@ -20089,7 +20089,7 @@
         <v>2.44707489013672</v>
       </c>
       <c r="G680" t="n">
-        <v>2.12117338180542</v>
+        <v>2.121173620224</v>
       </c>
       <c r="H680" t="n">
         <v>581279</v>
@@ -20118,7 +20118,7 @@
         <v>2.43199300765991</v>
       </c>
       <c r="G681" t="n">
-        <v>2.10810017585754</v>
+        <v>2.10810041427612</v>
       </c>
       <c r="H681" t="n">
         <v>650896</v>
@@ -20147,7 +20147,7 @@
         <v>2.43387794494629</v>
       </c>
       <c r="G682" t="n">
-        <v>2.10973429679871</v>
+        <v>2.10973405838013</v>
       </c>
       <c r="H682" t="n">
         <v>235141</v>
@@ -20176,7 +20176,7 @@
         <v>2.38674688339233</v>
       </c>
       <c r="G683" t="n">
-        <v>2.06888008117676</v>
+        <v>2.06887984275818</v>
       </c>
       <c r="H683" t="n">
         <v>602259</v>
@@ -20234,7 +20234,7 @@
         <v>2.3584680557251</v>
       </c>
       <c r="G685" t="n">
-        <v>2.04436731338501</v>
+        <v>2.04436707496643</v>
       </c>
       <c r="H685" t="n">
         <v>961137</v>
@@ -20292,7 +20292,7 @@
         <v>2.43764901161194</v>
       </c>
       <c r="G687" t="n">
-        <v>2.11300325393677</v>
+        <v>2.11300301551819</v>
       </c>
       <c r="H687" t="n">
         <v>1031942</v>
@@ -20350,7 +20350,7 @@
         <v>2.36035299301147</v>
       </c>
       <c r="G689" t="n">
-        <v>2.04600095748901</v>
+        <v>2.04600119590759</v>
       </c>
       <c r="H689" t="n">
         <v>336844</v>
@@ -20379,7 +20379,7 @@
         <v>2.28494191169739</v>
       </c>
       <c r="G690" t="n">
-        <v>1.98063325881958</v>
+        <v>1.98063349723816</v>
       </c>
       <c r="H690" t="n">
         <v>930830</v>
@@ -20408,7 +20408,7 @@
         <v>2.28682804107666</v>
       </c>
       <c r="G691" t="n">
-        <v>1.98226833343506</v>
+        <v>1.98226857185364</v>
       </c>
       <c r="H691" t="n">
         <v>1350172</v>
@@ -20437,7 +20437,7 @@
         <v>2.3584680557251</v>
       </c>
       <c r="G692" t="n">
-        <v>2.04436731338501</v>
+        <v>2.04436707496643</v>
       </c>
       <c r="H692" t="n">
         <v>1661009</v>
@@ -20466,7 +20466,7 @@
         <v>2.39805793762207</v>
       </c>
       <c r="G693" t="n">
-        <v>2.07868432998657</v>
+        <v>2.07868456840515</v>
       </c>
       <c r="H693" t="n">
         <v>1715806</v>
@@ -20495,7 +20495,7 @@
         <v>2.52437090873718</v>
       </c>
       <c r="G694" t="n">
-        <v>2.18817496299744</v>
+        <v>2.18817543983459</v>
       </c>
       <c r="H694" t="n">
         <v>2228810</v>
@@ -20524,7 +20524,7 @@
         <v>2.65633988380432</v>
       </c>
       <c r="G695" t="n">
-        <v>2.30256843566895</v>
+        <v>2.3025689125061</v>
       </c>
       <c r="H695" t="n">
         <v>5128352</v>
@@ -20553,7 +20553,7 @@
         <v>2.61674904823303</v>
       </c>
       <c r="G696" t="n">
-        <v>2.26825046539307</v>
+        <v>2.26825070381165</v>
       </c>
       <c r="H696" t="n">
         <v>2075384</v>
@@ -20669,7 +20669,7 @@
         <v>2.33584499359131</v>
       </c>
       <c r="G700" t="n">
-        <v>2.02475690841675</v>
+        <v>2.02475738525391</v>
       </c>
       <c r="H700" t="n">
         <v>4161423</v>
@@ -20727,7 +20727,7 @@
         <v>2.25854897499084</v>
       </c>
       <c r="G702" t="n">
-        <v>1.95775556564331</v>
+        <v>1.95775532722473</v>
       </c>
       <c r="H702" t="n">
         <v>2275972</v>
@@ -20756,7 +20756,7 @@
         <v>2.25666308403015</v>
       </c>
       <c r="G703" t="n">
-        <v>1.9561208486557</v>
+        <v>1.95612108707428</v>
       </c>
       <c r="H703" t="n">
         <v>2290274</v>
@@ -20785,7 +20785,7 @@
         <v>2.23781108856201</v>
       </c>
       <c r="G704" t="n">
-        <v>1.93977928161621</v>
+        <v>1.93977963924408</v>
       </c>
       <c r="H704" t="n">
         <v>572312</v>
@@ -20814,7 +20814,7 @@
         <v>2.19633507728577</v>
       </c>
       <c r="G705" t="n">
-        <v>1.90382707118988</v>
+        <v>1.90382730960846</v>
       </c>
       <c r="H705" t="n">
         <v>1378014</v>
@@ -20843,7 +20843,7 @@
         <v>2.11715388298035</v>
       </c>
       <c r="G706" t="n">
-        <v>1.83519124984741</v>
+        <v>1.83519148826599</v>
       </c>
       <c r="H706" t="n">
         <v>1637795</v>
@@ -20901,7 +20901,7 @@
         <v>1.91354501247406</v>
       </c>
       <c r="G708" t="n">
-        <v>1.65869927406311</v>
+        <v>1.65869915485382</v>
       </c>
       <c r="H708" t="n">
         <v>2623162</v>
@@ -21017,7 +21017,7 @@
         <v>1.83813405036926</v>
       </c>
       <c r="G712" t="n">
-        <v>1.59333145618439</v>
+        <v>1.59333157539368</v>
       </c>
       <c r="H712" t="n">
         <v>1494844</v>
@@ -21162,7 +21162,7 @@
         <v>1.48653197288513</v>
       </c>
       <c r="G717" t="n">
-        <v>1.28855574131012</v>
+        <v>1.28855562210083</v>
       </c>
       <c r="H717" t="n">
         <v>2964565</v>
@@ -21220,7 +21220,7 @@
         <v>1.43468701839447</v>
       </c>
       <c r="G719" t="n">
-        <v>1.24361550807953</v>
+        <v>1.24361538887024</v>
       </c>
       <c r="H719" t="n">
         <v>3658364</v>
@@ -21249,7 +21249,7 @@
         <v>1.4101790189743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.22237145900726</v>
+        <v>1.22237133979797</v>
       </c>
       <c r="H720" t="n">
         <v>1596691</v>
@@ -21336,7 +21336,7 @@
         <v>1.4403430223465</v>
       </c>
       <c r="G723" t="n">
-        <v>1.2485179901123</v>
+        <v>1.24851810932159</v>
       </c>
       <c r="H723" t="n">
         <v>1773305</v>
@@ -21394,7 +21394,7 @@
         <v>1.48464703559875</v>
       </c>
       <c r="G725" t="n">
-        <v>1.28692173957825</v>
+        <v>1.28692185878754</v>
       </c>
       <c r="H725" t="n">
         <v>1321948</v>
@@ -21539,7 +21539,7 @@
         <v>1.48464703559875</v>
       </c>
       <c r="G730" t="n">
-        <v>1.28692173957825</v>
+        <v>1.28692185878754</v>
       </c>
       <c r="H730" t="n">
         <v>5995183</v>
@@ -21597,7 +21597,7 @@
         <v>1.46108102798462</v>
       </c>
       <c r="G732" t="n">
-        <v>1.2664942741394</v>
+        <v>1.26649451255798</v>
       </c>
       <c r="H732" t="n">
         <v>2352817</v>
@@ -21655,7 +21655,7 @@
         <v>1.43468701839447</v>
       </c>
       <c r="G734" t="n">
-        <v>1.24361550807953</v>
+        <v>1.24361538887024</v>
       </c>
       <c r="H734" t="n">
         <v>1525577</v>
@@ -21713,7 +21713,7 @@
         <v>1.41300702095032</v>
       </c>
       <c r="G736" t="n">
-        <v>1.2248227596283</v>
+        <v>1.22482287883759</v>
       </c>
       <c r="H736" t="n">
         <v>1061893</v>
@@ -21858,7 +21858,7 @@
         <v>1.41960501670837</v>
       </c>
       <c r="G741" t="n">
-        <v>1.23054194450378</v>
+        <v>1.23054206371307</v>
       </c>
       <c r="H741" t="n">
         <v>544390</v>
@@ -21887,7 +21887,7 @@
         <v>1.42243301868439</v>
       </c>
       <c r="G742" t="n">
-        <v>1.23299360275269</v>
+        <v>1.23299336433411</v>
       </c>
       <c r="H742" t="n">
         <v>2200236</v>
@@ -21916,7 +21916,7 @@
         <v>1.54403305053711</v>
       </c>
       <c r="G743" t="n">
-        <v>1.33839881420135</v>
+        <v>1.33839869499207</v>
       </c>
       <c r="H743" t="n">
         <v>2798011</v>
@@ -21945,7 +21945,7 @@
         <v>1.54591798782349</v>
       </c>
       <c r="G744" t="n">
-        <v>1.34003257751465</v>
+        <v>1.34003269672394</v>
       </c>
       <c r="H744" t="n">
         <v>2398400</v>
@@ -22061,7 +22061,7 @@
         <v>1.48370397090912</v>
       </c>
       <c r="G748" t="n">
-        <v>1.28610420227051</v>
+        <v>1.2861043214798</v>
       </c>
       <c r="H748" t="n">
         <v>977564</v>
@@ -22119,7 +22119,7 @@
         <v>1.41206395626068</v>
       </c>
       <c r="G750" t="n">
-        <v>1.22400522232056</v>
+        <v>1.22400534152985</v>
       </c>
       <c r="H750" t="n">
         <v>1769729</v>
@@ -22148,7 +22148,7 @@
         <v>1.39792501926422</v>
       </c>
       <c r="G751" t="n">
-        <v>1.21174943447113</v>
+        <v>1.21174931526184</v>
       </c>
       <c r="H751" t="n">
         <v>1365628</v>
@@ -22177,7 +22177,7 @@
         <v>1.20562696456909</v>
       </c>
       <c r="G752" t="n">
-        <v>1.04506158828735</v>
+        <v>1.04506170749664</v>
       </c>
       <c r="H752" t="n">
         <v>6243157</v>
@@ -22235,7 +22235,7 @@
         <v>1.11702001094818</v>
       </c>
       <c r="G754" t="n">
-        <v>0.968255400657654</v>
+        <v>0.968255221843719</v>
       </c>
       <c r="H754" t="n">
         <v>5603729</v>
@@ -22293,7 +22293,7 @@
         <v>0.793696999549866</v>
       </c>
       <c r="G756" t="n">
-        <v>0.68799239397049</v>
+        <v>0.687992453575134</v>
       </c>
       <c r="H756" t="n">
         <v>27623553</v>
@@ -22322,7 +22322,7 @@
         <v>0.793696999549866</v>
       </c>
       <c r="G757" t="n">
-        <v>0.68799239397049</v>
+        <v>0.687992453575134</v>
       </c>
       <c r="H757" t="n">
         <v>18120413</v>
@@ -22467,7 +22467,7 @@
         <v>0.957714974880219</v>
       </c>
       <c r="G762" t="n">
-        <v>0.830166459083557</v>
+        <v>0.830166518688202</v>
       </c>
       <c r="H762" t="n">
         <v>5372597</v>
@@ -22496,7 +22496,7 @@
         <v>1.03123998641968</v>
       </c>
       <c r="G763" t="n">
-        <v>0.893899440765381</v>
+        <v>0.893899500370026</v>
       </c>
       <c r="H763" t="n">
         <v>10997713</v>
@@ -22554,7 +22554,7 @@
         <v>1.0368959903717</v>
       </c>
       <c r="G765" t="n">
-        <v>0.898802220821381</v>
+        <v>0.898802161216736</v>
       </c>
       <c r="H765" t="n">
         <v>2858913</v>
@@ -22583,7 +22583,7 @@
         <v>1.03501105308533</v>
       </c>
       <c r="G766" t="n">
-        <v>0.897168338298798</v>
+        <v>0.897168219089508</v>
       </c>
       <c r="H766" t="n">
         <v>2757978</v>
@@ -22612,7 +22612,7 @@
         <v>1.13398694992065</v>
       </c>
       <c r="G767" t="n">
-        <v>0.982962489128113</v>
+        <v>0.982962608337402</v>
       </c>
       <c r="H767" t="n">
         <v>8335044</v>
@@ -22699,7 +22699,7 @@
         <v>1.24050498008728</v>
       </c>
       <c r="G770" t="n">
-        <v>1.07529449462891</v>
+        <v>1.0752946138382</v>
       </c>
       <c r="H770" t="n">
         <v>5370354</v>
@@ -22728,7 +22728,7 @@
         <v>1.27726805210114</v>
       </c>
       <c r="G771" t="n">
-        <v>1.10716164112091</v>
+        <v>1.10716152191162</v>
       </c>
       <c r="H771" t="n">
         <v>3047066</v>
@@ -22786,7 +22786,7 @@
         <v>1.16886496543884</v>
       </c>
       <c r="G773" t="n">
-        <v>1.01319563388824</v>
+        <v>1.01319551467896</v>
       </c>
       <c r="H773" t="n">
         <v>4945592</v>
@@ -22844,7 +22844,7 @@
         <v>1.14906895160675</v>
       </c>
       <c r="G775" t="n">
-        <v>0.996036052703857</v>
+        <v>0.996035993099213</v>
       </c>
       <c r="H775" t="n">
         <v>2581766</v>
@@ -22873,7 +22873,7 @@
         <v>1.1273889541626</v>
       </c>
       <c r="G776" t="n">
-        <v>0.97724324464798</v>
+        <v>0.977243363857269</v>
       </c>
       <c r="H776" t="n">
         <v>2272017</v>
@@ -22931,7 +22931,7 @@
         <v>1.14341402053833</v>
       </c>
       <c r="G778" t="n">
-        <v>0.991134166717529</v>
+        <v>0.991134285926819</v>
       </c>
       <c r="H778" t="n">
         <v>1840754</v>
@@ -23047,7 +23047,7 @@
         <v>1.27444005012512</v>
       </c>
       <c r="G782" t="n">
-        <v>1.10470998287201</v>
+        <v>1.1047101020813</v>
       </c>
       <c r="H782" t="n">
         <v>1937220</v>
@@ -23163,7 +23163,7 @@
         <v>1.24427497386932</v>
       </c>
       <c r="G786" t="n">
-        <v>1.07856237888336</v>
+        <v>1.07856249809265</v>
       </c>
       <c r="H786" t="n">
         <v>2295183</v>
@@ -23192,7 +23192,7 @@
         <v>1.20279896259308</v>
       </c>
       <c r="G787" t="n">
-        <v>1.04261028766632</v>
+        <v>1.04261016845703</v>
       </c>
       <c r="H787" t="n">
         <v>2003813</v>
@@ -23250,7 +23250,7 @@
         <v>1.2084549665451</v>
       </c>
       <c r="G789" t="n">
-        <v>1.04751312732697</v>
+        <v>1.04751300811768</v>
       </c>
       <c r="H789" t="n">
         <v>2804151</v>
@@ -23337,7 +23337,7 @@
         <v>1.1679220199585</v>
       </c>
       <c r="G792" t="n">
-        <v>1.01237809658051</v>
+        <v>1.01237821578979</v>
       </c>
       <c r="H792" t="n">
         <v>2605504</v>
@@ -23366,7 +23366,7 @@
         <v>1.20185697078705</v>
       </c>
       <c r="G793" t="n">
-        <v>1.04179382324219</v>
+        <v>1.04179358482361</v>
       </c>
       <c r="H793" t="n">
         <v>1226658</v>
@@ -23395,7 +23395,7 @@
         <v>1.27349698543549</v>
       </c>
       <c r="G794" t="n">
-        <v>1.10389268398285</v>
+        <v>1.10389256477356</v>
       </c>
       <c r="H794" t="n">
         <v>6324232</v>
@@ -23453,7 +23453,7 @@
         <v>1.22636497020721</v>
       </c>
       <c r="G796" t="n">
-        <v>1.06303763389587</v>
+        <v>1.06303751468658</v>
       </c>
       <c r="H796" t="n">
         <v>1829164</v>
@@ -23511,7 +23511,7 @@
         <v>1.21976697444916</v>
       </c>
       <c r="G798" t="n">
-        <v>1.0573183298111</v>
+        <v>1.05731844902039</v>
       </c>
       <c r="H798" t="n">
         <v>1024822</v>
@@ -23569,7 +23569,7 @@
         <v>1.21693897247314</v>
       </c>
       <c r="G800" t="n">
-        <v>1.05486714839935</v>
+        <v>1.05486702919006</v>
       </c>
       <c r="H800" t="n">
         <v>1827954</v>
@@ -23598,7 +23598,7 @@
         <v>1.24144697189331</v>
       </c>
       <c r="G801" t="n">
-        <v>1.07611131668091</v>
+        <v>1.07611107826233</v>
       </c>
       <c r="H801" t="n">
         <v>3070628</v>
@@ -23772,7 +23772,7 @@
         <v>1.6496080160141</v>
       </c>
       <c r="G807" t="n">
-        <v>1.42991316318512</v>
+        <v>1.42991328239441</v>
       </c>
       <c r="H807" t="n">
         <v>21879908</v>
@@ -23801,7 +23801,7 @@
         <v>1.59776294231415</v>
       </c>
       <c r="G808" t="n">
-        <v>1.38497269153595</v>
+        <v>1.38497281074524</v>
       </c>
       <c r="H808" t="n">
         <v>9441741</v>
@@ -23830,7 +23830,7 @@
         <v>1.59587800502777</v>
       </c>
       <c r="G809" t="n">
-        <v>1.38333892822266</v>
+        <v>1.38333916664124</v>
       </c>
       <c r="H809" t="n">
         <v>3922021</v>
@@ -23946,7 +23946,7 @@
         <v>1.48653197288513</v>
       </c>
       <c r="G813" t="n">
-        <v>1.28855574131012</v>
+        <v>1.28855562210083</v>
       </c>
       <c r="H813" t="n">
         <v>3457635</v>
@@ -23975,7 +23975,7 @@
         <v>1.46485197544098</v>
       </c>
       <c r="G814" t="n">
-        <v>1.26976299285889</v>
+        <v>1.2697628736496</v>
       </c>
       <c r="H814" t="n">
         <v>3288010</v>
@@ -24004,7 +24004,7 @@
         <v>1.54968905448914</v>
       </c>
       <c r="G815" t="n">
-        <v>1.34330141544342</v>
+        <v>1.34330153465271</v>
       </c>
       <c r="H815" t="n">
         <v>6681049</v>
@@ -24149,7 +24149,7 @@
         <v>1.54968905448914</v>
       </c>
       <c r="G820" t="n">
-        <v>1.34330141544342</v>
+        <v>1.34330153465271</v>
       </c>
       <c r="H820" t="n">
         <v>3471111</v>
@@ -24671,7 +24671,7 @@
         <v>1.59776294231415</v>
       </c>
       <c r="G838" t="n">
-        <v>1.38497269153595</v>
+        <v>1.38497281074524</v>
       </c>
       <c r="H838" t="n">
         <v>2580843</v>
@@ -24729,7 +24729,7 @@
         <v>1.62038600444794</v>
       </c>
       <c r="G840" t="n">
-        <v>1.40458297729492</v>
+        <v>1.40458309650421</v>
       </c>
       <c r="H840" t="n">
         <v>7114566</v>
@@ -24787,7 +24787,7 @@
         <v>1.81833899021149</v>
       </c>
       <c r="G842" t="n">
-        <v>1.57617259025574</v>
+        <v>1.57617270946503</v>
       </c>
       <c r="H842" t="n">
         <v>9361902</v>
@@ -24932,7 +24932,7 @@
         <v>1.75046896934509</v>
       </c>
       <c r="G847" t="n">
-        <v>1.51734137535095</v>
+        <v>1.51734161376953</v>
       </c>
       <c r="H847" t="n">
         <v>1654984</v>
@@ -24990,7 +24990,7 @@
         <v>1.65997695922852</v>
       </c>
       <c r="G849" t="n">
-        <v>1.43890130519867</v>
+        <v>1.43890118598938</v>
       </c>
       <c r="H849" t="n">
         <v>1890007</v>
@@ -25048,7 +25048,7 @@
         <v>1.61850094795227</v>
       </c>
       <c r="G851" t="n">
-        <v>1.40294897556305</v>
+        <v>1.40294921398163</v>
       </c>
       <c r="H851" t="n">
         <v>2185554</v>
@@ -25077,7 +25077,7 @@
         <v>1.56665599346161</v>
       </c>
       <c r="G852" t="n">
-        <v>1.35800886154175</v>
+        <v>1.35800874233246</v>
       </c>
       <c r="H852" t="n">
         <v>2009882</v>
@@ -25106,7 +25106,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G853" t="n">
-        <v>1.3531060218811</v>
+        <v>1.35310614109039</v>
       </c>
       <c r="H853" t="n">
         <v>1248727</v>
@@ -25251,7 +25251,7 @@
         <v>1.52329504489899</v>
       </c>
       <c r="G858" t="n">
-        <v>1.32042264938354</v>
+        <v>1.32042276859283</v>
       </c>
       <c r="H858" t="n">
         <v>980195</v>
@@ -25309,7 +25309,7 @@
         <v>1.49218797683716</v>
       </c>
       <c r="G860" t="n">
-        <v>1.29345834255219</v>
+        <v>1.29345846176147</v>
       </c>
       <c r="H860" t="n">
         <v>857950</v>
@@ -25338,7 +25338,7 @@
         <v>1.48558902740479</v>
       </c>
       <c r="G861" t="n">
-        <v>1.28773832321167</v>
+        <v>1.28773844242096</v>
       </c>
       <c r="H861" t="n">
         <v>1421219</v>
@@ -25425,7 +25425,7 @@
         <v>1.47899103164673</v>
       </c>
       <c r="G864" t="n">
-        <v>1.28201901912689</v>
+        <v>1.2820188999176</v>
       </c>
       <c r="H864" t="n">
         <v>991058</v>
@@ -25483,7 +25483,7 @@
         <v>1.45825302600861</v>
       </c>
       <c r="G866" t="n">
-        <v>1.26404297351837</v>
+        <v>1.26404309272766</v>
       </c>
       <c r="H866" t="n">
         <v>885219</v>
@@ -25512,7 +25512,7 @@
         <v>1.45259702205658</v>
       </c>
       <c r="G867" t="n">
-        <v>1.25914001464844</v>
+        <v>1.25914013385773</v>
       </c>
       <c r="H867" t="n">
         <v>933015</v>
@@ -25541,7 +25541,7 @@
         <v>1.41112101078033</v>
       </c>
       <c r="G868" t="n">
-        <v>1.2231879234314</v>
+        <v>1.22318804264069</v>
       </c>
       <c r="H868" t="n">
         <v>1971713</v>
@@ -25599,7 +25599,7 @@
         <v>1.48558902740479</v>
       </c>
       <c r="G870" t="n">
-        <v>1.28773832321167</v>
+        <v>1.28773844242096</v>
       </c>
       <c r="H870" t="n">
         <v>1716632</v>
@@ -25715,7 +25715,7 @@
         <v>1.52235198020935</v>
       </c>
       <c r="G874" t="n">
-        <v>1.31960511207581</v>
+        <v>1.3196052312851</v>
       </c>
       <c r="H874" t="n">
         <v>1034087</v>
@@ -25744,7 +25744,7 @@
         <v>1.51952397823334</v>
       </c>
       <c r="G875" t="n">
-        <v>1.31715381145477</v>
+        <v>1.31715369224548</v>
       </c>
       <c r="H875" t="n">
         <v>1088179</v>
@@ -25860,7 +25860,7 @@
         <v>1.43185901641846</v>
       </c>
       <c r="G879" t="n">
-        <v>1.24116408824921</v>
+        <v>1.24116396903992</v>
       </c>
       <c r="H879" t="n">
         <v>1542117</v>
@@ -25918,7 +25918,7 @@
         <v>1.34513700008392</v>
       </c>
       <c r="G881" t="n">
-        <v>1.1659916639328</v>
+        <v>1.16599154472351</v>
       </c>
       <c r="H881" t="n">
         <v>2698790</v>
@@ -25947,7 +25947,7 @@
         <v>1.53272104263306</v>
       </c>
       <c r="G882" t="n">
-        <v>1.32859325408936</v>
+        <v>1.32859337329865</v>
       </c>
       <c r="H882" t="n">
         <v>8902814</v>
@@ -25976,7 +25976,7 @@
         <v>1.49313104152679</v>
       </c>
       <c r="G883" t="n">
-        <v>1.29427576065063</v>
+        <v>1.29427587985992</v>
       </c>
       <c r="H883" t="n">
         <v>6178388</v>
@@ -26121,7 +26121,7 @@
         <v>1.42337596416473</v>
       </c>
       <c r="G888" t="n">
-        <v>1.23381090164185</v>
+        <v>1.23381078243256</v>
       </c>
       <c r="H888" t="n">
         <v>1036182</v>
@@ -26208,7 +26208,7 @@
         <v>1.51009798049927</v>
       </c>
       <c r="G891" t="n">
-        <v>1.30898308753967</v>
+        <v>1.30898320674896</v>
       </c>
       <c r="H891" t="n">
         <v>3259028</v>
@@ -26266,7 +26266,7 @@
         <v>1.6722309589386</v>
       </c>
       <c r="G893" t="n">
-        <v>1.4495233297348</v>
+        <v>1.44952321052551</v>
       </c>
       <c r="H893" t="n">
         <v>4507642</v>
@@ -26353,7 +26353,7 @@
         <v>1.69673895835876</v>
       </c>
       <c r="G896" t="n">
-        <v>1.47076725959778</v>
+        <v>1.47076714038849</v>
       </c>
       <c r="H896" t="n">
         <v>1392355</v>
@@ -26382,7 +26382,7 @@
         <v>1.74292802810669</v>
       </c>
       <c r="G897" t="n">
-        <v>1.51080501079559</v>
+        <v>1.5108048915863</v>
       </c>
       <c r="H897" t="n">
         <v>2711993</v>
@@ -26411,7 +26411,7 @@
         <v>1.76460897922516</v>
       </c>
       <c r="G898" t="n">
-        <v>1.52959835529327</v>
+        <v>1.52959823608398</v>
       </c>
       <c r="H898" t="n">
         <v>2034202</v>
@@ -26440,7 +26440,7 @@
         <v>1.73633003234863</v>
       </c>
       <c r="G899" t="n">
-        <v>1.50508558750153</v>
+        <v>1.50508546829224</v>
       </c>
       <c r="H899" t="n">
         <v>1758659</v>
@@ -26469,7 +26469,7 @@
         <v>1.74764204025269</v>
       </c>
       <c r="G900" t="n">
-        <v>1.51489114761353</v>
+        <v>1.51489126682281</v>
       </c>
       <c r="H900" t="n">
         <v>1809511</v>
@@ -26643,7 +26643,7 @@
         <v>1.57231199741364</v>
       </c>
       <c r="G906" t="n">
-        <v>1.36291146278381</v>
+        <v>1.3629115819931</v>
       </c>
       <c r="H906" t="n">
         <v>1413691</v>
@@ -26672,7 +26672,7 @@
         <v>1.56948399543762</v>
       </c>
       <c r="G907" t="n">
-        <v>1.36046004295349</v>
+        <v>1.36046016216278</v>
       </c>
       <c r="H907" t="n">
         <v>1182753</v>
@@ -26759,7 +26759,7 @@
         <v>1.52140998840332</v>
       </c>
       <c r="G910" t="n">
-        <v>1.31878864765167</v>
+        <v>1.31878852844238</v>
       </c>
       <c r="H910" t="n">
         <v>1254389</v>
@@ -26788,7 +26788,7 @@
         <v>1.50255703926086</v>
       </c>
       <c r="G911" t="n">
-        <v>1.30244660377502</v>
+        <v>1.30244648456573</v>
       </c>
       <c r="H911" t="n">
         <v>1396560</v>
@@ -26817,7 +26817,7 @@
         <v>1.50255703926086</v>
       </c>
       <c r="G912" t="n">
-        <v>1.30244660377502</v>
+        <v>1.30244648456573</v>
       </c>
       <c r="H912" t="n">
         <v>983007</v>
@@ -26846,7 +26846,7 @@
         <v>1.49878597259521</v>
       </c>
       <c r="G913" t="n">
-        <v>1.29917776584625</v>
+        <v>1.29917788505554</v>
       </c>
       <c r="H913" t="n">
         <v>1320093</v>
@@ -26875,7 +26875,7 @@
         <v>1.46390902996063</v>
       </c>
       <c r="G914" t="n">
-        <v>1.26894569396973</v>
+        <v>1.26894557476044</v>
       </c>
       <c r="H914" t="n">
         <v>1472065</v>
@@ -26962,7 +26962,7 @@
         <v>1.50444197654724</v>
       </c>
       <c r="G917" t="n">
-        <v>1.30408036708832</v>
+        <v>1.30408048629761</v>
       </c>
       <c r="H917" t="n">
         <v>411599</v>
@@ -27020,7 +27020,7 @@
         <v>1.41112101078033</v>
       </c>
       <c r="G919" t="n">
-        <v>1.2231879234314</v>
+        <v>1.22318804264069</v>
       </c>
       <c r="H919" t="n">
         <v>2938513</v>
@@ -27049,7 +27049,7 @@
         <v>1.42808902263641</v>
       </c>
       <c r="G920" t="n">
-        <v>1.23789608478546</v>
+        <v>1.23789620399475</v>
       </c>
       <c r="H920" t="n">
         <v>1268130</v>
@@ -27107,7 +27107,7 @@
         <v>1.40169501304626</v>
       </c>
       <c r="G922" t="n">
-        <v>1.21501731872559</v>
+        <v>1.2150171995163</v>
       </c>
       <c r="H922" t="n">
         <v>501877</v>
@@ -27165,7 +27165,7 @@
         <v>1.50255703926086</v>
       </c>
       <c r="G924" t="n">
-        <v>1.30244660377502</v>
+        <v>1.30244648456573</v>
       </c>
       <c r="H924" t="n">
         <v>1334809</v>
@@ -27310,7 +27310,7 @@
         <v>1.54686105251312</v>
       </c>
       <c r="G929" t="n">
-        <v>1.34085011482239</v>
+        <v>1.34085023403168</v>
       </c>
       <c r="H929" t="n">
         <v>895670</v>
@@ -27339,7 +27339,7 @@
         <v>1.56288504600525</v>
       </c>
       <c r="G930" t="n">
-        <v>1.35474014282227</v>
+        <v>1.35474002361298</v>
       </c>
       <c r="H930" t="n">
         <v>2638419</v>
@@ -27426,7 +27426,7 @@
         <v>1.55722999572754</v>
       </c>
       <c r="G933" t="n">
-        <v>1.34983813762665</v>
+        <v>1.34983801841736</v>
       </c>
       <c r="H933" t="n">
         <v>1427843</v>
@@ -27484,7 +27484,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G935" t="n">
-        <v>1.3531060218811</v>
+        <v>1.35310614109039</v>
       </c>
       <c r="H935" t="n">
         <v>1110453</v>
@@ -27513,7 +27513,7 @@
         <v>1.57231199741364</v>
       </c>
       <c r="G936" t="n">
-        <v>1.36291146278381</v>
+        <v>1.3629115819931</v>
       </c>
       <c r="H936" t="n">
         <v>1607200</v>
@@ -27571,7 +27571,7 @@
         <v>1.6722309589386</v>
       </c>
       <c r="G938" t="n">
-        <v>1.4495233297348</v>
+        <v>1.44952321052551</v>
       </c>
       <c r="H938" t="n">
         <v>4648127</v>
@@ -27600,7 +27600,7 @@
         <v>1.67977201938629</v>
       </c>
       <c r="G939" t="n">
-        <v>1.45606005191803</v>
+        <v>1.45606017112732</v>
       </c>
       <c r="H939" t="n">
         <v>2515803</v>
@@ -27629,7 +27629,7 @@
         <v>1.68919801712036</v>
       </c>
       <c r="G940" t="n">
-        <v>1.46423065662384</v>
+        <v>1.46423077583313</v>
       </c>
       <c r="H940" t="n">
         <v>1946774</v>
@@ -27658,7 +27658,7 @@
         <v>1.69391095638275</v>
       </c>
       <c r="G941" t="n">
-        <v>1.46831595897675</v>
+        <v>1.46831583976746</v>
       </c>
       <c r="H941" t="n">
         <v>1286199</v>
@@ -27716,7 +27716,7 @@
         <v>1.63358294963837</v>
       </c>
       <c r="G943" t="n">
-        <v>1.41602230072021</v>
+        <v>1.41602253913879</v>
       </c>
       <c r="H943" t="n">
         <v>1896598</v>
@@ -27803,7 +27803,7 @@
         <v>1.74104297161102</v>
       </c>
       <c r="G946" t="n">
-        <v>1.50917077064514</v>
+        <v>1.50917088985443</v>
       </c>
       <c r="H946" t="n">
         <v>11566722</v>
@@ -27948,7 +27948,7 @@
         <v>1.5892790555954</v>
       </c>
       <c r="G951" t="n">
-        <v>1.37761902809143</v>
+        <v>1.37761890888214</v>
       </c>
       <c r="H951" t="n">
         <v>938953</v>
@@ -28035,7 +28035,7 @@
         <v>1.58833599090576</v>
       </c>
       <c r="G954" t="n">
-        <v>1.3768013715744</v>
+        <v>1.37680149078369</v>
       </c>
       <c r="H954" t="n">
         <v>2373698</v>
@@ -28064,7 +28064,7 @@
         <v>1.52329504489899</v>
       </c>
       <c r="G955" t="n">
-        <v>1.32042264938354</v>
+        <v>1.32042276859283</v>
       </c>
       <c r="H955" t="n">
         <v>3012476</v>
@@ -28093,7 +28093,7 @@
         <v>1.49218797683716</v>
       </c>
       <c r="G956" t="n">
-        <v>1.29345834255219</v>
+        <v>1.29345846176147</v>
       </c>
       <c r="H956" t="n">
         <v>2537869</v>
@@ -28325,7 +28325,7 @@
         <v>1.54497504234314</v>
       </c>
       <c r="G964" t="n">
-        <v>1.3392151594162</v>
+        <v>1.33921539783478</v>
       </c>
       <c r="H964" t="n">
         <v>1070154</v>
@@ -28354,7 +28354,7 @@
         <v>1.63075494766235</v>
       </c>
       <c r="G965" t="n">
-        <v>1.41357088088989</v>
+        <v>1.41357100009918</v>
       </c>
       <c r="H965" t="n">
         <v>6626061</v>
@@ -28499,7 +28499,7 @@
         <v>1.66091895103455</v>
       </c>
       <c r="G970" t="n">
-        <v>1.4397177696228</v>
+        <v>1.43971788883209</v>
       </c>
       <c r="H970" t="n">
         <v>4372365</v>
@@ -28528,7 +28528,7 @@
         <v>1.65337800979614</v>
       </c>
       <c r="G971" t="n">
-        <v>1.43318116664886</v>
+        <v>1.43318104743958</v>
       </c>
       <c r="H971" t="n">
         <v>2747197</v>
@@ -28557,7 +28557,7 @@
         <v>1.66186201572418</v>
       </c>
       <c r="G972" t="n">
-        <v>1.44053518772125</v>
+        <v>1.44053530693054</v>
       </c>
       <c r="H972" t="n">
         <v>1104430</v>
@@ -28673,7 +28673,7 @@
         <v>1.68448495864868</v>
       </c>
       <c r="G976" t="n">
-        <v>1.46014535427094</v>
+        <v>1.46014523506165</v>
       </c>
       <c r="H976" t="n">
         <v>2077611</v>
@@ -28731,7 +28731,7 @@
         <v>1.73821496963501</v>
       </c>
       <c r="G978" t="n">
-        <v>1.50671947002411</v>
+        <v>1.5067195892334</v>
       </c>
       <c r="H978" t="n">
         <v>2839380</v>
@@ -28760,7 +28760,7 @@
         <v>1.74292802810669</v>
       </c>
       <c r="G979" t="n">
-        <v>1.51080501079559</v>
+        <v>1.5108048915863</v>
       </c>
       <c r="H979" t="n">
         <v>4869838</v>
@@ -28789,7 +28789,7 @@
         <v>1.73255896568298</v>
       </c>
       <c r="G980" t="n">
-        <v>1.50181698799133</v>
+        <v>1.50181686878204</v>
       </c>
       <c r="H980" t="n">
         <v>2350191</v>
@@ -28818,7 +28818,7 @@
         <v>1.80325698852539</v>
       </c>
       <c r="G981" t="n">
-        <v>1.56309914588928</v>
+        <v>1.56309926509857</v>
       </c>
       <c r="H981" t="n">
         <v>5793909</v>
@@ -28905,7 +28905,7 @@
         <v>1.85698699951172</v>
       </c>
       <c r="G984" t="n">
-        <v>1.60967361927032</v>
+        <v>1.60967350006104</v>
       </c>
       <c r="H984" t="n">
         <v>5218101</v>
@@ -28992,7 +28992,7 @@
         <v>1.80325698852539</v>
       </c>
       <c r="G987" t="n">
-        <v>1.56309914588928</v>
+        <v>1.56309926509857</v>
       </c>
       <c r="H987" t="n">
         <v>2672514</v>
@@ -29021,7 +29021,7 @@
         <v>1.78817498683929</v>
       </c>
       <c r="G988" t="n">
-        <v>1.55002582073212</v>
+        <v>1.55002593994141</v>
       </c>
       <c r="H988" t="n">
         <v>1470714</v>
@@ -29079,7 +29079,7 @@
         <v>1.74010002613068</v>
       </c>
       <c r="G990" t="n">
-        <v>1.50835347175598</v>
+        <v>1.50835335254669</v>
       </c>
       <c r="H990" t="n">
         <v>2101310</v>
@@ -29108,7 +29108,7 @@
         <v>1.75895297527313</v>
       </c>
       <c r="G991" t="n">
-        <v>1.52469563484192</v>
+        <v>1.52469551563263</v>
       </c>
       <c r="H991" t="n">
         <v>1454756</v>
@@ -29137,7 +29137,7 @@
         <v>1.76743698120117</v>
       </c>
       <c r="G992" t="n">
-        <v>1.53204965591431</v>
+        <v>1.5320497751236</v>
       </c>
       <c r="H992" t="n">
         <v>1331771</v>
@@ -29166,7 +29166,7 @@
         <v>1.73821496963501</v>
       </c>
       <c r="G993" t="n">
-        <v>1.50671947002411</v>
+        <v>1.5067195892334</v>
       </c>
       <c r="H993" t="n">
         <v>1136829</v>
@@ -29195,7 +29195,7 @@
         <v>1.7683789730072</v>
       </c>
       <c r="G994" t="n">
-        <v>1.53286635875702</v>
+        <v>1.53286623954773</v>
       </c>
       <c r="H994" t="n">
         <v>2026243</v>
@@ -29224,7 +29224,7 @@
         <v>1.79100298881531</v>
       </c>
       <c r="G995" t="n">
-        <v>1.55247712135315</v>
+        <v>1.55247735977173</v>
       </c>
       <c r="H995" t="n">
         <v>1985110</v>
@@ -29282,7 +29282,7 @@
         <v>1.96444702148438</v>
       </c>
       <c r="G997" t="n">
-        <v>1.70282185077667</v>
+        <v>1.70282196998596</v>
       </c>
       <c r="H997" t="n">
         <v>10415714</v>
@@ -29340,7 +29340,7 @@
         <v>1.93993902206421</v>
       </c>
       <c r="G999" t="n">
-        <v>1.6815779209137</v>
+        <v>1.68157780170441</v>
       </c>
       <c r="H999" t="n">
         <v>4188383</v>
@@ -29369,7 +29369,7 @@
         <v>1.95124995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.69138264656067</v>
+        <v>1.69138252735138</v>
       </c>
       <c r="H1000" t="n">
         <v>2213738</v>
@@ -29485,7 +29485,7 @@
         <v>1.9927259683609</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.72733473777771</v>
+        <v>1.72733461856842</v>
       </c>
       <c r="H1004" t="n">
         <v>3842765</v>
@@ -29514,7 +29514,7 @@
         <v>1.97387301921844</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.71099269390106</v>
+        <v>1.71099257469177</v>
       </c>
       <c r="H1005" t="n">
         <v>2579441</v>
@@ -29601,7 +29601,7 @@
         <v>1.81551098823547</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.57372117042542</v>
+        <v>1.5737212896347</v>
       </c>
       <c r="H1008" t="n">
         <v>3709348</v>
@@ -29775,7 +29775,7 @@
         <v>1.90411901473999</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.65052843093872</v>
+        <v>1.65052855014801</v>
       </c>
       <c r="H1014" t="n">
         <v>1777965</v>
@@ -29833,7 +29833,7 @@
         <v>1.8965779542923</v>
       </c>
       <c r="G1016" t="n">
-        <v>1.6439915895462</v>
+        <v>1.64399170875549</v>
       </c>
       <c r="H1016" t="n">
         <v>1384256</v>
@@ -29891,7 +29891,7 @@
         <v>1.82305204868317</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.58025801181793</v>
+        <v>1.58025813102722</v>
       </c>
       <c r="H1018" t="n">
         <v>1745371</v>
@@ -29978,7 +29978,7 @@
         <v>1.85133099555969</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.60477077960968</v>
+        <v>1.60477066040039</v>
       </c>
       <c r="H1021" t="n">
         <v>1556641</v>
@@ -30007,7 +30007,7 @@
         <v>1.83247804641724</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.58842873573303</v>
+        <v>1.58842861652374</v>
       </c>
       <c r="H1022" t="n">
         <v>1149492</v>
@@ -30181,7 +30181,7 @@
         <v>1.80042898654938</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.56064784526825</v>
+        <v>1.56064808368683</v>
       </c>
       <c r="H1028" t="n">
         <v>1277340</v>
@@ -30268,7 +30268,7 @@
         <v>1.8060849905014</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.56555068492889</v>
+        <v>1.5655505657196</v>
       </c>
       <c r="H1031" t="n">
         <v>1904804</v>
@@ -30297,7 +30297,7 @@
         <v>1.78911697864532</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.55084252357483</v>
+        <v>1.55084228515625</v>
       </c>
       <c r="H1032" t="n">
         <v>1177621</v>
@@ -30326,7 +30326,7 @@
         <v>1.74387097358704</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.51162230968475</v>
+        <v>1.51162219047546</v>
       </c>
       <c r="H1033" t="n">
         <v>1444376</v>
@@ -30384,7 +30384,7 @@
         <v>1.77969098091125</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.54267191886902</v>
+        <v>1.54267168045044</v>
       </c>
       <c r="H1035" t="n">
         <v>2139195</v>
@@ -30500,7 +30500,7 @@
         <v>1.67977201938629</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.45606005191803</v>
+        <v>1.45606017112732</v>
       </c>
       <c r="H1039" t="n">
         <v>3336366</v>
@@ -30558,7 +30558,7 @@
         <v>1.6722309589386</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.4495233297348</v>
+        <v>1.44952321052551</v>
       </c>
       <c r="H1041" t="n">
         <v>1663936</v>
@@ -30616,7 +30616,7 @@
         <v>1.65620601177216</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.43563258647919</v>
+        <v>1.4356324672699</v>
       </c>
       <c r="H1043" t="n">
         <v>1409934</v>
@@ -30703,7 +30703,7 @@
         <v>1.72878897190094</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.4985488653183</v>
+        <v>1.49854898452759</v>
       </c>
       <c r="H1046" t="n">
         <v>2143556</v>
@@ -30761,7 +30761,7 @@
         <v>1.74669897556305</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.51407372951508</v>
+        <v>1.51407361030579</v>
       </c>
       <c r="H1048" t="n">
         <v>3015458</v>
@@ -30848,7 +30848,7 @@
         <v>1.67317295074463</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.45033967494965</v>
+        <v>1.45033979415894</v>
       </c>
       <c r="H1051" t="n">
         <v>2093950</v>
@@ -30993,7 +30993,7 @@
         <v>1.42337596416473</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.23381090164185</v>
+        <v>1.23381078243256</v>
       </c>
       <c r="H1056" t="n">
         <v>3946679</v>
@@ -31051,7 +31051,7 @@
         <v>1.33194005489349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.15455234050751</v>
+        <v>1.1545524597168</v>
       </c>
       <c r="H1058" t="n">
         <v>4472695</v>
@@ -31109,7 +31109,7 @@
         <v>1.28198099136353</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.11124694347382</v>
+        <v>1.11124682426453</v>
       </c>
       <c r="H1060" t="n">
         <v>9609855</v>
@@ -31138,7 +31138,7 @@
         <v>1.15943801403046</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.00502407550812</v>
+        <v>1.00502395629883</v>
       </c>
       <c r="H1061" t="n">
         <v>4747444</v>
@@ -31167,7 +31167,7 @@
         <v>1.05292105674744</v>
       </c>
       <c r="G1062" t="n">
-        <v>0.912693023681641</v>
+        <v>0.912693083286285</v>
       </c>
       <c r="H1062" t="n">
         <v>4266726</v>
@@ -31196,7 +31196,7 @@
         <v>0.876648008823395</v>
       </c>
       <c r="G1063" t="n">
-        <v>0.759896099567413</v>
+        <v>0.759896039962769</v>
       </c>
       <c r="H1063" t="n">
         <v>5592929</v>
@@ -31370,7 +31370,7 @@
         <v>0.676338970661163</v>
       </c>
       <c r="G1069" t="n">
-        <v>0.586264133453369</v>
+        <v>0.586264193058014</v>
       </c>
       <c r="H1069" t="n">
         <v>3086776</v>
@@ -31428,7 +31428,7 @@
         <v>0.818204998970032</v>
       </c>
       <c r="G1071" t="n">
-        <v>0.7092365026474</v>
+        <v>0.709236443042755</v>
       </c>
       <c r="H1071" t="n">
         <v>3963307</v>
@@ -31457,7 +31457,7 @@
         <v>0.791810989379883</v>
       </c>
       <c r="G1072" t="n">
-        <v>0.686357617378235</v>
+        <v>0.68635767698288</v>
       </c>
       <c r="H1072" t="n">
         <v>4856984</v>
@@ -31486,7 +31486,7 @@
         <v>0.719228982925415</v>
       </c>
       <c r="G1073" t="n">
-        <v>0.623442053794861</v>
+        <v>0.623442113399506</v>
       </c>
       <c r="H1073" t="n">
         <v>2647950</v>
@@ -31515,7 +31515,7 @@
         <v>0.77013099193573</v>
       </c>
       <c r="G1074" t="n">
-        <v>0.667564988136292</v>
+        <v>0.667564928531647</v>
       </c>
       <c r="H1074" t="n">
         <v>2035579</v>
@@ -31660,7 +31660,7 @@
         <v>0.744207978248596</v>
       </c>
       <c r="G1079" t="n">
-        <v>0.645094335079193</v>
+        <v>0.645094454288483</v>
       </c>
       <c r="H1079" t="n">
         <v>1189206</v>
@@ -31718,7 +31718,7 @@
         <v>0.707916975021362</v>
       </c>
       <c r="G1081" t="n">
-        <v>0.613636612892151</v>
+        <v>0.613636553287506</v>
       </c>
       <c r="H1081" t="n">
         <v>1526138</v>
@@ -31834,7 +31834,7 @@
         <v>0.745621979236603</v>
       </c>
       <c r="G1085" t="n">
-        <v>0.646320044994354</v>
+        <v>0.646320104598999</v>
       </c>
       <c r="H1085" t="n">
         <v>1814614</v>
@@ -31863,7 +31863,7 @@
         <v>0.729597985744476</v>
       </c>
       <c r="G1086" t="n">
-        <v>0.632430076599121</v>
+        <v>0.632430136203766</v>
       </c>
       <c r="H1086" t="n">
         <v>3374910</v>
@@ -31950,7 +31950,7 @@
         <v>0.720170974731445</v>
       </c>
       <c r="G1089" t="n">
-        <v>0.624258577823639</v>
+        <v>0.624258637428284</v>
       </c>
       <c r="H1089" t="n">
         <v>1612111</v>
@@ -32008,7 +32008,7 @@
         <v>0.722527980804443</v>
       </c>
       <c r="G1091" t="n">
-        <v>0.626301646232605</v>
+        <v>0.62630170583725</v>
       </c>
       <c r="H1091" t="n">
         <v>1311531</v>
@@ -32095,7 +32095,7 @@
         <v>0.688592970371246</v>
       </c>
       <c r="G1094" t="n">
-        <v>0.596886098384857</v>
+        <v>0.596886157989502</v>
       </c>
       <c r="H1094" t="n">
         <v>1078903</v>
@@ -32269,7 +32269,7 @@
         <v>0.72488397359848</v>
       </c>
       <c r="G1100" t="n">
-        <v>0.628343939781189</v>
+        <v>0.628343999385834</v>
       </c>
       <c r="H1100" t="n">
         <v>1666272</v>
@@ -32298,7 +32298,7 @@
         <v>0.72394198179245</v>
       </c>
       <c r="G1101" t="n">
-        <v>0.627527415752411</v>
+        <v>0.627527356147766</v>
       </c>
       <c r="H1101" t="n">
         <v>1565172</v>
@@ -32385,7 +32385,7 @@
         <v>0.73242598772049</v>
       </c>
       <c r="G1104" t="n">
-        <v>0.634881496429443</v>
+        <v>0.634881436824799</v>
       </c>
       <c r="H1104" t="n">
         <v>707656</v>
@@ -32414,7 +32414,7 @@
         <v>0.754105985164642</v>
       </c>
       <c r="G1105" t="n">
-        <v>0.653674125671387</v>
+        <v>0.653674244880676</v>
       </c>
       <c r="H1105" t="n">
         <v>2364730</v>
@@ -32443,7 +32443,7 @@
         <v>0.733838975429535</v>
       </c>
       <c r="G1106" t="n">
-        <v>0.636106252670288</v>
+        <v>0.636106312274933</v>
       </c>
       <c r="H1106" t="n">
         <v>2009008</v>
@@ -32501,7 +32501,7 @@
         <v>0.688121974468231</v>
       </c>
       <c r="G1108" t="n">
-        <v>0.596477925777435</v>
+        <v>0.596477866172791</v>
       </c>
       <c r="H1108" t="n">
         <v>1462577</v>
@@ -32617,7 +32617,7 @@
         <v>0.648531019687653</v>
       </c>
       <c r="G1112" t="n">
-        <v>0.562159657478333</v>
+        <v>0.562159597873688</v>
       </c>
       <c r="H1112" t="n">
         <v>4709144</v>
@@ -32646,7 +32646,7 @@
         <v>0.656544029712677</v>
       </c>
       <c r="G1113" t="n">
-        <v>0.569105505943298</v>
+        <v>0.569105565547943</v>
       </c>
       <c r="H1113" t="n">
         <v>2932271</v>
@@ -32704,7 +32704,7 @@
         <v>0.679166972637177</v>
       </c>
       <c r="G1115" t="n">
-        <v>0.588715493679047</v>
+        <v>0.588715553283691</v>
       </c>
       <c r="H1115" t="n">
         <v>3872661</v>
@@ -32733,7 +32733,7 @@
         <v>0.711687982082367</v>
       </c>
       <c r="G1116" t="n">
-        <v>0.616905450820923</v>
+        <v>0.616905391216278</v>
       </c>
       <c r="H1116" t="n">
         <v>6026748</v>
@@ -32791,7 +32791,7 @@
         <v>0.890788018703461</v>
       </c>
       <c r="G1118" t="n">
-        <v>0.772152900695801</v>
+        <v>0.772152841091156</v>
       </c>
       <c r="H1118" t="n">
         <v>13034771</v>
@@ -32849,7 +32849,7 @@
         <v>0.867222011089325</v>
       </c>
       <c r="G1120" t="n">
-        <v>0.751725375652313</v>
+        <v>0.751725435256958</v>
       </c>
       <c r="H1120" t="n">
         <v>4442703</v>
@@ -32878,7 +32878,7 @@
         <v>0.934149026870728</v>
       </c>
       <c r="G1121" t="n">
-        <v>0.809738993644714</v>
+        <v>0.809739112854004</v>
       </c>
       <c r="H1121" t="n">
         <v>8340203</v>
@@ -32965,7 +32965,7 @@
         <v>1.02746999263763</v>
       </c>
       <c r="G1124" t="n">
-        <v>0.890631556510925</v>
+        <v>0.890631496906281</v>
       </c>
       <c r="H1124" t="n">
         <v>6637938</v>
@@ -33052,7 +33052,7 @@
         <v>1.09345400333405</v>
       </c>
       <c r="G1127" t="n">
-        <v>0.947827875614166</v>
+        <v>0.947827816009521</v>
       </c>
       <c r="H1127" t="n">
         <v>5730778</v>
@@ -33139,7 +33139,7 @@
         <v>1.0444370508194</v>
       </c>
       <c r="G1130" t="n">
-        <v>0.905338943004608</v>
+        <v>0.905338883399963</v>
       </c>
       <c r="H1130" t="n">
         <v>3458290</v>
@@ -33168,7 +33168,7 @@
         <v>1.05857694149017</v>
       </c>
       <c r="G1131" t="n">
-        <v>0.917595624923706</v>
+        <v>0.917595744132996</v>
       </c>
       <c r="H1131" t="n">
         <v>3666073</v>
@@ -33197,7 +33197,7 @@
         <v>1.04066705703735</v>
       </c>
       <c r="G1132" t="n">
-        <v>0.902071058750153</v>
+        <v>0.902071118354797</v>
       </c>
       <c r="H1132" t="n">
         <v>2854939</v>
@@ -33226,7 +33226,7 @@
         <v>1.04066705703735</v>
       </c>
       <c r="G1133" t="n">
-        <v>0.902071058750153</v>
+        <v>0.902071118354797</v>
       </c>
       <c r="H1133" t="n">
         <v>2068797</v>
@@ -33255,7 +33255,7 @@
         <v>1.00673198699951</v>
       </c>
       <c r="G1134" t="n">
-        <v>0.87265545129776</v>
+        <v>0.872655510902405</v>
       </c>
       <c r="H1134" t="n">
         <v>2532879</v>
@@ -33284,7 +33284,7 @@
         <v>1.00861704349518</v>
       </c>
       <c r="G1135" t="n">
-        <v>0.874289453029633</v>
+        <v>0.874289393424988</v>
       </c>
       <c r="H1135" t="n">
         <v>1489806</v>
@@ -33371,7 +33371,7 @@
         <v>0.929436028003693</v>
       </c>
       <c r="G1138" t="n">
-        <v>0.805653750896454</v>
+        <v>0.805653691291809</v>
       </c>
       <c r="H1138" t="n">
         <v>3252596</v>
@@ -33458,7 +33458,7 @@
         <v>0.909641027450562</v>
       </c>
       <c r="G1141" t="n">
-        <v>0.788495004177094</v>
+        <v>0.788495123386383</v>
       </c>
       <c r="H1141" t="n">
         <v>1525939</v>
@@ -33574,7 +33574,7 @@
         <v>0.904927015304565</v>
       </c>
       <c r="G1145" t="n">
-        <v>0.784408867359161</v>
+        <v>0.784408807754517</v>
       </c>
       <c r="H1145" t="n">
         <v>1673440</v>
@@ -33806,7 +33806,7 @@
         <v>0.965255975723267</v>
       </c>
       <c r="G1153" t="n">
-        <v>0.836703181266785</v>
+        <v>0.836703240871429</v>
       </c>
       <c r="H1153" t="n">
         <v>2650102</v>
@@ -33835,7 +33835,7 @@
         <v>0.953001976013184</v>
       </c>
       <c r="G1154" t="n">
-        <v>0.826081156730652</v>
+        <v>0.826081216335297</v>
       </c>
       <c r="H1154" t="n">
         <v>1623548</v>
@@ -33864,7 +33864,7 @@
         <v>0.957714974880219</v>
       </c>
       <c r="G1155" t="n">
-        <v>0.830166459083557</v>
+        <v>0.830166518688202</v>
       </c>
       <c r="H1155" t="n">
         <v>2005421</v>
@@ -33893,7 +33893,7 @@
         <v>0.96808397769928</v>
       </c>
       <c r="G1156" t="n">
-        <v>0.839154541492462</v>
+        <v>0.839154601097107</v>
       </c>
       <c r="H1156" t="n">
         <v>7398745</v>
@@ -33922,7 +33922,7 @@
         <v>0.943575024604797</v>
       </c>
       <c r="G1157" t="n">
-        <v>0.81790965795517</v>
+        <v>0.817909717559814</v>
       </c>
       <c r="H1157" t="n">
         <v>2696114</v>
@@ -34067,7 +34067,7 @@
         <v>0.891259014606476</v>
       </c>
       <c r="G1162" t="n">
-        <v>0.772561073303223</v>
+        <v>0.772561192512512</v>
       </c>
       <c r="H1162" t="n">
         <v>1386789</v>
@@ -34154,7 +34154,7 @@
         <v>0.875234007835388</v>
       </c>
       <c r="G1165" t="n">
-        <v>0.758670330047607</v>
+        <v>0.758670389652252</v>
       </c>
       <c r="H1165" t="n">
         <v>1306049</v>
@@ -34183,7 +34183,7 @@
         <v>0.887960016727448</v>
       </c>
       <c r="G1166" t="n">
-        <v>0.769701540470123</v>
+        <v>0.769701600074768</v>
       </c>
       <c r="H1166" t="n">
         <v>1490631</v>
@@ -34357,7 +34357,7 @@
         <v>0.91388201713562</v>
       </c>
       <c r="G1172" t="n">
-        <v>0.79217118024826</v>
+        <v>0.792171239852905</v>
       </c>
       <c r="H1172" t="n">
         <v>2307595</v>
@@ -34415,7 +34415,7 @@
         <v>0.887960016727448</v>
       </c>
       <c r="G1174" t="n">
-        <v>0.769701540470123</v>
+        <v>0.769701600074768</v>
       </c>
       <c r="H1174" t="n">
         <v>2034991</v>
@@ -34473,7 +34473,7 @@
         <v>0.870050013065338</v>
       </c>
       <c r="G1176" t="n">
-        <v>0.754176735877991</v>
+        <v>0.754176676273346</v>
       </c>
       <c r="H1176" t="n">
         <v>1382759</v>
@@ -34531,7 +34531,7 @@
         <v>0.836115002632141</v>
       </c>
       <c r="G1178" t="n">
-        <v>0.724761188030243</v>
+        <v>0.724761247634888</v>
       </c>
       <c r="H1178" t="n">
         <v>1859529</v>
@@ -34560,7 +34560,7 @@
         <v>0.810193002223969</v>
       </c>
       <c r="G1179" t="n">
-        <v>0.702291488647461</v>
+        <v>0.702291548252106</v>
       </c>
       <c r="H1179" t="n">
         <v>2310930</v>
@@ -34589,7 +34589,7 @@
         <v>0.803593993186951</v>
       </c>
       <c r="G1180" t="n">
-        <v>0.696571350097656</v>
+        <v>0.696571409702301</v>
       </c>
       <c r="H1180" t="n">
         <v>3370740</v>
@@ -34647,7 +34647,7 @@
         <v>0.7795569896698</v>
       </c>
       <c r="G1182" t="n">
-        <v>0.675735592842102</v>
+        <v>0.675735533237457</v>
       </c>
       <c r="H1182" t="n">
         <v>2456482</v>
@@ -34676,7 +34676,7 @@
         <v>0.781913995742798</v>
       </c>
       <c r="G1183" t="n">
-        <v>0.677778720855713</v>
+        <v>0.677778661251068</v>
       </c>
       <c r="H1183" t="n">
         <v>1964418</v>
@@ -34734,7 +34734,7 @@
         <v>0.76070499420166</v>
       </c>
       <c r="G1185" t="n">
-        <v>0.659394323825836</v>
+        <v>0.659394264221191</v>
       </c>
       <c r="H1185" t="n">
         <v>2296141</v>
@@ -34763,7 +34763,7 @@
         <v>0.752220988273621</v>
       </c>
       <c r="G1186" t="n">
-        <v>0.652040183544159</v>
+        <v>0.652040243148804</v>
       </c>
       <c r="H1186" t="n">
         <v>2808648</v>
@@ -34966,7 +34966,7 @@
         <v>0.787097990512848</v>
       </c>
       <c r="G1193" t="n">
-        <v>0.68227231502533</v>
+        <v>0.682272255420685</v>
       </c>
       <c r="H1193" t="n">
         <v>1604251</v>
@@ -34995,7 +34995,7 @@
         <v>0.794167995452881</v>
       </c>
       <c r="G1194" t="n">
-        <v>0.688400685787201</v>
+        <v>0.688400745391846</v>
       </c>
       <c r="H1194" t="n">
         <v>1269454</v>
@@ -35082,7 +35082,7 @@
         <v>0.813021004199982</v>
       </c>
       <c r="G1197" t="n">
-        <v>0.704742848873138</v>
+        <v>0.704742908477783</v>
       </c>
       <c r="H1197" t="n">
         <v>1326414</v>
@@ -35111,7 +35111,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1198" t="n">
-        <v>0.72639524936676</v>
+        <v>0.726395130157471</v>
       </c>
       <c r="H1198" t="n">
         <v>3034004</v>
@@ -35140,7 +35140,7 @@
         <v>0.866279006004333</v>
       </c>
       <c r="G1199" t="n">
-        <v>0.750908017158508</v>
+        <v>0.750907957553864</v>
       </c>
       <c r="H1199" t="n">
         <v>6934564</v>
@@ -35169,7 +35169,7 @@
         <v>0.810663998126984</v>
       </c>
       <c r="G1200" t="n">
-        <v>0.702699720859528</v>
+        <v>0.702699780464172</v>
       </c>
       <c r="H1200" t="n">
         <v>2835724</v>
@@ -35314,7 +35314,7 @@
         <v>0.879005014896393</v>
       </c>
       <c r="G1205" t="n">
-        <v>0.761939108371735</v>
+        <v>0.761939167976379</v>
       </c>
       <c r="H1205" t="n">
         <v>2086206</v>
@@ -35343,7 +35343,7 @@
         <v>0.898800015449524</v>
       </c>
       <c r="G1206" t="n">
-        <v>0.77909779548645</v>
+        <v>0.779097855091095</v>
       </c>
       <c r="H1206" t="n">
         <v>3480071</v>
@@ -35372,7 +35372,7 @@
         <v>0.931321024894714</v>
       </c>
       <c r="G1207" t="n">
-        <v>0.807287693023682</v>
+        <v>0.807287752628326</v>
       </c>
       <c r="H1207" t="n">
         <v>3139484</v>
@@ -35401,7 +35401,7 @@
         <v>0.95959997177124</v>
       </c>
       <c r="G1208" t="n">
-        <v>0.83180046081543</v>
+        <v>0.831800401210785</v>
       </c>
       <c r="H1208" t="n">
         <v>5019017</v>
@@ -35488,7 +35488,7 @@
         <v>0.969026029109955</v>
       </c>
       <c r="G1211" t="n">
-        <v>0.83997118473053</v>
+        <v>0.839971125125885</v>
       </c>
       <c r="H1211" t="n">
         <v>1427610</v>
@@ -35517,7 +35517,7 @@
         <v>0.95959997177124</v>
       </c>
       <c r="G1212" t="n">
-        <v>0.83180046081543</v>
+        <v>0.831800401210785</v>
       </c>
       <c r="H1212" t="n">
         <v>1184592</v>
@@ -35546,7 +35546,7 @@
         <v>0.952058970928192</v>
       </c>
       <c r="G1213" t="n">
-        <v>0.825263798236847</v>
+        <v>0.825263738632202</v>
       </c>
       <c r="H1213" t="n">
         <v>1664648</v>
@@ -35691,7 +35691,7 @@
         <v>0.91718202829361</v>
       </c>
       <c r="G1218" t="n">
-        <v>0.795031785964966</v>
+        <v>0.795031726360321</v>
       </c>
       <c r="H1218" t="n">
         <v>3430045</v>
@@ -35720,7 +35720,7 @@
         <v>0.911526024341583</v>
       </c>
       <c r="G1219" t="n">
-        <v>0.790129005908966</v>
+        <v>0.790129065513611</v>
       </c>
       <c r="H1219" t="n">
         <v>2205142</v>
@@ -35836,7 +35836,7 @@
         <v>0.92613697052002</v>
       </c>
       <c r="G1223" t="n">
-        <v>0.802794098854065</v>
+        <v>0.80279403924942</v>
       </c>
       <c r="H1223" t="n">
         <v>2660311</v>
@@ -35923,7 +35923,7 @@
         <v>0.802179992198944</v>
       </c>
       <c r="G1226" t="n">
-        <v>0.69534569978714</v>
+        <v>0.695345640182495</v>
       </c>
       <c r="H1226" t="n">
         <v>4229859</v>
@@ -35981,7 +35981,7 @@
         <v>0.71545797586441</v>
       </c>
       <c r="G1228" t="n">
-        <v>0.620173215866089</v>
+        <v>0.620173275470734</v>
       </c>
       <c r="H1228" t="n">
         <v>3297489</v>
@@ -36010,7 +36010,7 @@
         <v>0.72818398475647</v>
       </c>
       <c r="G1229" t="n">
-        <v>0.63120448589325</v>
+        <v>0.631204426288605</v>
       </c>
       <c r="H1229" t="n">
         <v>2917830</v>
@@ -36039,7 +36039,7 @@
         <v>0.729597985744476</v>
       </c>
       <c r="G1230" t="n">
-        <v>0.632430076599121</v>
+        <v>0.632430136203766</v>
       </c>
       <c r="H1230" t="n">
         <v>1630338</v>
@@ -36184,7 +36184,7 @@
         <v>0.849783003330231</v>
       </c>
       <c r="G1235" t="n">
-        <v>0.736608922481537</v>
+        <v>0.736608862876892</v>
       </c>
       <c r="H1235" t="n">
         <v>3041173</v>
@@ -36329,7 +36329,7 @@
         <v>0.890788018703461</v>
       </c>
       <c r="G1240" t="n">
-        <v>0.772152900695801</v>
+        <v>0.772152841091156</v>
       </c>
       <c r="H1240" t="n">
         <v>7220618</v>
@@ -36387,7 +36387,7 @@
         <v>0.95959997177124</v>
       </c>
       <c r="G1242" t="n">
-        <v>0.83180046081543</v>
+        <v>0.831800401210785</v>
       </c>
       <c r="H1242" t="n">
         <v>6443923</v>
@@ -36474,7 +36474,7 @@
         <v>0.989763975143433</v>
       </c>
       <c r="G1245" t="n">
-        <v>0.857947170734406</v>
+        <v>0.85794723033905</v>
       </c>
       <c r="H1245" t="n">
         <v>2277559</v>
@@ -36503,7 +36503,7 @@
         <v>1.01615798473358</v>
       </c>
       <c r="G1246" t="n">
-        <v>0.880825996398926</v>
+        <v>0.880826115608215</v>
       </c>
       <c r="H1246" t="n">
         <v>2905965</v>
@@ -36706,7 +36706,7 @@
         <v>1.04066705703735</v>
       </c>
       <c r="G1253" t="n">
-        <v>0.902071058750153</v>
+        <v>0.902071118354797</v>
       </c>
       <c r="H1253" t="n">
         <v>4937362</v>
@@ -36764,7 +36764,7 @@
         <v>1.00861704349518</v>
       </c>
       <c r="G1255" t="n">
-        <v>0.874289453029633</v>
+        <v>0.874289393424988</v>
       </c>
       <c r="H1255" t="n">
         <v>1723351</v>
@@ -36822,7 +36822,7 @@
         <v>0.995419979095459</v>
       </c>
       <c r="G1257" t="n">
-        <v>0.86285001039505</v>
+        <v>0.862849950790405</v>
       </c>
       <c r="H1257" t="n">
         <v>1057448</v>
@@ -36851,7 +36851,7 @@
         <v>0.979394972324371</v>
       </c>
       <c r="G1258" t="n">
-        <v>0.8489590883255</v>
+        <v>0.84895920753479</v>
       </c>
       <c r="H1258" t="n">
         <v>1526082</v>
@@ -36909,7 +36909,7 @@
         <v>0.949231028556824</v>
       </c>
       <c r="G1260" t="n">
-        <v>0.822812497615814</v>
+        <v>0.822812438011169</v>
       </c>
       <c r="H1260" t="n">
         <v>1650218</v>
@@ -36938,7 +36938,7 @@
         <v>0.969026029109955</v>
       </c>
       <c r="G1261" t="n">
-        <v>0.83997118473053</v>
+        <v>0.839971125125885</v>
       </c>
       <c r="H1261" t="n">
         <v>1579521</v>
@@ -37025,7 +37025,7 @@
         <v>0.95017397403717</v>
       </c>
       <c r="G1264" t="n">
-        <v>0.823629915714264</v>
+        <v>0.823629796504974</v>
       </c>
       <c r="H1264" t="n">
         <v>1851657</v>
@@ -37083,7 +37083,7 @@
         <v>0.948288977146149</v>
       </c>
       <c r="G1266" t="n">
-        <v>0.821995794773102</v>
+        <v>0.821995854377747</v>
       </c>
       <c r="H1266" t="n">
         <v>1463574</v>
@@ -37112,7 +37112,7 @@
         <v>0.969968974590302</v>
       </c>
       <c r="G1267" t="n">
-        <v>0.840788424015045</v>
+        <v>0.840788543224335</v>
       </c>
       <c r="H1267" t="n">
         <v>1574615</v>
@@ -37199,7 +37199,7 @@
         <v>0.989763975143433</v>
       </c>
       <c r="G1270" t="n">
-        <v>0.857947170734406</v>
+        <v>0.85794723033905</v>
       </c>
       <c r="H1270" t="n">
         <v>1405018</v>
@@ -37286,7 +37286,7 @@
         <v>0.985050976276398</v>
       </c>
       <c r="G1273" t="n">
-        <v>0.853861927986145</v>
+        <v>0.8538618683815</v>
       </c>
       <c r="H1273" t="n">
         <v>1468625</v>
@@ -37315,7 +37315,7 @@
         <v>1.02275705337524</v>
       </c>
       <c r="G1274" t="n">
-        <v>0.886546313762665</v>
+        <v>0.88654625415802</v>
       </c>
       <c r="H1274" t="n">
         <v>3118362</v>
@@ -37373,7 +37373,7 @@
         <v>1.07648694515228</v>
       </c>
       <c r="G1276" t="n">
-        <v>0.933120489120483</v>
+        <v>0.933120369911194</v>
       </c>
       <c r="H1276" t="n">
         <v>2580942</v>
@@ -37402,7 +37402,7 @@
         <v>1.08025705814362</v>
       </c>
       <c r="G1277" t="n">
-        <v>0.936388552188873</v>
+        <v>0.936388492584229</v>
       </c>
       <c r="H1277" t="n">
         <v>7347018</v>
@@ -37431,7 +37431,7 @@
         <v>1.089684009552</v>
       </c>
       <c r="G1278" t="n">
-        <v>0.944559931755066</v>
+        <v>0.944559872150421</v>
       </c>
       <c r="H1278" t="n">
         <v>3168683</v>
@@ -37460,7 +37460,7 @@
         <v>1.10382294654846</v>
       </c>
       <c r="G1279" t="n">
-        <v>0.956815898418427</v>
+        <v>0.956815838813782</v>
       </c>
       <c r="H1279" t="n">
         <v>1811020</v>
@@ -37547,7 +37547,7 @@
         <v>1.08496999740601</v>
       </c>
       <c r="G1282" t="n">
-        <v>0.940473794937134</v>
+        <v>0.940473735332489</v>
       </c>
       <c r="H1282" t="n">
         <v>1427458</v>
@@ -37576,7 +37576,7 @@
         <v>1.05480599403381</v>
       </c>
       <c r="G1283" t="n">
-        <v>0.914326906204224</v>
+        <v>0.914326965808868</v>
       </c>
       <c r="H1283" t="n">
         <v>1756689</v>
@@ -37605,7 +37605,7 @@
         <v>1.01898598670959</v>
       </c>
       <c r="G1284" t="n">
-        <v>0.883277475833893</v>
+        <v>0.883277416229248</v>
       </c>
       <c r="H1284" t="n">
         <v>2073401</v>
@@ -37692,7 +37692,7 @@
         <v>0.989763975143433</v>
       </c>
       <c r="G1287" t="n">
-        <v>0.857947170734406</v>
+        <v>0.85794723033905</v>
       </c>
       <c r="H1287" t="n">
         <v>1848908</v>
@@ -37721,7 +37721,7 @@
         <v>0.979394972324371</v>
       </c>
       <c r="G1288" t="n">
-        <v>0.8489590883255</v>
+        <v>0.84895920753479</v>
       </c>
       <c r="H1288" t="n">
         <v>1571600</v>
@@ -37808,7 +37808,7 @@
         <v>0.978452980518341</v>
       </c>
       <c r="G1291" t="n">
-        <v>0.848142623901367</v>
+        <v>0.848142683506012</v>
       </c>
       <c r="H1291" t="n">
         <v>1798343</v>
@@ -37837,7 +37837,7 @@
         <v>0.978452980518341</v>
       </c>
       <c r="G1292" t="n">
-        <v>0.848142623901367</v>
+        <v>0.848142683506012</v>
       </c>
       <c r="H1292" t="n">
         <v>868517</v>
@@ -37895,7 +37895,7 @@
         <v>1.02369904518127</v>
       </c>
       <c r="G1294" t="n">
-        <v>0.887362837791443</v>
+        <v>0.887362897396088</v>
       </c>
       <c r="H1294" t="n">
         <v>1991092</v>
@@ -37953,7 +37953,7 @@
         <v>1.05103600025177</v>
       </c>
       <c r="G1296" t="n">
-        <v>0.911059141159058</v>
+        <v>0.911059081554413</v>
       </c>
       <c r="H1296" t="n">
         <v>2175010</v>
@@ -38011,7 +38011,7 @@
         <v>1.04632198810577</v>
       </c>
       <c r="G1298" t="n">
-        <v>0.906972885131836</v>
+        <v>0.906972825527191</v>
       </c>
       <c r="H1298" t="n">
         <v>1463188</v>
@@ -38069,7 +38069,7 @@
         <v>1.03029799461365</v>
       </c>
       <c r="G1300" t="n">
-        <v>0.893082857131958</v>
+        <v>0.893082916736603</v>
       </c>
       <c r="H1300" t="n">
         <v>1061604</v>
@@ -38127,7 +38127,7 @@
         <v>1.06894600391388</v>
       </c>
       <c r="G1302" t="n">
-        <v>0.926583826541901</v>
+        <v>0.926583707332611</v>
       </c>
       <c r="H1302" t="n">
         <v>2168025</v>
@@ -38156,7 +38156,7 @@
         <v>1.0444370508194</v>
       </c>
       <c r="G1303" t="n">
-        <v>0.905338943004608</v>
+        <v>0.905338883399963</v>
       </c>
       <c r="H1303" t="n">
         <v>1960484</v>
@@ -38214,7 +38214,7 @@
         <v>1.04632198810577</v>
       </c>
       <c r="G1305" t="n">
-        <v>0.906972885131836</v>
+        <v>0.906972825527191</v>
       </c>
       <c r="H1305" t="n">
         <v>1492288</v>
@@ -38243,7 +38243,7 @@
         <v>1.04914999008179</v>
       </c>
       <c r="G1306" t="n">
-        <v>0.909424245357513</v>
+        <v>0.909424185752869</v>
       </c>
       <c r="H1306" t="n">
         <v>741023</v>
@@ -38330,7 +38330,7 @@
         <v>1.05951905250549</v>
       </c>
       <c r="G1309" t="n">
-        <v>0.918412446975708</v>
+        <v>0.918412327766418</v>
       </c>
       <c r="H1309" t="n">
         <v>1701718</v>
@@ -38359,7 +38359,7 @@
         <v>1.05763399600983</v>
       </c>
       <c r="G1310" t="n">
-        <v>0.916778326034546</v>
+        <v>0.916778385639191</v>
       </c>
       <c r="H1310" t="n">
         <v>1821748</v>
@@ -38446,7 +38446,7 @@
         <v>1.06234705448151</v>
       </c>
       <c r="G1313" t="n">
-        <v>0.920863687992096</v>
+        <v>0.920863747596741</v>
       </c>
       <c r="H1313" t="n">
         <v>2022653</v>
@@ -38475,7 +38475,7 @@
         <v>1.06800305843353</v>
       </c>
       <c r="G1314" t="n">
-        <v>0.925766468048096</v>
+        <v>0.925766408443451</v>
       </c>
       <c r="H1314" t="n">
         <v>1195930</v>
@@ -38504,7 +38504,7 @@
         <v>1.05574905872345</v>
       </c>
       <c r="G1315" t="n">
-        <v>0.915144324302673</v>
+        <v>0.915144503116608</v>
       </c>
       <c r="H1315" t="n">
         <v>1384008</v>
@@ -38591,7 +38591,7 @@
         <v>1.29423499107361</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.12186896800995</v>
+        <v>1.12186884880066</v>
       </c>
       <c r="H1318" t="n">
         <v>7470737</v>
@@ -38649,7 +38649,7 @@
         <v>1.41960501670837</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.23054194450378</v>
+        <v>1.23054206371307</v>
       </c>
       <c r="H1320" t="n">
         <v>7466356</v>
@@ -38678,7 +38678,7 @@
         <v>1.3243989944458</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.14801549911499</v>
+        <v>1.14801561832428</v>
       </c>
       <c r="H1321" t="n">
         <v>8650645</v>
@@ -38707,7 +38707,7 @@
         <v>1.3093169927597</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.13494217395782</v>
+        <v>1.13494229316711</v>
       </c>
       <c r="H1322" t="n">
         <v>3474337</v>
@@ -38736,7 +38736,7 @@
         <v>1.30648899078369</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.13249087333679</v>
+        <v>1.1324907541275</v>
       </c>
       <c r="H1323" t="n">
         <v>2179319</v>
@@ -38794,7 +38794,7 @@
         <v>1.28480899333954</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.11369812488556</v>
+        <v>1.11369824409485</v>
       </c>
       <c r="H1325" t="n">
         <v>2481320</v>
@@ -38823,7 +38823,7 @@
         <v>1.27444005012512</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.10470998287201</v>
+        <v>1.1047101020813</v>
       </c>
       <c r="H1326" t="n">
         <v>869235</v>
@@ -38852,7 +38852,7 @@
         <v>1.25181603431702</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.08509922027588</v>
+        <v>1.08509910106659</v>
       </c>
       <c r="H1327" t="n">
         <v>1444707</v>
@@ -38881,7 +38881,7 @@
         <v>1.253702044487</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.08673393726349</v>
+        <v>1.08673405647278</v>
       </c>
       <c r="H1328" t="n">
         <v>1775265</v>
@@ -38910,7 +38910,7 @@
         <v>1.24898898601532</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.08264863491058</v>
+        <v>1.08264851570129</v>
       </c>
       <c r="H1329" t="n">
         <v>1994192</v>
@@ -39026,7 +39026,7 @@
         <v>1.26501297950745</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.09653878211975</v>
+        <v>1.09653866291046</v>
       </c>
       <c r="H1333" t="n">
         <v>1764206</v>
@@ -39055,7 +39055,7 @@
         <v>1.27726805210114</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.10716164112091</v>
+        <v>1.10716152191162</v>
       </c>
       <c r="H1334" t="n">
         <v>1117293</v>
@@ -39084,7 +39084,7 @@
         <v>1.31308805942535</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.1382110118866</v>
+        <v>1.13821113109589</v>
       </c>
       <c r="H1335" t="n">
         <v>1384060</v>
@@ -39113,7 +39113,7 @@
         <v>1.29235005378723</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.12023484706879</v>
+        <v>1.1202347278595</v>
       </c>
       <c r="H1336" t="n">
         <v>1186807</v>
@@ -39142,7 +39142,7 @@
         <v>1.25181603431702</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.08509922027588</v>
+        <v>1.08509910106659</v>
       </c>
       <c r="H1337" t="n">
         <v>1949907</v>
@@ -39171,7 +39171,7 @@
         <v>1.25841498374939</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.09081935882568</v>
+        <v>1.09081923961639</v>
       </c>
       <c r="H1338" t="n">
         <v>867724</v>
@@ -39229,7 +39229,7 @@
         <v>1.253702044487</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.08673393726349</v>
+        <v>1.08673405647278</v>
       </c>
       <c r="H1340" t="n">
         <v>931225</v>
@@ -39258,7 +39258,7 @@
         <v>1.27444005012512</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.10470998287201</v>
+        <v>1.1047101020813</v>
       </c>
       <c r="H1341" t="n">
         <v>1213980</v>
@@ -39287,7 +39287,7 @@
         <v>1.27444005012512</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.10470998287201</v>
+        <v>1.1047101020813</v>
       </c>
       <c r="H1342" t="n">
         <v>1163909</v>
@@ -39345,7 +39345,7 @@
         <v>1.55440199375153</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.34738683700562</v>
+        <v>1.34738671779633</v>
       </c>
       <c r="H1344" t="n">
         <v>10339257</v>
@@ -39374,7 +39374,7 @@
         <v>1.5487459897995</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.34248387813568</v>
+        <v>1.34248399734497</v>
       </c>
       <c r="H1345" t="n">
         <v>6584878</v>
@@ -39403,7 +39403,7 @@
         <v>1.56665599346161</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.35800886154175</v>
+        <v>1.35800874233246</v>
       </c>
       <c r="H1346" t="n">
         <v>3396596</v>
@@ -39490,7 +39490,7 @@
         <v>1.63075494766235</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.41357088088989</v>
+        <v>1.41357100009918</v>
       </c>
       <c r="H1349" t="n">
         <v>2421693</v>
@@ -39577,7 +39577,7 @@
         <v>1.62509894371033</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.40866816043854</v>
+        <v>1.40866827964783</v>
       </c>
       <c r="H1352" t="n">
         <v>1702360</v>
@@ -39635,7 +39635,7 @@
         <v>1.58739399909973</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.37598478794098</v>
+        <v>1.37598490715027</v>
       </c>
       <c r="H1354" t="n">
         <v>1357173</v>
@@ -39664,7 +39664,7 @@
         <v>1.5487459897995</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.34248387813568</v>
+        <v>1.34248399734497</v>
       </c>
       <c r="H1355" t="n">
         <v>2148173</v>
@@ -39780,7 +39780,7 @@
         <v>1.66657495498657</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.44462049007416</v>
+        <v>1.44462060928345</v>
       </c>
       <c r="H1359" t="n">
         <v>2348411</v>
@@ -39809,7 +39809,7 @@
         <v>1.64678001403809</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.42746186256409</v>
+        <v>1.4274617433548</v>
       </c>
       <c r="H1360" t="n">
         <v>2308884</v>
@@ -39867,7 +39867,7 @@
         <v>1.62604200839996</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.40948569774628</v>
+        <v>1.40948581695557</v>
       </c>
       <c r="H1362" t="n">
         <v>1889084</v>
@@ -39925,7 +39925,7 @@
         <v>1.63358294963837</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.41602230072021</v>
+        <v>1.41602253913879</v>
       </c>
       <c r="H1364" t="n">
         <v>1318395</v>
@@ -40128,7 +40128,7 @@
         <v>1.59776294231415</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.38497269153595</v>
+        <v>1.38497281074524</v>
       </c>
       <c r="H1371" t="n">
         <v>1437485</v>
@@ -40244,7 +40244,7 @@
         <v>1.74952697753906</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.51652503013611</v>
+        <v>1.51652491092682</v>
       </c>
       <c r="H1375" t="n">
         <v>3410180</v>
@@ -40273,7 +40273,7 @@
         <v>1.76460897922516</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.52959835529327</v>
+        <v>1.52959823608398</v>
       </c>
       <c r="H1376" t="n">
         <v>1932661</v>
@@ -40302,7 +40302,7 @@
         <v>1.73633003234863</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.50508558750153</v>
+        <v>1.50508546829224</v>
       </c>
       <c r="H1377" t="n">
         <v>1683069</v>
@@ -40360,7 +40360,7 @@
         <v>1.74764204025269</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.51489114761353</v>
+        <v>1.51489126682281</v>
       </c>
       <c r="H1379" t="n">
         <v>1193898</v>
@@ -40418,7 +40418,7 @@
         <v>1.81928205490112</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.57699000835419</v>
+        <v>1.57699024677277</v>
       </c>
       <c r="H1381" t="n">
         <v>1940759</v>
@@ -40447,7 +40447,7 @@
         <v>1.78911697864532</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.55084252357483</v>
+        <v>1.55084228515625</v>
       </c>
       <c r="H1382" t="n">
         <v>1455756</v>
@@ -40505,7 +40505,7 @@
         <v>1.82776498794556</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.58434331417084</v>
+        <v>1.58434319496155</v>
       </c>
       <c r="H1384" t="n">
         <v>1446299</v>
@@ -40563,7 +40563,7 @@
         <v>1.8362489938736</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.59169745445251</v>
+        <v>1.59169721603394</v>
       </c>
       <c r="H1386" t="n">
         <v>1417326</v>
@@ -40592,7 +40592,7 @@
         <v>1.8211669921875</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.57862401008606</v>
+        <v>1.57862389087677</v>
       </c>
       <c r="H1387" t="n">
         <v>3872176</v>
@@ -40679,7 +40679,7 @@
         <v>1.64395201206207</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.42501056194305</v>
+        <v>1.42501044273376</v>
       </c>
       <c r="H1390" t="n">
         <v>5457381</v>
@@ -40708,7 +40708,7 @@
         <v>1.59776294231415</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.38497269153595</v>
+        <v>1.38497281074524</v>
       </c>
       <c r="H1391" t="n">
         <v>2553946</v>
@@ -40737,7 +40737,7 @@
         <v>1.58739399909973</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.37598478794098</v>
+        <v>1.37598490715027</v>
       </c>
       <c r="H1392" t="n">
         <v>1889363</v>
@@ -40795,7 +40795,7 @@
         <v>1.51575398445129</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.31388580799103</v>
+        <v>1.31388592720032</v>
       </c>
       <c r="H1394" t="n">
         <v>2200403</v>
@@ -40824,7 +40824,7 @@
         <v>1.53083598613739</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.32695925235748</v>
+        <v>1.32695937156677</v>
       </c>
       <c r="H1395" t="n">
         <v>2013608</v>
@@ -40853,7 +40853,7 @@
         <v>1.50444197654724</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.30408036708832</v>
+        <v>1.30408048629761</v>
       </c>
       <c r="H1396" t="n">
         <v>1728332</v>
@@ -40882,7 +40882,7 @@
         <v>1.5336639881134</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.32941067218781</v>
+        <v>1.32941055297852</v>
       </c>
       <c r="H1397" t="n">
         <v>1677517</v>
@@ -40911,7 +40911,7 @@
         <v>1.51575398445129</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.31388580799103</v>
+        <v>1.31388592720032</v>
       </c>
       <c r="H1398" t="n">
         <v>946193</v>
@@ -40940,7 +40940,7 @@
         <v>1.54026198387146</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.33512997627258</v>
+        <v>1.33512985706329</v>
       </c>
       <c r="H1399" t="n">
         <v>944434</v>
@@ -40998,7 +40998,7 @@
         <v>1.54686105251312</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.34085011482239</v>
+        <v>1.34085023403168</v>
       </c>
       <c r="H1401" t="n">
         <v>2490320</v>
@@ -41114,7 +41114,7 @@
         <v>1.61899995803833</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.40338146686554</v>
+        <v>1.40338158607483</v>
       </c>
       <c r="H1405" t="n">
         <v>2975417</v>
@@ -41143,7 +41143,7 @@
         <v>1.59399998188019</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.38171100616455</v>
+        <v>1.38171112537384</v>
       </c>
       <c r="H1406" t="n">
         <v>2115107</v>
@@ -41259,7 +41259,7 @@
         <v>1.63399994373322</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.41638386249542</v>
+        <v>1.41638374328613</v>
       </c>
       <c r="H1410" t="n">
         <v>9470248</v>
@@ -41317,7 +41317,7 @@
         <v>1.71300005912781</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.48486280441284</v>
+        <v>1.48486268520355</v>
       </c>
       <c r="H1412" t="n">
         <v>4235986</v>
@@ -41346,7 +41346,7 @@
         <v>1.72899997234344</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.49873197078705</v>
+        <v>1.49873185157776</v>
       </c>
       <c r="H1413" t="n">
         <v>1868785</v>
@@ -41433,7 +41433,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.51520133018494</v>
+        <v>1.51520144939423</v>
       </c>
       <c r="H1416" t="n">
         <v>4216448</v>
@@ -41462,7 +41462,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.51086723804474</v>
+        <v>1.51086735725403</v>
       </c>
       <c r="H1417" t="n">
         <v>2208366</v>
@@ -41520,7 +41520,7 @@
         <v>1.75899994373322</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.52473628520966</v>
+        <v>1.52473640441895</v>
       </c>
       <c r="H1419" t="n">
         <v>1878660</v>
@@ -41549,7 +41549,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.54207301139832</v>
+        <v>1.54207289218903</v>
       </c>
       <c r="H1420" t="n">
         <v>1257479</v>
@@ -41578,7 +41578,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.57934594154358</v>
+        <v>1.57934606075287</v>
       </c>
       <c r="H1421" t="n">
         <v>4157779</v>
@@ -41607,7 +41607,7 @@
         <v>1.81299996376038</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.57154476642609</v>
+        <v>1.5715446472168</v>
       </c>
       <c r="H1422" t="n">
         <v>2266510</v>
@@ -41636,7 +41636,7 @@
         <v>1.77100002765656</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.53513824939728</v>
+        <v>1.53513836860657</v>
       </c>
       <c r="H1423" t="n">
         <v>2372636</v>
@@ -41665,7 +41665,7 @@
         <v>1.79299998283386</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.55420827865601</v>
+        <v>1.55420815944672</v>
       </c>
       <c r="H1424" t="n">
         <v>1093441</v>
@@ -41694,7 +41694,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.56894409656525</v>
+        <v>1.56894421577454</v>
       </c>
       <c r="H1425" t="n">
         <v>1132253</v>
@@ -41897,7 +41897,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.46059155464172</v>
+        <v>1.46059167385101</v>
       </c>
       <c r="H1432" t="n">
         <v>2543581</v>
@@ -41955,7 +41955,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.46059155464172</v>
+        <v>1.46059167385101</v>
       </c>
       <c r="H1434" t="n">
         <v>1897472</v>
@@ -41984,7 +41984,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.49179720878601</v>
+        <v>1.49179697036743</v>
       </c>
       <c r="H1435" t="n">
         <v>1352324</v>
@@ -42013,7 +42013,7 @@
         <v>1.70099997520447</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.47446084022522</v>
+        <v>1.47446072101593</v>
       </c>
       <c r="H1436" t="n">
         <v>1106465</v>
@@ -42071,7 +42071,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.46839308738708</v>
+        <v>1.46839320659637</v>
       </c>
       <c r="H1438" t="n">
         <v>3681357</v>
@@ -42158,7 +42158,7 @@
         <v>1.75300002098083</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.51953554153442</v>
+        <v>1.51953542232513</v>
       </c>
       <c r="H1441" t="n">
         <v>1767174</v>
@@ -42187,7 +42187,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.51086723804474</v>
+        <v>1.51086735725403</v>
       </c>
       <c r="H1442" t="n">
         <v>858934</v>
@@ -42216,7 +42216,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.49179720878601</v>
+        <v>1.49179697036743</v>
       </c>
       <c r="H1443" t="n">
         <v>959752</v>
@@ -42245,7 +42245,7 @@
         <v>1.84899997711182</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.60275018215179</v>
+        <v>1.6027500629425</v>
       </c>
       <c r="H1444" t="n">
         <v>7153801</v>
@@ -42303,7 +42303,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.52993738651276</v>
+        <v>1.52993726730347</v>
       </c>
       <c r="H1446" t="n">
         <v>6137208</v>
@@ -42361,7 +42361,7 @@
         <v>1.71200001239777</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.48399591445923</v>
+        <v>1.48399579524994</v>
       </c>
       <c r="H1448" t="n">
         <v>1707205</v>
@@ -42390,7 +42390,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.45625758171082</v>
+        <v>1.4562577009201</v>
       </c>
       <c r="H1449" t="n">
         <v>2348458</v>
@@ -42419,7 +42419,7 @@
         <v>1.65400004386902</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.4337203502655</v>
+        <v>1.43372023105621</v>
       </c>
       <c r="H1450" t="n">
         <v>2061607</v>
@@ -42506,7 +42506,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1453" t="n">
-        <v>1.45625758171082</v>
+        <v>1.4562577009201</v>
       </c>
       <c r="H1453" t="n">
         <v>2487600</v>
@@ -42651,7 +42651,7 @@
         <v>2.08400011062622</v>
       </c>
       <c r="G1458" t="n">
-        <v>1.80645287036896</v>
+        <v>1.80645298957825</v>
       </c>
       <c r="H1458" t="n">
         <v>9798506</v>
@@ -42680,7 +42680,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1459" t="n">
-        <v>1.86366307735443</v>
+        <v>1.86366295814514</v>
       </c>
       <c r="H1459" t="n">
         <v>7335774</v>
@@ -42709,7 +42709,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1460" t="n">
-        <v>1.85499477386475</v>
+        <v>1.85499489307404</v>
       </c>
       <c r="H1460" t="n">
         <v>5134046</v>
@@ -42738,7 +42738,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1461" t="n">
-        <v>1.93994331359863</v>
+        <v>1.93994343280792</v>
       </c>
       <c r="H1461" t="n">
         <v>11842820</v>
@@ -42767,7 +42767,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G1462" t="n">
-        <v>1.9919525384903</v>
+        <v>1.99195230007172</v>
       </c>
       <c r="H1462" t="n">
         <v>7592056</v>
@@ -42796,7 +42796,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.04569530487061</v>
+        <v>2.04569506645203</v>
       </c>
       <c r="H1463" t="n">
         <v>9353750</v>
@@ -42854,7 +42854,7 @@
         <v>2.21199989318848</v>
       </c>
       <c r="G1465" t="n">
-        <v>1.91740596294403</v>
+        <v>1.91740584373474</v>
       </c>
       <c r="H1465" t="n">
         <v>17268071</v>
@@ -42883,7 +42883,7 @@
         <v>2.13199996948242</v>
       </c>
       <c r="G1466" t="n">
-        <v>1.84806025028229</v>
+        <v>1.84806048870087</v>
       </c>
       <c r="H1466" t="n">
         <v>10131373</v>
@@ -42912,7 +42912,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1467" t="n">
-        <v>1.91913938522339</v>
+        <v>1.9191392660141</v>
       </c>
       <c r="H1467" t="n">
         <v>5970613</v>
@@ -42970,7 +42970,7 @@
         <v>2.27800011634827</v>
       </c>
       <c r="G1469" t="n">
-        <v>1.9746161699295</v>
+        <v>1.97461640834808</v>
       </c>
       <c r="H1469" t="n">
         <v>6037420</v>
@@ -42999,7 +42999,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1470" t="n">
-        <v>2.06303191184998</v>
+        <v>2.06303143501282</v>
       </c>
       <c r="H1470" t="n">
         <v>5352857</v>
@@ -43115,7 +43115,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1474" t="n">
-        <v>2.08036828041077</v>
+        <v>2.08036804199219</v>
       </c>
       <c r="H1474" t="n">
         <v>2667968</v>
@@ -43144,7 +43144,7 @@
         <v>2.45799994468689</v>
       </c>
       <c r="G1475" t="n">
-        <v>2.13064336776733</v>
+        <v>2.13064360618591</v>
       </c>
       <c r="H1475" t="n">
         <v>6165881</v>
@@ -43202,7 +43202,7 @@
         <v>2.45600008964539</v>
       </c>
       <c r="G1477" t="n">
-        <v>2.12891006469727</v>
+        <v>2.12890982627869</v>
       </c>
       <c r="H1477" t="n">
         <v>2466738</v>
@@ -43260,7 +43260,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G1479" t="n">
-        <v>2.19478869438171</v>
+        <v>2.19478845596313</v>
       </c>
       <c r="H1479" t="n">
         <v>4629737</v>
@@ -43347,7 +43347,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G1482" t="n">
-        <v>2.09943795204163</v>
+        <v>2.09943771362305</v>
       </c>
       <c r="H1482" t="n">
         <v>3247783</v>
@@ -43405,7 +43405,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G1484" t="n">
-        <v>2.25546550750732</v>
+        <v>2.2554657459259</v>
       </c>
       <c r="H1484" t="n">
         <v>5054235</v>
@@ -43434,7 +43434,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.23639559745789</v>
+        <v>2.23639535903931</v>
       </c>
       <c r="H1485" t="n">
         <v>2591760</v>
@@ -43521,7 +43521,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.36468505859375</v>
+        <v>2.36468482017517</v>
       </c>
       <c r="H1488" t="n">
         <v>5755446</v>
@@ -43550,7 +43550,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.392422914505</v>
+        <v>2.39242339134216</v>
       </c>
       <c r="H1489" t="n">
         <v>4018176</v>
@@ -43579,7 +43579,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.33174633979797</v>
+        <v>2.33174610137939</v>
       </c>
       <c r="H1490" t="n">
         <v>2775027</v>
@@ -43637,7 +43637,7 @@
         <v>2.73600006103516</v>
       </c>
       <c r="G1492" t="n">
-        <v>2.37161946296692</v>
+        <v>2.3716197013855</v>
       </c>
       <c r="H1492" t="n">
         <v>2335714</v>
@@ -43666,7 +43666,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.42016124725342</v>
+        <v>2.42016172409058</v>
       </c>
       <c r="H1493" t="n">
         <v>4929942</v>
@@ -43985,7 +43985,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1504" t="n">
-        <v>2.33174633979797</v>
+        <v>2.33174610137939</v>
       </c>
       <c r="H1504" t="n">
         <v>4871108</v>
@@ -44043,7 +44043,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.4253625869751</v>
+        <v>2.42536234855652</v>
       </c>
       <c r="H1506" t="n">
         <v>4660987</v>
@@ -44072,7 +44072,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.43749809265137</v>
+        <v>2.43749785423279</v>
       </c>
       <c r="H1507" t="n">
         <v>3331115</v>
@@ -44101,7 +44101,7 @@
         <v>2.79200005531311</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.42016124725342</v>
+        <v>2.42016172409058</v>
       </c>
       <c r="H1508" t="n">
         <v>3635925</v>
@@ -44130,7 +44130,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.50511002540588</v>
+        <v>2.5051097869873</v>
       </c>
       <c r="H1509" t="n">
         <v>4057633</v>
@@ -44188,7 +44188,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.58312392234802</v>
+        <v>2.58312368392944</v>
       </c>
       <c r="H1511" t="n">
         <v>5723407</v>
@@ -44217,7 +44217,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.57445549964905</v>
+        <v>2.57445526123047</v>
       </c>
       <c r="H1512" t="n">
         <v>4457747</v>
@@ -44246,7 +44246,7 @@
         <v>2.99399995803833</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.59525895118713</v>
+        <v>2.59525918960571</v>
       </c>
       <c r="H1513" t="n">
         <v>3263177</v>
@@ -44304,7 +44304,7 @@
         <v>2.84800004959106</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.46870374679565</v>
+        <v>2.46870350837708</v>
       </c>
       <c r="H1515" t="n">
         <v>3181956</v>
@@ -44420,7 +44420,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.23639559745789</v>
+        <v>2.23639535903931</v>
       </c>
       <c r="H1519" t="n">
         <v>2482792</v>
@@ -44478,7 +44478,7 @@
         <v>2.56800007820129</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.22599411010742</v>
+        <v>2.22599387168884</v>
       </c>
       <c r="H1521" t="n">
         <v>1158052</v>
@@ -44507,7 +44507,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.21039080619812</v>
+        <v>2.21039128303528</v>
       </c>
       <c r="H1522" t="n">
         <v>1135251</v>
@@ -44565,7 +44565,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.22946095466614</v>
+        <v>2.22946119308472</v>
       </c>
       <c r="H1524" t="n">
         <v>1113620</v>
@@ -44623,7 +44623,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.21905946731567</v>
+        <v>2.21905922889709</v>
       </c>
       <c r="H1526" t="n">
         <v>768689</v>
@@ -44652,7 +44652,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.21905946731567</v>
+        <v>2.21905922889709</v>
       </c>
       <c r="H1527" t="n">
         <v>830847</v>
@@ -44710,7 +44710,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.3144097328186</v>
+        <v>2.31440949440002</v>
       </c>
       <c r="H1529" t="n">
         <v>2092342</v>
@@ -44826,7 +44826,7 @@
         <v>2.43799996376038</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.11330699920654</v>
+        <v>2.11330723762512</v>
       </c>
       <c r="H1533" t="n">
         <v>1647717</v>
@@ -44913,7 +44913,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1536" t="n">
-        <v>2.09250330924988</v>
+        <v>2.09250378608704</v>
       </c>
       <c r="H1536" t="n">
         <v>1873385</v>
@@ -45000,7 +45000,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.10984015464783</v>
+        <v>2.10983991622925</v>
       </c>
       <c r="H1539" t="n">
         <v>1461887</v>
@@ -45116,7 +45116,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.01275587081909</v>
+        <v>2.01275610923767</v>
       </c>
       <c r="H1543" t="n">
         <v>1247629</v>
@@ -45145,7 +45145,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.12197542190552</v>
+        <v>2.12197518348694</v>
       </c>
       <c r="H1544" t="n">
         <v>1761495</v>
@@ -45261,7 +45261,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.34041428565979</v>
+        <v>2.34041404724121</v>
       </c>
       <c r="H1548" t="n">
         <v>7869695</v>
@@ -45290,7 +45290,7 @@
         <v>2.70199990272522</v>
       </c>
       <c r="G1549" t="n">
-        <v>2.34214782714844</v>
+        <v>2.34214735031128</v>
       </c>
       <c r="H1549" t="n">
         <v>2996680</v>
@@ -45377,7 +45377,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.02142405509949</v>
+        <v>2.02142429351807</v>
       </c>
       <c r="H1552" t="n">
         <v>3048763</v>
@@ -45493,7 +45493,7 @@
         <v>2.36400008201599</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.04916262626648</v>
+        <v>2.0491623878479</v>
       </c>
       <c r="H1556" t="n">
         <v>1017937</v>
@@ -45522,7 +45522,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G1557" t="n">
-        <v>2.01275587081909</v>
+        <v>2.01275610923767</v>
       </c>
       <c r="H1557" t="n">
         <v>2090260</v>
@@ -45551,7 +45551,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.08036828041077</v>
+        <v>2.08036804199219</v>
       </c>
       <c r="H1558" t="n">
         <v>1578298</v>
@@ -45638,7 +45638,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.03529334068298</v>
+        <v>2.03529357910156</v>
       </c>
       <c r="H1561" t="n">
         <v>1733708</v>
@@ -45696,7 +45696,7 @@
         <v>2.2960000038147</v>
       </c>
       <c r="G1563" t="n">
-        <v>1.99021875858307</v>
+        <v>1.99021899700165</v>
       </c>
       <c r="H1563" t="n">
         <v>3187008</v>
@@ -45754,7 +45754,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1565" t="n">
-        <v>1.88966751098633</v>
+        <v>1.88966739177704</v>
       </c>
       <c r="H1565" t="n">
         <v>3720862</v>
@@ -45812,7 +45812,7 @@
         <v>2.26200008392334</v>
       </c>
       <c r="G1567" t="n">
-        <v>1.96074688434601</v>
+        <v>1.96074712276459</v>
       </c>
       <c r="H1567" t="n">
         <v>2270517</v>
@@ -45841,7 +45841,7 @@
         <v>2.10800004005432</v>
       </c>
       <c r="G1568" t="n">
-        <v>1.82725656032562</v>
+        <v>1.82725667953491</v>
       </c>
       <c r="H1568" t="n">
         <v>2811774</v>
@@ -45870,7 +45870,7 @@
         <v>2.14599990844727</v>
       </c>
       <c r="G1569" t="n">
-        <v>1.86019587516785</v>
+        <v>1.86019575595856</v>
       </c>
       <c r="H1569" t="n">
         <v>2030806</v>
@@ -45928,7 +45928,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G1571" t="n">
-        <v>1.60968494415283</v>
+        <v>1.60968482494354</v>
       </c>
       <c r="H1571" t="n">
         <v>3734204</v>
@@ -45957,7 +45957,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1572" t="n">
-        <v>1.52907049655914</v>
+        <v>1.52907061576843</v>
       </c>
       <c r="H1572" t="n">
         <v>7704363</v>
@@ -46015,7 +46015,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1574" t="n">
-        <v>1.6434907913208</v>
+        <v>1.64349091053009</v>
       </c>
       <c r="H1574" t="n">
         <v>5170698</v>
@@ -46044,7 +46044,7 @@
         <v>1.78299999237061</v>
       </c>
       <c r="G1575" t="n">
-        <v>1.5455402135849</v>
+        <v>1.54554009437561</v>
       </c>
       <c r="H1575" t="n">
         <v>4316215</v>
@@ -46073,7 +46073,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1576" t="n">
-        <v>1.56027579307556</v>
+        <v>1.56027591228485</v>
       </c>
       <c r="H1576" t="n">
         <v>3491990</v>
@@ -46131,7 +46131,7 @@
         <v>1.87300002574921</v>
       </c>
       <c r="G1578" t="n">
-        <v>1.62355399131775</v>
+        <v>1.62355375289917</v>
       </c>
       <c r="H1578" t="n">
         <v>1729441</v>
@@ -46160,7 +46160,7 @@
         <v>2.01600003242493</v>
       </c>
       <c r="G1579" t="n">
-        <v>1.74750912189484</v>
+        <v>1.74750924110413</v>
       </c>
       <c r="H1579" t="n">
         <v>3565997</v>
@@ -46189,7 +46189,7 @@
         <v>1.98099994659424</v>
       </c>
       <c r="G1580" t="n">
-        <v>1.71717047691345</v>
+        <v>1.71717035770416</v>
       </c>
       <c r="H1580" t="n">
         <v>1336144</v>
@@ -46218,7 +46218,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1581" t="n">
-        <v>1.69896733760834</v>
+        <v>1.69896721839905</v>
       </c>
       <c r="H1581" t="n">
         <v>1570212</v>
@@ -46247,7 +46247,7 @@
         <v>1.95700001716614</v>
       </c>
       <c r="G1582" t="n">
-        <v>1.6963666677475</v>
+        <v>1.69636690616608</v>
       </c>
       <c r="H1582" t="n">
         <v>1287911</v>
@@ -46276,7 +46276,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G1583" t="n">
-        <v>1.66949546337128</v>
+        <v>1.66949534416199</v>
       </c>
       <c r="H1583" t="n">
         <v>1987514</v>
@@ -46392,7 +46392,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G1587" t="n">
-        <v>1.69029891490936</v>
+        <v>1.69029903411865</v>
       </c>
       <c r="H1587" t="n">
         <v>1910783</v>
@@ -46450,7 +46450,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1589" t="n">
-        <v>1.79431748390198</v>
+        <v>1.7943172454834</v>
       </c>
       <c r="H1589" t="n">
         <v>1212095</v>
@@ -46479,7 +46479,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1590" t="n">
-        <v>1.70763540267944</v>
+        <v>1.70763552188873</v>
       </c>
       <c r="H1590" t="n">
         <v>2404158</v>
@@ -46508,7 +46508,7 @@
         <v>2.01399993896484</v>
       </c>
       <c r="G1591" t="n">
-        <v>1.74577558040619</v>
+        <v>1.7457754611969</v>
       </c>
       <c r="H1591" t="n">
         <v>794809</v>
@@ -46537,7 +46537,7 @@
         <v>1.9889999628067</v>
       </c>
       <c r="G1592" t="n">
-        <v>1.72410500049591</v>
+        <v>1.72410488128662</v>
       </c>
       <c r="H1592" t="n">
         <v>1407194</v>
@@ -46624,7 +46624,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G1595" t="n">
-        <v>1.60968494415283</v>
+        <v>1.60968482494354</v>
       </c>
       <c r="H1595" t="n">
         <v>1419458</v>
@@ -46653,7 +46653,7 @@
         <v>1.85699999332428</v>
       </c>
       <c r="G1596" t="n">
-        <v>1.60968494415283</v>
+        <v>1.60968482494354</v>
       </c>
       <c r="H1596" t="n">
         <v>1419557</v>
@@ -46682,7 +46682,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1597" t="n">
-        <v>1.60535073280334</v>
+        <v>1.60535061359406</v>
       </c>
       <c r="H1597" t="n">
         <v>664307</v>
@@ -46711,7 +46711,7 @@
         <v>1.807000041008</v>
       </c>
       <c r="G1598" t="n">
-        <v>1.56634390354156</v>
+        <v>1.56634378433228</v>
       </c>
       <c r="H1598" t="n">
         <v>2239744</v>
@@ -46827,7 +46827,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G1602" t="n">
-        <v>1.6434907913208</v>
+        <v>1.64349091053009</v>
       </c>
       <c r="H1602" t="n">
         <v>1707274</v>
@@ -46885,7 +46885,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G1604" t="n">
-        <v>1.64175724983215</v>
+        <v>1.64175701141357</v>
       </c>
       <c r="H1604" t="n">
         <v>3202786</v>
@@ -46914,7 +46914,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1605" t="n">
-        <v>1.57934594154358</v>
+        <v>1.57934606075287</v>
       </c>
       <c r="H1605" t="n">
         <v>2025949</v>
@@ -46943,7 +46943,7 @@
         <v>1.76400005817413</v>
       </c>
       <c r="G1606" t="n">
-        <v>1.52907049655914</v>
+        <v>1.52907061576843</v>
       </c>
       <c r="H1606" t="n">
         <v>1964099</v>
@@ -46972,7 +46972,7 @@
         <v>1.83899998664856</v>
       </c>
       <c r="G1607" t="n">
-        <v>1.5940819978714</v>
+        <v>1.59408187866211</v>
       </c>
       <c r="H1607" t="n">
         <v>1330652</v>
@@ -47001,7 +47001,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1608" t="n">
-        <v>1.60361695289612</v>
+        <v>1.60361707210541</v>
       </c>
       <c r="H1608" t="n">
         <v>928278</v>
@@ -47088,7 +47088,7 @@
         <v>1.8289999961853</v>
       </c>
       <c r="G1611" t="n">
-        <v>1.58541369438171</v>
+        <v>1.58541393280029</v>
       </c>
       <c r="H1611" t="n">
         <v>838935</v>
@@ -47117,7 +47117,7 @@
         <v>1.77900004386902</v>
       </c>
       <c r="G1612" t="n">
-        <v>1.54207301139832</v>
+        <v>1.54207289218903</v>
       </c>
       <c r="H1612" t="n">
         <v>1008192</v>
@@ -47175,7 +47175,7 @@
         <v>1.72099995613098</v>
       </c>
       <c r="G1614" t="n">
-        <v>1.49179720878601</v>
+        <v>1.49179697036743</v>
       </c>
       <c r="H1614" t="n">
         <v>1138123</v>
@@ -47233,7 +47233,7 @@
         <v>1.6690000295639</v>
       </c>
       <c r="G1616" t="n">
-        <v>1.44672250747681</v>
+        <v>1.44672274589539</v>
       </c>
       <c r="H1616" t="n">
         <v>837573</v>
@@ -47291,7 +47291,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G1618" t="n">
-        <v>1.51520133018494</v>
+        <v>1.51520144939423</v>
       </c>
       <c r="H1618" t="n">
         <v>843208</v>
@@ -47320,7 +47320,7 @@
         <v>1.81500005722046</v>
       </c>
       <c r="G1619" t="n">
-        <v>1.57327842712402</v>
+        <v>1.57327830791473</v>
       </c>
       <c r="H1619" t="n">
         <v>1148697</v>
@@ -47465,7 +47465,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1624" t="n">
-        <v>1.56547689437866</v>
+        <v>1.56547701358795</v>
       </c>
       <c r="H1624" t="n">
         <v>495990</v>
@@ -47494,7 +47494,7 @@
         <v>1.82200002670288</v>
       </c>
       <c r="G1625" t="n">
-        <v>1.57934594154358</v>
+        <v>1.57934606075287</v>
       </c>
       <c r="H1625" t="n">
         <v>577507</v>
@@ -47523,7 +47523,7 @@
         <v>1.72200000286102</v>
       </c>
       <c r="G1626" t="n">
-        <v>1.49266397953033</v>
+        <v>1.49266409873962</v>
       </c>
       <c r="H1626" t="n">
         <v>2050007</v>
@@ -47552,7 +47552,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G1627" t="n">
-        <v>1.48833012580872</v>
+        <v>1.48833000659943</v>
       </c>
       <c r="H1627" t="n">
         <v>2247192</v>
@@ -47581,7 +47581,7 @@
         <v>1.84099996089935</v>
       </c>
       <c r="G1628" t="n">
-        <v>1.59581565856934</v>
+        <v>1.59581553936005</v>
       </c>
       <c r="H1628" t="n">
         <v>2008244</v>
@@ -47668,7 +47668,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G1631" t="n">
-        <v>1.65389251708984</v>
+        <v>1.65389239788055</v>
       </c>
       <c r="H1631" t="n">
         <v>1003290</v>
@@ -47697,7 +47697,7 @@
         <v>1.93700003623962</v>
       </c>
       <c r="G1632" t="n">
-        <v>1.67903029918671</v>
+        <v>1.679030418396</v>
       </c>
       <c r="H1632" t="n">
         <v>2466125</v>
@@ -47726,7 +47726,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1633" t="n">
-        <v>1.7423083782196</v>
+        <v>1.74230813980103</v>
       </c>
       <c r="H1633" t="n">
         <v>1109703</v>
@@ -47755,7 +47755,7 @@
         <v>2.08200001716614</v>
       </c>
       <c r="G1634" t="n">
-        <v>1.80471920967102</v>
+        <v>1.80471932888031</v>
       </c>
       <c r="H1634" t="n">
         <v>3553721</v>
@@ -47813,7 +47813,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1636" t="n">
-        <v>1.75964462757111</v>
+        <v>1.75964450836182</v>
       </c>
       <c r="H1636" t="n">
         <v>1062543</v>
@@ -47871,7 +47871,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1638" t="n">
-        <v>1.7423083782196</v>
+        <v>1.74230813980103</v>
       </c>
       <c r="H1638" t="n">
         <v>1224002</v>
@@ -47900,7 +47900,7 @@
         <v>1.87100005149841</v>
       </c>
       <c r="G1639" t="n">
-        <v>1.62182009220123</v>
+        <v>1.62182033061981</v>
       </c>
       <c r="H1639" t="n">
         <v>1925036</v>
@@ -47929,7 +47929,7 @@
         <v>1.80599999427795</v>
       </c>
       <c r="G1640" t="n">
-        <v>1.56547689437866</v>
+        <v>1.56547701358795</v>
       </c>
       <c r="H1640" t="n">
         <v>1767586</v>
@@ -48045,7 +48045,7 @@
         <v>1.60099995136261</v>
       </c>
       <c r="G1644" t="n">
-        <v>1.38777875900269</v>
+        <v>1.38777887821198</v>
       </c>
       <c r="H1644" t="n">
         <v>2799416</v>
@@ -48074,7 +48074,7 @@
         <v>1.61199998855591</v>
       </c>
       <c r="G1645" t="n">
-        <v>1.43311941623688</v>
+        <v>1.43311953544617</v>
       </c>
       <c r="H1645" t="n">
         <v>1080580</v>
@@ -48190,7 +48190,7 @@
         <v>1.62399995326996</v>
       </c>
       <c r="G1649" t="n">
-        <v>1.44378793239594</v>
+        <v>1.44378781318665</v>
       </c>
       <c r="H1649" t="n">
         <v>1415349</v>
@@ -48248,7 +48248,7 @@
         <v>1.62199997901917</v>
       </c>
       <c r="G1651" t="n">
-        <v>1.44200956821442</v>
+        <v>1.442009806633</v>
       </c>
       <c r="H1651" t="n">
         <v>1855038</v>
@@ -48306,7 +48306,7 @@
         <v>1.55599999427795</v>
       </c>
       <c r="G1653" t="n">
-        <v>1.38333380222321</v>
+        <v>1.38333368301392</v>
       </c>
       <c r="H1653" t="n">
         <v>2717090</v>
@@ -48335,7 +48335,7 @@
         <v>1.50999999046326</v>
       </c>
       <c r="G1654" t="n">
-        <v>1.34243810176849</v>
+        <v>1.34243822097778</v>
       </c>
       <c r="H1654" t="n">
         <v>2268765</v>
@@ -48422,7 +48422,7 @@
         <v>1.46099996566772</v>
       </c>
       <c r="G1657" t="n">
-        <v>1.29887568950653</v>
+        <v>1.29887557029724</v>
       </c>
       <c r="H1657" t="n">
         <v>1540196</v>
@@ -48451,7 +48451,7 @@
         <v>1.51199996471405</v>
       </c>
       <c r="G1658" t="n">
-        <v>1.34421610832214</v>
+        <v>1.34421622753143</v>
       </c>
       <c r="H1658" t="n">
         <v>1272930</v>
@@ -48509,7 +48509,7 @@
         <v>1.52499997615814</v>
       </c>
       <c r="G1660" t="n">
-        <v>1.35577368736267</v>
+        <v>1.35577356815338</v>
       </c>
       <c r="H1660" t="n">
         <v>638118</v>
@@ -48538,7 +48538,7 @@
         <v>1.44700002670288</v>
       </c>
       <c r="G1661" t="n">
-        <v>1.28642928600311</v>
+        <v>1.28642916679382</v>
       </c>
       <c r="H1661" t="n">
         <v>3556866</v>
@@ -48596,7 +48596,7 @@
         <v>1.40799999237061</v>
       </c>
       <c r="G1663" t="n">
-        <v>1.25175702571869</v>
+        <v>1.2517569065094</v>
       </c>
       <c r="H1663" t="n">
         <v>1704275</v>
@@ -48654,7 +48654,7 @@
         <v>1.46000003814697</v>
       </c>
       <c r="G1665" t="n">
-        <v>1.29798650741577</v>
+        <v>1.29798662662506</v>
       </c>
       <c r="H1665" t="n">
         <v>569940</v>
@@ -48683,7 +48683,7 @@
         <v>1.53799998760223</v>
       </c>
       <c r="G1666" t="n">
-        <v>1.36733090877533</v>
+        <v>1.36733102798462</v>
       </c>
       <c r="H1666" t="n">
         <v>1024543</v>
@@ -48712,7 +48712,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G1667" t="n">
-        <v>1.34154903888702</v>
+        <v>1.34154915809631</v>
       </c>
       <c r="H1667" t="n">
         <v>1039344</v>
@@ -48741,7 +48741,7 @@
         <v>1.49399995803833</v>
       </c>
       <c r="G1668" t="n">
-        <v>1.32821357250214</v>
+        <v>1.32821369171143</v>
       </c>
       <c r="H1668" t="n">
         <v>1525820</v>
@@ -48770,7 +48770,7 @@
         <v>1.49300003051758</v>
       </c>
       <c r="G1669" t="n">
-        <v>1.32732474803925</v>
+        <v>1.32732462882996</v>
       </c>
       <c r="H1669" t="n">
         <v>353421</v>
@@ -48799,7 +48799,7 @@
         <v>1.50899994373322</v>
       </c>
       <c r="G1670" t="n">
-        <v>1.34154903888702</v>
+        <v>1.34154915809631</v>
       </c>
       <c r="H1670" t="n">
         <v>528455</v>
@@ -48857,7 +48857,7 @@
         <v>1.44500005245209</v>
       </c>
       <c r="G1672" t="n">
-        <v>1.28465116024017</v>
+        <v>1.28465104103088</v>
       </c>
       <c r="H1672" t="n">
         <v>754039</v>
@@ -48915,7 +48915,7 @@
         <v>1.56200003623962</v>
       </c>
       <c r="G1674" t="n">
-        <v>1.38866782188416</v>
+        <v>1.38866794109344</v>
       </c>
       <c r="H1674" t="n">
         <v>2206308</v>
@@ -48944,7 +48944,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1675" t="n">
-        <v>1.39578020572662</v>
+        <v>1.39578008651733</v>
       </c>
       <c r="H1675" t="n">
         <v>1668193</v>
@@ -48973,7 +48973,7 @@
         <v>1.54200005531311</v>
       </c>
       <c r="G1676" t="n">
-        <v>1.37088716030121</v>
+        <v>1.3708872795105</v>
       </c>
       <c r="H1676" t="n">
         <v>641763</v>
@@ -49002,7 +49002,7 @@
         <v>1.58899998664856</v>
       </c>
       <c r="G1677" t="n">
-        <v>1.41267156600952</v>
+        <v>1.41267168521881</v>
       </c>
       <c r="H1677" t="n">
         <v>747131</v>
@@ -49031,7 +49031,7 @@
         <v>1.61699998378754</v>
       </c>
       <c r="G1678" t="n">
-        <v>1.43756437301636</v>
+        <v>1.43756449222565</v>
       </c>
       <c r="H1678" t="n">
         <v>1221897</v>
@@ -49089,7 +49089,7 @@
         <v>1.63699996471405</v>
       </c>
       <c r="G1680" t="n">
-        <v>1.4553450345993</v>
+        <v>1.45534515380859</v>
       </c>
       <c r="H1680" t="n">
         <v>599718</v>
@@ -49147,7 +49147,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G1682" t="n">
-        <v>1.46245729923248</v>
+        <v>1.46245753765106</v>
       </c>
       <c r="H1682" t="n">
         <v>715835</v>
@@ -49321,7 +49321,7 @@
         <v>1.62899994850159</v>
       </c>
       <c r="G1688" t="n">
-        <v>1.4482330083847</v>
+        <v>1.44823288917542</v>
       </c>
       <c r="H1688" t="n">
         <v>872033</v>
@@ -49350,7 +49350,7 @@
         <v>1.5440000295639</v>
       </c>
       <c r="G1689" t="n">
-        <v>1.37266540527344</v>
+        <v>1.37266528606415</v>
       </c>
       <c r="H1689" t="n">
         <v>1285720</v>
@@ -49408,7 +49408,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1691" t="n">
-        <v>1.38777875900269</v>
+        <v>1.38777887821198</v>
       </c>
       <c r="H1691" t="n">
         <v>1031562</v>
@@ -49466,7 +49466,7 @@
         <v>1.48199999332428</v>
       </c>
       <c r="G1693" t="n">
-        <v>1.31754517555237</v>
+        <v>1.31754541397095</v>
       </c>
       <c r="H1693" t="n">
         <v>983761</v>
@@ -49495,7 +49495,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G1694" t="n">
-        <v>1.31398928165436</v>
+        <v>1.31398916244507</v>
       </c>
       <c r="H1694" t="n">
         <v>635780</v>
@@ -49553,7 +49553,7 @@
         <v>1.51400005817413</v>
       </c>
       <c r="G1696" t="n">
-        <v>1.34599435329437</v>
+        <v>1.34599447250366</v>
       </c>
       <c r="H1696" t="n">
         <v>1113019</v>
@@ -49611,7 +49611,7 @@
         <v>1.53199994564056</v>
       </c>
       <c r="G1698" t="n">
-        <v>1.36199676990509</v>
+        <v>1.36199688911438</v>
       </c>
       <c r="H1698" t="n">
         <v>752663</v>
@@ -49640,7 +49640,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1699" t="n">
-        <v>1.30687701702118</v>
+        <v>1.30687689781189</v>
       </c>
       <c r="H1699" t="n">
         <v>1880728</v>
@@ -49669,7 +49669,7 @@
         <v>1.48800003528595</v>
       </c>
       <c r="G1700" t="n">
-        <v>1.32287955284119</v>
+        <v>1.3228794336319</v>
       </c>
       <c r="H1700" t="n">
         <v>683164</v>
@@ -49698,7 +49698,7 @@
         <v>1.50699996948242</v>
       </c>
       <c r="G1701" t="n">
-        <v>1.33977091312408</v>
+        <v>1.33977115154266</v>
       </c>
       <c r="H1701" t="n">
         <v>748271</v>
@@ -49756,7 +49756,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G1703" t="n">
-        <v>1.38244450092316</v>
+        <v>1.38244462013245</v>
       </c>
       <c r="H1703" t="n">
         <v>1005504</v>
@@ -49785,7 +49785,7 @@
         <v>1.5789999961853</v>
       </c>
       <c r="G1704" t="n">
-        <v>1.40378153324127</v>
+        <v>1.40378141403198</v>
       </c>
       <c r="H1704" t="n">
         <v>901854</v>
@@ -49814,7 +49814,7 @@
         <v>1.55900001525879</v>
       </c>
       <c r="G1705" t="n">
-        <v>1.38600087165833</v>
+        <v>1.38600075244904</v>
       </c>
       <c r="H1705" t="n">
         <v>767422</v>
@@ -49872,7 +49872,7 @@
         <v>1.56099998950958</v>
       </c>
       <c r="G1707" t="n">
-        <v>1.38777875900269</v>
+        <v>1.38777887821198</v>
       </c>
       <c r="H1707" t="n">
         <v>3007052</v>
@@ -49901,7 +49901,7 @@
         <v>1.55400002002716</v>
       </c>
       <c r="G1708" t="n">
-        <v>1.38155567646027</v>
+        <v>1.38155555725098</v>
       </c>
       <c r="H1708" t="n">
         <v>2843082</v>
@@ -49930,7 +49930,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1709" t="n">
-        <v>1.39578020572662</v>
+        <v>1.39578008651733</v>
       </c>
       <c r="H1709" t="n">
         <v>1097162</v>
@@ -49988,7 +49988,7 @@
         <v>1.87699997425079</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.66871297359467</v>
+        <v>1.66871285438538</v>
       </c>
       <c r="H1711" t="n">
         <v>12136044</v>
@@ -50017,7 +50017,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.64915430545807</v>
+        <v>1.64915418624878</v>
       </c>
       <c r="H1712" t="n">
         <v>5566273</v>
@@ -50046,7 +50046,7 @@
         <v>1.74300003051758</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.54958260059357</v>
+        <v>1.54958271980286</v>
       </c>
       <c r="H1713" t="n">
         <v>2371200</v>
@@ -50075,7 +50075,7 @@
         <v>1.73699998855591</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.54424858093262</v>
+        <v>1.54424846172333</v>
       </c>
       <c r="H1714" t="n">
         <v>1974262</v>
@@ -50162,7 +50162,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.46690249443054</v>
+        <v>1.46690273284912</v>
       </c>
       <c r="H1717" t="n">
         <v>1583429</v>
@@ -50191,7 +50191,7 @@
         <v>1.71399998664856</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.52380084991455</v>
+        <v>1.52380061149597</v>
       </c>
       <c r="H1718" t="n">
         <v>1699554</v>
@@ -50307,7 +50307,7 @@
         <v>1.69200003147125</v>
       </c>
       <c r="G1722" t="n">
-        <v>1.50424206256866</v>
+        <v>1.50424194335938</v>
       </c>
       <c r="H1722" t="n">
         <v>1330786</v>
@@ -50394,7 +50394,7 @@
         <v>1.71700000762939</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.52646791934967</v>
+        <v>1.52646780014038</v>
       </c>
       <c r="H1725" t="n">
         <v>1265306</v>
@@ -50510,7 +50510,7 @@
         <v>1.80499994754791</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.60470247268677</v>
+        <v>1.60470259189606</v>
       </c>
       <c r="H1729" t="n">
         <v>877262</v>
@@ -50539,7 +50539,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.62159419059753</v>
+        <v>1.62159407138824</v>
       </c>
       <c r="H1730" t="n">
         <v>1136052</v>
@@ -50597,7 +50597,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.62337231636047</v>
+        <v>1.62337219715118</v>
       </c>
       <c r="H1732" t="n">
         <v>609788</v>
@@ -50626,7 +50626,7 @@
         <v>1.82599997520447</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.62337231636047</v>
+        <v>1.62337219715118</v>
       </c>
       <c r="H1733" t="n">
         <v>704727</v>
@@ -50655,7 +50655,7 @@
         <v>1.83800005912781</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.63404059410095</v>
+        <v>1.63404071331024</v>
       </c>
       <c r="H1734" t="n">
         <v>528161</v>
@@ -50684,7 +50684,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1735" t="n">
-        <v>1.72472190856934</v>
+        <v>1.72472202777863</v>
       </c>
       <c r="H1735" t="n">
         <v>2236681</v>
@@ -50742,7 +50742,7 @@
         <v>1.96800005435944</v>
       </c>
       <c r="G1737" t="n">
-        <v>1.74961483478546</v>
+        <v>1.74961495399475</v>
       </c>
       <c r="H1737" t="n">
         <v>1184153</v>
@@ -50771,7 +50771,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1738" t="n">
-        <v>1.69271683692932</v>
+        <v>1.69271671772003</v>
       </c>
       <c r="H1738" t="n">
         <v>999179</v>
@@ -50800,7 +50800,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1739" t="n">
-        <v>1.6802704334259</v>
+        <v>1.68027031421661</v>
       </c>
       <c r="H1739" t="n">
         <v>887826</v>
@@ -50829,7 +50829,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1740" t="n">
-        <v>1.68916070461273</v>
+        <v>1.68916058540344</v>
       </c>
       <c r="H1740" t="n">
         <v>765876</v>
@@ -50858,7 +50858,7 @@
         <v>1.94900000095367</v>
       </c>
       <c r="G1741" t="n">
-        <v>1.73272323608398</v>
+        <v>1.73272311687469</v>
       </c>
       <c r="H1741" t="n">
         <v>1187656</v>
@@ -50916,7 +50916,7 @@
         <v>1.92700004577637</v>
       </c>
       <c r="G1743" t="n">
-        <v>1.71316456794739</v>
+        <v>1.7131644487381</v>
       </c>
       <c r="H1743" t="n">
         <v>815109</v>
@@ -50945,7 +50945,7 @@
         <v>1.96700000762939</v>
       </c>
       <c r="G1744" t="n">
-        <v>1.74872577190399</v>
+        <v>1.7487256526947</v>
       </c>
       <c r="H1744" t="n">
         <v>924610</v>
@@ -50974,7 +50974,7 @@
         <v>2.03399991989136</v>
       </c>
       <c r="G1745" t="n">
-        <v>1.80829083919525</v>
+        <v>1.80829107761383</v>
       </c>
       <c r="H1745" t="n">
         <v>1414180</v>
@@ -51003,7 +51003,7 @@
         <v>2.05399990081787</v>
       </c>
       <c r="G1746" t="n">
-        <v>1.8260715007782</v>
+        <v>1.82607161998749</v>
       </c>
       <c r="H1746" t="n">
         <v>1362654</v>
@@ -51032,7 +51032,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1747" t="n">
-        <v>1.83140563964844</v>
+        <v>1.83140552043915</v>
       </c>
       <c r="H1747" t="n">
         <v>994050</v>
@@ -51061,7 +51061,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1748" t="n">
-        <v>1.85807681083679</v>
+        <v>1.8580766916275</v>
       </c>
       <c r="H1748" t="n">
         <v>2071710</v>
@@ -51090,7 +51090,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G1749" t="n">
-        <v>1.89185988903046</v>
+        <v>1.89186000823975</v>
       </c>
       <c r="H1749" t="n">
         <v>1305734</v>
@@ -51119,7 +51119,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1750" t="n">
-        <v>1.90252816677094</v>
+        <v>1.90252828598022</v>
       </c>
       <c r="H1750" t="n">
         <v>1058340</v>
@@ -51177,7 +51177,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1752" t="n">
-        <v>1.90252816677094</v>
+        <v>1.90252828598022</v>
       </c>
       <c r="H1752" t="n">
         <v>941769</v>
@@ -51206,7 +51206,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1753" t="n">
-        <v>1.91141855716705</v>
+        <v>1.91141867637634</v>
       </c>
       <c r="H1753" t="n">
         <v>568003</v>
@@ -51235,7 +51235,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G1754" t="n">
-        <v>1.92742109298706</v>
+        <v>1.92742133140564</v>
       </c>
       <c r="H1754" t="n">
         <v>821928</v>
@@ -51264,7 +51264,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G1755" t="n">
-        <v>1.92742109298706</v>
+        <v>1.92742133140564</v>
       </c>
       <c r="H1755" t="n">
         <v>564229</v>
@@ -51293,7 +51293,7 @@
         <v>2.20600008964539</v>
       </c>
       <c r="G1756" t="n">
-        <v>1.96120417118073</v>
+        <v>1.9612044095993</v>
       </c>
       <c r="H1756" t="n">
         <v>967007</v>
@@ -51322,7 +51322,7 @@
         <v>2.19600009918213</v>
       </c>
       <c r="G1757" t="n">
-        <v>1.95231413841248</v>
+        <v>1.95231437683105</v>
       </c>
       <c r="H1757" t="n">
         <v>1317743</v>
@@ -51351,7 +51351,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G1758" t="n">
-        <v>1.92919933795929</v>
+        <v>1.92919945716858</v>
       </c>
       <c r="H1758" t="n">
         <v>613120</v>
@@ -51380,7 +51380,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G1759" t="n">
-        <v>1.93097734451294</v>
+        <v>1.93097722530365</v>
       </c>
       <c r="H1759" t="n">
         <v>3733233</v>
@@ -51409,7 +51409,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1760" t="n">
-        <v>1.94697988033295</v>
+        <v>1.94697999954224</v>
       </c>
       <c r="H1760" t="n">
         <v>957602</v>
@@ -51438,7 +51438,7 @@
         <v>2.16799998283386</v>
       </c>
       <c r="G1761" t="n">
-        <v>1.92742109298706</v>
+        <v>1.92742133140564</v>
       </c>
       <c r="H1761" t="n">
         <v>800566</v>
@@ -51467,7 +51467,7 @@
         <v>2.25</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.00032186508179</v>
+        <v>2.00032210350037</v>
       </c>
       <c r="H1762" t="n">
         <v>1749102</v>
@@ -51496,7 +51496,7 @@
         <v>2.34800004959106</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.08744668960571</v>
+        <v>2.08744692802429</v>
       </c>
       <c r="H1763" t="n">
         <v>2225248</v>
@@ -51525,7 +51525,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.10700559616089</v>
+        <v>2.10700583457947</v>
       </c>
       <c r="H1764" t="n">
         <v>1941030</v>
@@ -51554,7 +51554,7 @@
         <v>2.33599996566772</v>
       </c>
       <c r="G1765" t="n">
-        <v>2.07677841186523</v>
+        <v>2.07677865028381</v>
       </c>
       <c r="H1765" t="n">
         <v>2065923</v>
@@ -51583,7 +51583,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.07322239875793</v>
+        <v>2.07322216033936</v>
       </c>
       <c r="H1766" t="n">
         <v>1283914</v>
@@ -51641,7 +51641,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G1768" t="n">
-        <v>2.12123012542725</v>
+        <v>2.12123036384583</v>
       </c>
       <c r="H1768" t="n">
         <v>920473</v>
@@ -51670,7 +51670,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.0643322467804</v>
+        <v>2.06433200836182</v>
       </c>
       <c r="H1769" t="n">
         <v>1440384</v>
@@ -51757,7 +51757,7 @@
         <v>2.17400002479553</v>
       </c>
       <c r="G1772" t="n">
-        <v>1.93275535106659</v>
+        <v>1.93275547027588</v>
       </c>
       <c r="H1772" t="n">
         <v>2784866</v>
@@ -51873,7 +51873,7 @@
         <v>2.10400009155273</v>
       </c>
       <c r="G1776" t="n">
-        <v>1.87052309513092</v>
+        <v>1.87052321434021</v>
       </c>
       <c r="H1776" t="n">
         <v>1778785</v>
@@ -51902,7 +51902,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1777" t="n">
-        <v>1.88474774360657</v>
+        <v>1.88474762439728</v>
       </c>
       <c r="H1777" t="n">
         <v>1349017</v>
@@ -51931,7 +51931,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1778" t="n">
-        <v>1.89363825321198</v>
+        <v>1.8936380147934</v>
       </c>
       <c r="H1778" t="n">
         <v>791692</v>
@@ -51960,7 +51960,7 @@
         <v>2.1340000629425</v>
       </c>
       <c r="G1779" t="n">
-        <v>1.89719390869141</v>
+        <v>1.89719414710999</v>
       </c>
       <c r="H1779" t="n">
         <v>823651</v>
@@ -52018,7 +52018,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1781" t="n">
-        <v>1.91141855716705</v>
+        <v>1.91141867637634</v>
       </c>
       <c r="H1781" t="n">
         <v>872960</v>
@@ -52076,7 +52076,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1783" t="n">
-        <v>1.92030894756317</v>
+        <v>1.92030918598175</v>
       </c>
       <c r="H1783" t="n">
         <v>339479</v>
@@ -52105,7 +52105,7 @@
         <v>2.16599988937378</v>
       </c>
       <c r="G1784" t="n">
-        <v>1.92564308643341</v>
+        <v>1.92564296722412</v>
       </c>
       <c r="H1784" t="n">
         <v>752659</v>
@@ -52134,7 +52134,7 @@
         <v>2.23600006103516</v>
       </c>
       <c r="G1785" t="n">
-        <v>1.9878751039505</v>
+        <v>1.98787534236908</v>
       </c>
       <c r="H1785" t="n">
         <v>1197888</v>
@@ -52192,7 +52192,7 @@
         <v>2.25</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.00032186508179</v>
+        <v>2.00032210350037</v>
       </c>
       <c r="H1787" t="n">
         <v>529560</v>
@@ -52250,7 +52250,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.01454639434814</v>
+        <v>2.01454663276672</v>
       </c>
       <c r="H1789" t="n">
         <v>1136288</v>
@@ -52279,7 +52279,7 @@
         <v>2.31599998474121</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.058997631073</v>
+        <v>2.05899786949158</v>
       </c>
       <c r="H1790" t="n">
         <v>1186227</v>
@@ -52366,7 +52366,7 @@
         <v>2.32200002670288</v>
       </c>
       <c r="G1793" t="n">
-        <v>2.0643322467804</v>
+        <v>2.06433200836182</v>
       </c>
       <c r="H1793" t="n">
         <v>490453</v>
@@ -52424,7 +52424,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.05366373062134</v>
+        <v>2.05366349220276</v>
       </c>
       <c r="H1795" t="n">
         <v>1280942</v>
@@ -52453,7 +52453,7 @@
         <v>2.22199988365173</v>
       </c>
       <c r="G1796" t="n">
-        <v>1.97542893886566</v>
+        <v>1.97542870044708</v>
       </c>
       <c r="H1796" t="n">
         <v>1565756</v>
@@ -52511,7 +52511,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.01810264587402</v>
+        <v>2.01810216903687</v>
       </c>
       <c r="H1798" t="n">
         <v>691923</v>
@@ -52598,7 +52598,7 @@
         <v>2.21399998664856</v>
       </c>
       <c r="G1801" t="n">
-        <v>1.96831691265106</v>
+        <v>1.96831667423248</v>
       </c>
       <c r="H1801" t="n">
         <v>824751</v>
@@ -52627,7 +52627,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1802" t="n">
-        <v>1.9736510515213</v>
+        <v>1.97365081310272</v>
       </c>
       <c r="H1802" t="n">
         <v>595172</v>
@@ -52685,7 +52685,7 @@
         <v>2.20199990272522</v>
       </c>
       <c r="G1804" t="n">
-        <v>1.95764803886414</v>
+        <v>1.95764827728271</v>
       </c>
       <c r="H1804" t="n">
         <v>788765</v>
@@ -52801,7 +52801,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.25814127922058</v>
+        <v>2.25814080238342</v>
       </c>
       <c r="H1808" t="n">
         <v>1656175</v>
@@ -52859,7 +52859,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.32037329673767</v>
+        <v>2.32037305831909</v>
       </c>
       <c r="H1810" t="n">
         <v>2063443</v>
@@ -52917,7 +52917,7 @@
         <v>2.61400008201599</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.32392954826355</v>
+        <v>2.32392930984497</v>
       </c>
       <c r="H1812" t="n">
         <v>1181161</v>
@@ -52946,7 +52946,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.35593485832214</v>
+        <v>2.35593461990356</v>
       </c>
       <c r="H1813" t="n">
         <v>1194310</v>
@@ -52975,7 +52975,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.34526586532593</v>
+        <v>2.34526610374451</v>
       </c>
       <c r="H1814" t="n">
         <v>709549</v>
@@ -53004,7 +53004,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.33637571334839</v>
+        <v>2.33637595176697</v>
       </c>
       <c r="H1815" t="n">
         <v>571678</v>
@@ -53033,7 +53033,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G1816" t="n">
-        <v>2.33993172645569</v>
+        <v>2.33993196487427</v>
       </c>
       <c r="H1816" t="n">
         <v>708046</v>
@@ -53062,7 +53062,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.32037329673767</v>
+        <v>2.32037305831909</v>
       </c>
       <c r="H1817" t="n">
         <v>870990</v>
@@ -53091,7 +53091,7 @@
         <v>2.59400010108948</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.30614900588989</v>
+        <v>2.30614876747131</v>
       </c>
       <c r="H1818" t="n">
         <v>473208</v>
@@ -53120,7 +53120,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.2937023639679</v>
+        <v>2.29370212554932</v>
       </c>
       <c r="H1819" t="n">
         <v>641477</v>
@@ -53207,7 +53207,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.26525354385376</v>
+        <v>2.26525330543518</v>
       </c>
       <c r="H1822" t="n">
         <v>807379</v>
@@ -53265,7 +53265,7 @@
         <v>2.57399988174438</v>
       </c>
       <c r="G1824" t="n">
-        <v>2.28836822509766</v>
+        <v>2.28836798667908</v>
       </c>
       <c r="H1824" t="n">
         <v>698474</v>
@@ -53294,7 +53294,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.32037329673767</v>
+        <v>2.32037305831909</v>
       </c>
       <c r="H1825" t="n">
         <v>850330</v>
@@ -53323,7 +53323,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.32926368713379</v>
+        <v>2.32926344871521</v>
       </c>
       <c r="H1826" t="n">
         <v>594559</v>
@@ -53352,7 +53352,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.35415649414062</v>
+        <v>2.35415625572205</v>
       </c>
       <c r="H1827" t="n">
         <v>811441</v>
@@ -53410,7 +53410,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.33815407752991</v>
+        <v>2.33815383911133</v>
       </c>
       <c r="H1829" t="n">
         <v>725507</v>
@@ -53526,7 +53526,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G1833" t="n">
-        <v>2.13723254203796</v>
+        <v>2.13723278045654</v>
       </c>
       <c r="H1833" t="n">
         <v>1420099</v>
@@ -53642,7 +53642,7 @@
         <v>2.35800004005432</v>
       </c>
       <c r="G1837" t="n">
-        <v>2.09633708000183</v>
+        <v>2.09633731842041</v>
       </c>
       <c r="H1837" t="n">
         <v>1271017</v>
@@ -53671,7 +53671,7 @@
         <v>2.38599991798401</v>
       </c>
       <c r="G1838" t="n">
-        <v>2.12123012542725</v>
+        <v>2.12123036384583</v>
       </c>
       <c r="H1838" t="n">
         <v>583673</v>
@@ -53700,7 +53700,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G1839" t="n">
-        <v>2.15679121017456</v>
+        <v>2.15679168701172</v>
       </c>
       <c r="H1839" t="n">
         <v>470668</v>
@@ -53758,7 +53758,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G1841" t="n">
-        <v>2.12300825119019</v>
+        <v>2.12300801277161</v>
       </c>
       <c r="H1841" t="n">
         <v>399083</v>
@@ -53845,7 +53845,7 @@
         <v>2.33200001716614</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.07322239875793</v>
+        <v>2.07322216033936</v>
       </c>
       <c r="H1844" t="n">
         <v>558490</v>
@@ -53932,7 +53932,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.14256691932678</v>
+        <v>2.14256715774536</v>
       </c>
       <c r="H1847" t="n">
         <v>692716</v>
@@ -53990,7 +53990,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G1849" t="n">
-        <v>2.19768691062927</v>
+        <v>2.19768714904785</v>
       </c>
       <c r="H1849" t="n">
         <v>1015705</v>
@@ -54048,7 +54048,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G1851" t="n">
-        <v>2.19768691062927</v>
+        <v>2.19768714904785</v>
       </c>
       <c r="H1851" t="n">
         <v>765803</v>
@@ -54135,7 +54135,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.25102877616882</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1854" t="n">
         <v>527515</v>
@@ -54222,7 +54222,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.32926368713379</v>
+        <v>2.32926344871521</v>
       </c>
       <c r="H1857" t="n">
         <v>1227483</v>
@@ -54251,7 +54251,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.35593485832214</v>
+        <v>2.35593461990356</v>
       </c>
       <c r="H1858" t="n">
         <v>1769297</v>
@@ -54280,7 +54280,7 @@
         <v>2.57599997520447</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.29014611244202</v>
+        <v>2.2901463508606</v>
       </c>
       <c r="H1859" t="n">
         <v>6028161</v>
@@ -54338,7 +54338,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.39505171775818</v>
+        <v>2.39505195617676</v>
       </c>
       <c r="H1861" t="n">
         <v>1519947</v>
@@ -54367,7 +54367,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.43416929244995</v>
+        <v>2.43416953086853</v>
       </c>
       <c r="H1862" t="n">
         <v>1149222</v>
@@ -54396,7 +54396,7 @@
         <v>2.69400000572205</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.39505171775818</v>
+        <v>2.39505195617676</v>
       </c>
       <c r="H1863" t="n">
         <v>740688</v>
@@ -54425,7 +54425,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.41461086273193</v>
+        <v>2.41461062431335</v>
       </c>
       <c r="H1864" t="n">
         <v>988137</v>
@@ -54483,7 +54483,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.40572071075439</v>
+        <v>2.40572047233582</v>
       </c>
       <c r="H1866" t="n">
         <v>1200482</v>
@@ -54512,7 +54512,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.40394234657288</v>
+        <v>2.4039421081543</v>
       </c>
       <c r="H1867" t="n">
         <v>1175289</v>
@@ -54570,7 +54570,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.38082718849182</v>
+        <v>2.3808274269104</v>
       </c>
       <c r="H1869" t="n">
         <v>449259</v>
@@ -54599,7 +54599,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.41461086273193</v>
+        <v>2.41461062431335</v>
       </c>
       <c r="H1870" t="n">
         <v>874987</v>
@@ -54628,7 +54628,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.45906257629395</v>
+        <v>2.45906233787537</v>
       </c>
       <c r="H1871" t="n">
         <v>1021782</v>
@@ -54744,7 +54744,7 @@
         <v>2.71600008010864</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.41461086273193</v>
+        <v>2.41461062431335</v>
       </c>
       <c r="H1875" t="n">
         <v>408308</v>
@@ -54773,7 +54773,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.34882211685181</v>
+        <v>2.34882235527039</v>
       </c>
       <c r="H1876" t="n">
         <v>1247634</v>
@@ -54802,7 +54802,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.34882211685181</v>
+        <v>2.34882235527039</v>
       </c>
       <c r="H1877" t="n">
         <v>851789</v>
@@ -54889,7 +54889,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.36482524871826</v>
+        <v>2.36482501029968</v>
       </c>
       <c r="H1880" t="n">
         <v>603710</v>
@@ -54918,7 +54918,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.33993172645569</v>
+        <v>2.33993196487427</v>
       </c>
       <c r="H1881" t="n">
         <v>501774</v>
@@ -55034,7 +55034,7 @@
         <v>2.5220000743866</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.24213838577271</v>
+        <v>2.24213862419128</v>
       </c>
       <c r="H1885" t="n">
         <v>609802</v>
@@ -55063,7 +55063,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.22080159187317</v>
+        <v>2.22080135345459</v>
       </c>
       <c r="H1886" t="n">
         <v>389239</v>
@@ -55121,7 +55121,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.25280690193176</v>
+        <v>2.25280666351318</v>
       </c>
       <c r="H1888" t="n">
         <v>1396545</v>
@@ -55237,7 +55237,7 @@
         <v>2.66199994087219</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.36660265922546</v>
+        <v>2.36660289764404</v>
       </c>
       <c r="H1892" t="n">
         <v>2118016</v>
@@ -55295,7 +55295,7 @@
         <v>2.66400003433228</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.36838102340698</v>
+        <v>2.3683807849884</v>
       </c>
       <c r="H1894" t="n">
         <v>772214</v>
@@ -55411,7 +55411,7 @@
         <v>2.53399991989136</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.25280690193176</v>
+        <v>2.25280666351318</v>
       </c>
       <c r="H1898" t="n">
         <v>4536907</v>
@@ -55440,7 +55440,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.19768691062927</v>
+        <v>2.19768714904785</v>
       </c>
       <c r="H1899" t="n">
         <v>2366569</v>
@@ -55469,7 +55469,7 @@
         <v>2.42199993133545</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.2067985534668</v>
+        <v>2.20679831504822</v>
       </c>
       <c r="H1900" t="n">
         <v>1515064</v>
@@ -55556,7 +55556,7 @@
         <v>2.44199991226196</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.22502112388611</v>
+        <v>2.22502136230469</v>
       </c>
       <c r="H1903" t="n">
         <v>653498</v>
@@ -55585,7 +55585,7 @@
         <v>2.41400003433228</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.19950938224792</v>
+        <v>2.19950914382935</v>
       </c>
       <c r="H1904" t="n">
         <v>629954</v>
@@ -55730,7 +55730,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.3143138885498</v>
+        <v>2.31431365013123</v>
       </c>
       <c r="H1909" t="n">
         <v>1508750</v>
@@ -55817,7 +55817,7 @@
         <v>2.53800010681152</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.31249165534973</v>
+        <v>2.31249141693115</v>
       </c>
       <c r="H1912" t="n">
         <v>964726</v>
@@ -55846,7 +55846,7 @@
         <v>2.46600008010864</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.2468888759613</v>
+        <v>2.24688911437988</v>
       </c>
       <c r="H1913" t="n">
         <v>1020156</v>
@@ -55875,7 +55875,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.27604579925537</v>
+        <v>2.27604532241821</v>
       </c>
       <c r="H1914" t="n">
         <v>808937</v>
@@ -55904,7 +55904,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.29062366485596</v>
+        <v>2.29062390327454</v>
       </c>
       <c r="H1915" t="n">
         <v>692837</v>
@@ -55962,7 +55962,7 @@
         <v>2.54399991035461</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.31795811653137</v>
+        <v>2.31795835494995</v>
       </c>
       <c r="H1917" t="n">
         <v>543910</v>
@@ -55991,7 +55991,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.3143138885498</v>
+        <v>2.31431365013123</v>
       </c>
       <c r="H1918" t="n">
         <v>763017</v>
@@ -56049,7 +56049,7 @@
         <v>2.51399993896484</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.29062366485596</v>
+        <v>2.29062390327454</v>
       </c>
       <c r="H1920" t="n">
         <v>455957</v>
@@ -56107,7 +56107,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.24871134757996</v>
+        <v>2.24871110916138</v>
       </c>
       <c r="H1922" t="n">
         <v>813677</v>
@@ -56165,7 +56165,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.23048830032349</v>
+        <v>2.23048806190491</v>
       </c>
       <c r="H1924" t="n">
         <v>542712</v>
@@ -56194,7 +56194,7 @@
         <v>2.46399998664856</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.24506664276123</v>
+        <v>2.24506640434265</v>
       </c>
       <c r="H1925" t="n">
         <v>768954</v>
@@ -56281,7 +56281,7 @@
         <v>2.50200009346008</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.2796905040741</v>
+        <v>2.27969026565552</v>
       </c>
       <c r="H1928" t="n">
         <v>750746</v>
@@ -56310,7 +56310,7 @@
         <v>2.48399996757507</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.26328945159912</v>
+        <v>2.26328921318054</v>
       </c>
       <c r="H1929" t="n">
         <v>488118</v>
@@ -56339,7 +56339,7 @@
         <v>2.49799990653992</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.27604579925537</v>
+        <v>2.27604532241821</v>
       </c>
       <c r="H1930" t="n">
         <v>404571</v>
@@ -56397,7 +56397,7 @@
         <v>2.38800001144409</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.17581939697266</v>
+        <v>2.17581915855408</v>
       </c>
       <c r="H1932" t="n">
         <v>1487337</v>
@@ -56484,7 +56484,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.09381628036499</v>
+        <v>2.09381604194641</v>
       </c>
       <c r="H1935" t="n">
         <v>731567</v>
@@ -56571,7 +56571,7 @@
         <v>2.28200006484985</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.07923793792725</v>
+        <v>2.07923769950867</v>
       </c>
       <c r="H1938" t="n">
         <v>1185890</v>
@@ -56600,7 +56600,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.06283688545227</v>
+        <v>2.06283712387085</v>
       </c>
       <c r="H1939" t="n">
         <v>400759</v>
@@ -56629,7 +56629,7 @@
         <v>2.29800009727478</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.09381628036499</v>
+        <v>2.09381604194641</v>
       </c>
       <c r="H1940" t="n">
         <v>264822</v>
@@ -56716,7 +56716,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G1943" t="n">
-        <v>1.99905681610107</v>
+        <v>1.9990565776825</v>
       </c>
       <c r="H1943" t="n">
         <v>657168</v>
@@ -56774,7 +56774,7 @@
         <v>2.23799991607666</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.03914713859558</v>
+        <v>2.03914737701416</v>
       </c>
       <c r="H1945" t="n">
         <v>453880</v>
@@ -56803,7 +56803,7 @@
         <v>2.21600008010864</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.01910209655762</v>
+        <v>2.0191023349762</v>
       </c>
       <c r="H1946" t="n">
         <v>689901</v>
@@ -56861,7 +56861,7 @@
         <v>2.19199991226196</v>
       </c>
       <c r="G1948" t="n">
-        <v>1.99723446369171</v>
+        <v>1.99723422527313</v>
       </c>
       <c r="H1948" t="n">
         <v>591803</v>
@@ -56977,7 +56977,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.10657238960266</v>
+        <v>2.1065719127655</v>
       </c>
       <c r="H1952" t="n">
         <v>864742</v>
@@ -57006,7 +57006,7 @@
         <v>2.31200003623962</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.10657238960266</v>
+        <v>2.1065719127655</v>
       </c>
       <c r="H1953" t="n">
         <v>347603</v>
@@ -57151,7 +57151,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G1958" t="n">
-        <v>1.99905681610107</v>
+        <v>1.9990565776825</v>
       </c>
       <c r="H1958" t="n">
         <v>645295</v>
@@ -57180,7 +57180,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G1959" t="n">
-        <v>1.97901165485382</v>
+        <v>1.97901141643524</v>
       </c>
       <c r="H1959" t="n">
         <v>993929</v>
@@ -57325,7 +57325,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1964" t="n">
-        <v>1.94985496997833</v>
+        <v>1.94985485076904</v>
       </c>
       <c r="H1964" t="n">
         <v>1458841</v>
@@ -57412,7 +57412,7 @@
         <v>2.06800007820129</v>
       </c>
       <c r="G1967" t="n">
-        <v>1.88425230979919</v>
+        <v>1.88425242900848</v>
       </c>
       <c r="H1967" t="n">
         <v>3308354</v>
@@ -57441,7 +57441,7 @@
         <v>2.00200009346008</v>
       </c>
       <c r="G1968" t="n">
-        <v>1.82411658763885</v>
+        <v>1.82411646842957</v>
       </c>
       <c r="H1968" t="n">
         <v>2318938</v>
@@ -57470,7 +57470,7 @@
         <v>1.90400004386902</v>
       </c>
       <c r="G1969" t="n">
-        <v>1.73482429981232</v>
+        <v>1.73482418060303</v>
       </c>
       <c r="H1969" t="n">
         <v>2118233</v>
@@ -57528,7 +57528,7 @@
         <v>1.91600000858307</v>
       </c>
       <c r="G1971" t="n">
-        <v>1.74575781822205</v>
+        <v>1.74575793743134</v>
       </c>
       <c r="H1971" t="n">
         <v>1115161</v>
@@ -57557,7 +57557,7 @@
         <v>1.93599998950958</v>
       </c>
       <c r="G1972" t="n">
-        <v>1.76398086547852</v>
+        <v>1.76398074626923</v>
       </c>
       <c r="H1972" t="n">
         <v>593995</v>
@@ -57702,7 +57702,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G1977" t="n">
-        <v>1.67104387283325</v>
+        <v>1.67104375362396</v>
       </c>
       <c r="H1977" t="n">
         <v>913916</v>
@@ -57731,7 +57731,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1978" t="n">
-        <v>1.68197751045227</v>
+        <v>1.68197762966156</v>
       </c>
       <c r="H1978" t="n">
         <v>1381901</v>
@@ -57789,7 +57789,7 @@
         <v>1.84599995613098</v>
       </c>
       <c r="G1980" t="n">
-        <v>1.68197751045227</v>
+        <v>1.68197762966156</v>
       </c>
       <c r="H1980" t="n">
         <v>984110</v>
@@ -57905,7 +57905,7 @@
         <v>1.75</v>
       </c>
       <c r="G1984" t="n">
-        <v>1.59450745582581</v>
+        <v>1.5945075750351</v>
       </c>
       <c r="H1984" t="n">
         <v>849263</v>
@@ -58050,7 +58050,7 @@
         <v>1.64400005340576</v>
       </c>
       <c r="G1989" t="n">
-        <v>1.4979259967804</v>
+        <v>1.49792587757111</v>
       </c>
       <c r="H1989" t="n">
         <v>4784857</v>
@@ -58108,7 +58108,7 @@
         <v>1.65199995040894</v>
       </c>
       <c r="G1991" t="n">
-        <v>1.50521492958069</v>
+        <v>1.50521504878998</v>
       </c>
       <c r="H1991" t="n">
         <v>1164182</v>
@@ -58137,7 +58137,7 @@
         <v>1.65900003910065</v>
       </c>
       <c r="G1992" t="n">
-        <v>1.51159298419952</v>
+        <v>1.51159310340881</v>
       </c>
       <c r="H1992" t="n">
         <v>907658</v>
@@ -58224,7 +58224,7 @@
         <v>1.6710000038147</v>
       </c>
       <c r="G1995" t="n">
-        <v>1.52252697944641</v>
+        <v>1.52252686023712</v>
       </c>
       <c r="H1995" t="n">
         <v>771163</v>
@@ -58282,7 +58282,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G1997" t="n">
-        <v>1.54530560970306</v>
+        <v>1.54530549049377</v>
       </c>
       <c r="H1997" t="n">
         <v>995871</v>
@@ -58311,7 +58311,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G1998" t="n">
-        <v>1.5835736989975</v>
+        <v>1.58357381820679</v>
       </c>
       <c r="H1998" t="n">
         <v>987252</v>
@@ -58340,7 +58340,7 @@
         <v>1.71899998188019</v>
       </c>
       <c r="G1999" t="n">
-        <v>1.56626176834106</v>
+        <v>1.56626188755035</v>
       </c>
       <c r="H1999" t="n">
         <v>860658</v>
@@ -58485,7 +58485,7 @@
         <v>1.73099994659424</v>
       </c>
       <c r="G2004" t="n">
-        <v>1.57719564437866</v>
+        <v>1.57719552516937</v>
       </c>
       <c r="H2004" t="n">
         <v>476169</v>
@@ -58746,7 +58746,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2013" t="n">
-        <v>1.6400648355484</v>
+        <v>1.64006471633911</v>
       </c>
       <c r="H2013" t="n">
         <v>453129</v>
@@ -58804,7 +58804,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G2015" t="n">
-        <v>1.69017803668976</v>
+        <v>1.69017791748047</v>
       </c>
       <c r="H2015" t="n">
         <v>2126831</v>
@@ -58833,7 +58833,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G2016" t="n">
-        <v>1.80224907398224</v>
+        <v>1.80224919319153</v>
       </c>
       <c r="H2016" t="n">
         <v>3474495</v>
@@ -58920,7 +58920,7 @@
         <v>2.07200002670288</v>
       </c>
       <c r="G2019" t="n">
-        <v>1.88789689540863</v>
+        <v>1.88789677619934</v>
       </c>
       <c r="H2019" t="n">
         <v>2960692</v>
@@ -58949,7 +58949,7 @@
         <v>2.12199997901917</v>
       </c>
       <c r="G2020" t="n">
-        <v>1.93345427513123</v>
+        <v>1.93345415592194</v>
       </c>
       <c r="H2020" t="n">
         <v>2309920</v>
@@ -59007,7 +59007,7 @@
         <v>2.05599999427795</v>
       </c>
       <c r="G2022" t="n">
-        <v>1.87331855297089</v>
+        <v>1.8733184337616</v>
       </c>
       <c r="H2022" t="n">
         <v>1860243</v>
@@ -59210,7 +59210,7 @@
         <v>2.24799990653992</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.04825878143311</v>
+        <v>2.04825854301453</v>
       </c>
       <c r="H2029" t="n">
         <v>953782</v>
@@ -59268,7 +59268,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.06465935707092</v>
+        <v>2.0646595954895</v>
       </c>
       <c r="H2031" t="n">
         <v>1070287</v>
@@ -59384,7 +59384,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G2035" t="n">
-        <v>2.06283688545227</v>
+        <v>2.06283712387085</v>
       </c>
       <c r="H2035" t="n">
         <v>572356</v>
@@ -59442,7 +59442,7 @@
         <v>2.25600004196167</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.0555477142334</v>
+        <v>2.05554795265198</v>
       </c>
       <c r="H2037" t="n">
         <v>584350</v>
@@ -59471,7 +59471,7 @@
         <v>2.18600010871887</v>
       </c>
       <c r="G2038" t="n">
-        <v>1.99176752567291</v>
+        <v>1.99176776409149</v>
       </c>
       <c r="H2038" t="n">
         <v>909339</v>
@@ -59500,7 +59500,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2039" t="n">
-        <v>1.95896625518799</v>
+        <v>1.95896649360657</v>
       </c>
       <c r="H2039" t="n">
         <v>1050388</v>
@@ -59529,7 +59529,7 @@
         <v>2.12599992752075</v>
       </c>
       <c r="G2040" t="n">
-        <v>1.93709886074066</v>
+        <v>1.93709874153137</v>
       </c>
       <c r="H2040" t="n">
         <v>796113</v>
@@ -59558,7 +59558,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2041" t="n">
-        <v>1.95896625518799</v>
+        <v>1.95896649360657</v>
       </c>
       <c r="H2041" t="n">
         <v>663457</v>
@@ -59732,7 +59732,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2047" t="n">
-        <v>1.93892109394073</v>
+        <v>1.93892121315002</v>
       </c>
       <c r="H2047" t="n">
         <v>741451</v>
@@ -59761,7 +59761,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G2048" t="n">
-        <v>1.85874021053314</v>
+        <v>1.85874009132385</v>
       </c>
       <c r="H2048" t="n">
         <v>1658753</v>
@@ -59819,7 +59819,7 @@
         <v>2.03200006484985</v>
       </c>
       <c r="G2050" t="n">
-        <v>1.85145103931427</v>
+        <v>1.85145092010498</v>
       </c>
       <c r="H2050" t="n">
         <v>674798</v>
@@ -59848,7 +59848,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2051" t="n">
-        <v>1.88607466220856</v>
+        <v>1.88607442378998</v>
       </c>
       <c r="H2051" t="n">
         <v>393036</v>
@@ -59877,7 +59877,7 @@
         <v>2.09800004959106</v>
       </c>
       <c r="G2052" t="n">
-        <v>1.91158664226532</v>
+        <v>1.91158676147461</v>
       </c>
       <c r="H2052" t="n">
         <v>748313</v>
@@ -59906,7 +59906,7 @@
         <v>2.12800002098083</v>
       </c>
       <c r="G2053" t="n">
-        <v>1.93892109394073</v>
+        <v>1.93892121315002</v>
       </c>
       <c r="H2053" t="n">
         <v>970563</v>
@@ -59935,7 +59935,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2054" t="n">
-        <v>1.95896625518799</v>
+        <v>1.95896649360657</v>
       </c>
       <c r="H2054" t="n">
         <v>1073397</v>
@@ -59964,7 +59964,7 @@
         <v>2.17199993133545</v>
       </c>
       <c r="G2055" t="n">
-        <v>1.97901165485382</v>
+        <v>1.97901141643524</v>
       </c>
       <c r="H2055" t="n">
         <v>803438</v>
@@ -59993,7 +59993,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G2056" t="n">
-        <v>1.99905681610107</v>
+        <v>1.9990565776825</v>
       </c>
       <c r="H2056" t="n">
         <v>824094</v>
@@ -60080,7 +60080,7 @@
         <v>2.26399993896484</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.06283688545227</v>
+        <v>2.06283712387085</v>
       </c>
       <c r="H2059" t="n">
         <v>4800442</v>
@@ -60225,7 +60225,7 @@
         <v>2.2279999256134</v>
       </c>
       <c r="G2064" t="n">
-        <v>2.03003597259521</v>
+        <v>2.03003573417664</v>
       </c>
       <c r="H2064" t="n">
         <v>754905</v>
@@ -60254,7 +60254,7 @@
         <v>2.25</v>
       </c>
       <c r="G2065" t="n">
-        <v>2.05008101463318</v>
+        <v>2.05008125305176</v>
       </c>
       <c r="H2065" t="n">
         <v>777725</v>
@@ -60312,7 +60312,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2067" t="n">
-        <v>2.03185796737671</v>
+        <v>2.03185820579529</v>
       </c>
       <c r="H2067" t="n">
         <v>695494</v>
@@ -60341,7 +60341,7 @@
         <v>2.25</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.05008101463318</v>
+        <v>2.05008125305176</v>
       </c>
       <c r="H2068" t="n">
         <v>448734</v>
@@ -60370,7 +60370,7 @@
         <v>2.26600003242493</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.06465935707092</v>
+        <v>2.0646595954895</v>
       </c>
       <c r="H2069" t="n">
         <v>590832</v>
@@ -60399,7 +60399,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.03185796737671</v>
+        <v>2.03185820579529</v>
       </c>
       <c r="H2070" t="n">
         <v>712659</v>
@@ -60515,7 +60515,7 @@
         <v>2.19400000572205</v>
       </c>
       <c r="G2074" t="n">
-        <v>2.02631664276123</v>
+        <v>2.02631640434265</v>
       </c>
       <c r="H2074" t="n">
         <v>525414</v>
@@ -60544,7 +60544,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G2075" t="n">
-        <v>2.03185796737671</v>
+        <v>2.03185820579529</v>
       </c>
       <c r="H2075" t="n">
         <v>463047</v>
@@ -60776,7 +60776,7 @@
         <v>2.26799988746643</v>
       </c>
       <c r="G2083" t="n">
-        <v>2.09466075897217</v>
+        <v>2.09466099739075</v>
       </c>
       <c r="H2083" t="n">
         <v>941009</v>
@@ -60892,7 +60892,7 @@
         <v>2.22399997711182</v>
       </c>
       <c r="G2087" t="n">
-        <v>2.05402398109436</v>
+        <v>2.05402374267578</v>
       </c>
       <c r="H2087" t="n">
         <v>475416</v>
@@ -61298,7 +61298,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G2101" t="n">
-        <v>2.28306937217712</v>
+        <v>2.2830696105957</v>
       </c>
       <c r="H2101" t="n">
         <v>2512831</v>
@@ -61356,7 +61356,7 @@
         <v>2.35400009155273</v>
       </c>
       <c r="G2103" t="n">
-        <v>2.1740882396698</v>
+        <v>2.17408800125122</v>
       </c>
       <c r="H2103" t="n">
         <v>1885729</v>
@@ -61559,7 +61559,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2110" t="n">
-        <v>2.00415086746216</v>
+        <v>2.00415110588074</v>
       </c>
       <c r="H2110" t="n">
         <v>1068397</v>
@@ -61675,7 +61675,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G2114" t="n">
-        <v>2.26090407371521</v>
+        <v>2.26090383529663</v>
       </c>
       <c r="H2114" t="n">
         <v>2277715</v>
@@ -61733,7 +61733,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G2116" t="n">
-        <v>2.26090407371521</v>
+        <v>2.26090383529663</v>
       </c>
       <c r="H2116" t="n">
         <v>1592182</v>
@@ -61762,7 +61762,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2117" t="n">
-        <v>2.2442798614502</v>
+        <v>2.24427962303162</v>
       </c>
       <c r="H2117" t="n">
         <v>828882</v>
@@ -61936,7 +61936,7 @@
         <v>2.51600003242493</v>
       </c>
       <c r="G2123" t="n">
-        <v>2.32370686531067</v>
+        <v>2.32370662689209</v>
       </c>
       <c r="H2123" t="n">
         <v>1276768</v>
@@ -61994,7 +61994,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G2125" t="n">
-        <v>2.4086754322052</v>
+        <v>2.40867519378662</v>
       </c>
       <c r="H2125" t="n">
         <v>1128424</v>
@@ -62081,7 +62081,7 @@
         <v>2.6340000629425</v>
       </c>
       <c r="G2128" t="n">
-        <v>2.43268823623657</v>
+        <v>2.43268847465515</v>
       </c>
       <c r="H2128" t="n">
         <v>638512</v>
@@ -62110,7 +62110,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.44746518135071</v>
+        <v>2.44746541976929</v>
       </c>
       <c r="H2129" t="n">
         <v>1023965</v>
@@ -62139,7 +62139,7 @@
         <v>2.67600011825562</v>
       </c>
       <c r="G2130" t="n">
-        <v>2.47147846221924</v>
+        <v>2.47147822380066</v>
       </c>
       <c r="H2130" t="n">
         <v>1719985</v>
@@ -62371,7 +62371,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G2138" t="n">
-        <v>2.49918556213379</v>
+        <v>2.49918532371521</v>
       </c>
       <c r="H2138" t="n">
         <v>646234</v>
@@ -62545,7 +62545,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G2144" t="n">
-        <v>2.60631966590881</v>
+        <v>2.60631990432739</v>
       </c>
       <c r="H2144" t="n">
         <v>1254741</v>
@@ -62574,7 +62574,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G2145" t="n">
-        <v>2.58784818649292</v>
+        <v>2.5878484249115</v>
       </c>
       <c r="H2145" t="n">
         <v>1050361</v>
@@ -62603,7 +62603,7 @@
         <v>2.79399991035461</v>
       </c>
       <c r="G2146" t="n">
-        <v>2.58045959472656</v>
+        <v>2.58045983314514</v>
       </c>
       <c r="H2146" t="n">
         <v>809727</v>
@@ -62661,7 +62661,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G2148" t="n">
-        <v>2.64326286315918</v>
+        <v>2.6432626247406</v>
       </c>
       <c r="H2148" t="n">
         <v>1207232</v>
@@ -62893,7 +62893,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G2156" t="n">
-        <v>2.50287985801697</v>
+        <v>2.50287961959839</v>
       </c>
       <c r="H2156" t="n">
         <v>778835</v>
@@ -80096,6 +80096,35 @@
         <v>258317</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>5.84000015258789</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>5.6100001335144</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>5.79500007629395</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>5.79500007629395</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>203502</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>
